--- a/public/docs/tarifa-italgres.xlsx
+++ b/public/docs/tarifa-italgres.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amont\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C797C27-D4D1-46EB-AF59-938EA8A97074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0866BE2-7286-4926-B710-0A06FB3DB4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,32 +50,35 @@
     <sheet name="KERLUX" sheetId="119" r:id="rId35"/>
     <sheet name="KTL" sheetId="73" r:id="rId36"/>
     <sheet name="KRONOS" sheetId="111" r:id="rId37"/>
-    <sheet name="LIFE" sheetId="97" r:id="rId38"/>
-    <sheet name="LIVING" sheetId="65" r:id="rId39"/>
-    <sheet name="MH PARQUETS" sheetId="115" r:id="rId40"/>
-    <sheet name="MIRAGE" sheetId="30" r:id="rId41"/>
-    <sheet name="NATUCER" sheetId="110" r:id="rId42"/>
-    <sheet name="ONIX" sheetId="33" r:id="rId43"/>
-    <sheet name="PAVIGRES" sheetId="114" r:id="rId44"/>
-    <sheet name="PERONDA HARMONY" sheetId="80" r:id="rId45"/>
-    <sheet name="PERONDA-MUSEUM" sheetId="87" r:id="rId46"/>
-    <sheet name="PERONDA" sheetId="81" r:id="rId47"/>
-    <sheet name="PIEMME" sheetId="121" r:id="rId48"/>
-    <sheet name="PORTOBELLO" sheetId="78" r:id="rId49"/>
-    <sheet name="PROVENZA" sheetId="123" r:id="rId50"/>
-    <sheet name="REALONDA" sheetId="61" r:id="rId51"/>
-    <sheet name="SANT AGOSTINO" sheetId="43" r:id="rId52"/>
-    <sheet name="STN" sheetId="55" r:id="rId53"/>
-    <sheet name="VALLELUNGA" sheetId="82" r:id="rId54"/>
-    <sheet name="VENATTO" sheetId="45" r:id="rId55"/>
-    <sheet name="VIVES" sheetId="47" r:id="rId56"/>
+    <sheet name="LAMINAM" sheetId="126" r:id="rId38"/>
+    <sheet name="LIFE" sheetId="97" r:id="rId39"/>
+    <sheet name="LIVING" sheetId="65" r:id="rId40"/>
+    <sheet name="MH PARQUETS" sheetId="115" r:id="rId41"/>
+    <sheet name="MIA DESIGN" sheetId="128" r:id="rId42"/>
+    <sheet name="MIRAGE" sheetId="30" r:id="rId43"/>
+    <sheet name="NATUCER" sheetId="110" r:id="rId44"/>
+    <sheet name="ONIX" sheetId="33" r:id="rId45"/>
+    <sheet name="PAVIGRES" sheetId="114" r:id="rId46"/>
+    <sheet name="PERONDA HARMONY" sheetId="80" r:id="rId47"/>
+    <sheet name="PERONDA-MUSEUM" sheetId="87" r:id="rId48"/>
+    <sheet name="PERONDA" sheetId="81" r:id="rId49"/>
+    <sheet name="PIEMME" sheetId="121" r:id="rId50"/>
+    <sheet name="PORTOBELLO" sheetId="78" r:id="rId51"/>
+    <sheet name="PROVENZA" sheetId="123" r:id="rId52"/>
+    <sheet name="REALONDA" sheetId="61" r:id="rId53"/>
+    <sheet name="SANT AGOSTINO" sheetId="43" r:id="rId54"/>
+    <sheet name="SODAI" sheetId="127" r:id="rId55"/>
+    <sheet name="STN" sheetId="55" r:id="rId56"/>
+    <sheet name="VALLELUNGA" sheetId="82" r:id="rId57"/>
+    <sheet name="VENATTO" sheetId="45" r:id="rId58"/>
+    <sheet name="VIVES" sheetId="47" r:id="rId59"/>
   </sheets>
-  <calcPr calcId="181029" concurrentCalc="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2757" uniqueCount="1752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2813" uniqueCount="1770">
   <si>
     <t>SIZE</t>
   </si>
@@ -5538,9 +5541,6 @@
     <t>COTTO DÉSTE 2026</t>
   </si>
   <si>
-    <t>06.10.26</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kerlite </t>
   </si>
   <si>
@@ -5566,6 +5566,63 @@
   </si>
   <si>
     <t>Yosemite all the colours nat and grip</t>
+  </si>
+  <si>
+    <t>19.10.26</t>
+  </si>
+  <si>
+    <t>LAMINAM 2026</t>
+  </si>
+  <si>
+    <t>Bronzite rare bocciardato</t>
+  </si>
+  <si>
+    <t>Calacatta rosa rare dna</t>
+  </si>
+  <si>
+    <t>Ki no bi acai and Kuri</t>
+  </si>
+  <si>
+    <t>48"x118"</t>
+  </si>
+  <si>
+    <t>Quarzite rare dna</t>
+  </si>
+  <si>
+    <t>SODAI 2026</t>
+  </si>
+  <si>
+    <t>Titania bordeaux</t>
+  </si>
+  <si>
+    <t>Amber field beige ( FROM SPAIN)</t>
+  </si>
+  <si>
+    <t>Amber field beige ( FROM FLORIDA)</t>
+  </si>
+  <si>
+    <t>Banana bloom green ( FROM SPAIN)</t>
+  </si>
+  <si>
+    <t>Banana bloom green (FROM FLORIDA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (FROM SPAIN)</t>
+  </si>
+  <si>
+    <t>Travertine lux gold ( FROM FLORIDA)</t>
+  </si>
+  <si>
+    <t>MIA DESIGN 2026</t>
+  </si>
+  <si>
+    <t>24.10.26</t>
+  </si>
+  <si>
+    <t>DESCUENTO MÁXIMO 10 %</t>
+  </si>
+  <si>
+    <t>23 de oct</t>
   </si>
 </sst>
 </file>
@@ -5584,7 +5641,7 @@
     <numFmt numFmtId="171" formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * \-??_-;_-@_-"/>
     <numFmt numFmtId="172" formatCode="#,##0.00\ _€"/>
   </numFmts>
-  <fonts count="115">
+  <fonts count="117">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -6377,6 +6434,20 @@
     <font>
       <sz val="18"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -7391,7 +7462,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="440">
+  <cellXfs count="443">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="40" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -8001,13 +8072,16 @@
     </xf>
     <xf numFmtId="2" fontId="114" fillId="0" borderId="29" xfId="246" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="29" xfId="246" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="115" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="49" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="4" borderId="0" xfId="246" applyFont="1" applyFill="1" applyAlignment="1">
@@ -8053,6 +8127,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="80" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -8223,7 +8300,6 @@
     <xf numFmtId="0" fontId="49" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="16" fontId="55" fillId="0" borderId="0" xfId="246" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="313">
     <cellStyle name="Comma [0] 2" xfId="248" xr:uid="{00000000-0005-0000-0000-000025010000}"/>
@@ -8891,41 +8967,42 @@
       <c r="A1" s="333" t="s">
         <v>1701</v>
       </c>
-      <c r="B1" s="362" t="s">
+      <c r="B1" s="365" t="s">
         <v>1616</v>
       </c>
-      <c r="C1" s="362"/>
-      <c r="D1" s="362"/>
-      <c r="E1" s="362"/>
-      <c r="F1" s="362"/>
-      <c r="G1" s="362"/>
-      <c r="H1" s="362"/>
+      <c r="C1" s="365"/>
+      <c r="D1" s="365"/>
+      <c r="E1" s="365"/>
+      <c r="F1" s="365"/>
+      <c r="G1" s="365"/>
+      <c r="H1" s="365"/>
       <c r="I1" s="38"/>
     </row>
     <row r="2" spans="1:17" s="30" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B2" s="362"/>
-      <c r="C2" s="362"/>
-      <c r="D2" s="362"/>
-      <c r="E2" s="362"/>
-      <c r="F2" s="362"/>
-      <c r="G2" s="362"/>
-      <c r="H2" s="362"/>
+      <c r="B2" s="365"/>
+      <c r="C2" s="365"/>
+      <c r="D2" s="365"/>
+      <c r="E2" s="365"/>
+      <c r="F2" s="365"/>
+      <c r="G2" s="365"/>
+      <c r="H2" s="365"/>
       <c r="I2" s="38"/>
-      <c r="K2" s="439">
-        <v>46301</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" s="30" customFormat="1" ht="19.05" customHeight="1"/>
+    </row>
+    <row r="3" spans="1:17" s="30" customFormat="1" ht="19.05" customHeight="1">
+      <c r="K3" s="335" t="s">
+        <v>1769</v>
+      </c>
+    </row>
     <row r="4" spans="1:17" s="30" customFormat="1" ht="19.05" customHeight="1">
       <c r="O4" s="41"/>
       <c r="P4" s="41"/>
       <c r="Q4" s="41"/>
     </row>
     <row r="5" spans="1:17" s="30" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B5" s="363" t="s">
+      <c r="B5" s="366" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="363" t="s">
+      <c r="C5" s="366" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="106" t="s">
@@ -8943,8 +9020,8 @@
       <c r="Q5" s="41"/>
     </row>
     <row r="6" spans="1:17" s="30" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B6" s="363"/>
-      <c r="C6" s="363"/>
+      <c r="B6" s="366"/>
+      <c r="C6" s="366"/>
       <c r="D6" s="106" t="s">
         <v>104</v>
       </c>
@@ -8992,9 +9069,9 @@
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="32"/>
-      <c r="G8" s="364"/>
-      <c r="H8" s="364"/>
-      <c r="I8" s="364"/>
+      <c r="G8" s="367"/>
+      <c r="H8" s="367"/>
+      <c r="I8" s="367"/>
       <c r="J8" s="32"/>
       <c r="L8" s="31"/>
       <c r="M8" s="32"/>
@@ -9008,9 +9085,9 @@
       <c r="D9" s="189"/>
       <c r="E9" s="31"/>
       <c r="F9" s="32"/>
-      <c r="G9" s="364"/>
-      <c r="H9" s="364"/>
-      <c r="I9" s="364"/>
+      <c r="G9" s="367"/>
+      <c r="H9" s="367"/>
+      <c r="I9" s="367"/>
       <c r="J9" s="32"/>
       <c r="L9" s="31"/>
       <c r="M9" s="32"/>
@@ -9043,32 +9120,32 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1707</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
-      <c r="L2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
+      <c r="L2" s="363"/>
     </row>
     <row r="3" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+      <c r="L3" s="363"/>
     </row>
     <row r="4" spans="2:12" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -9078,10 +9155,10 @@
     <row r="5" spans="2:12" ht="19.05" customHeight="1" thickBot="1"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="374" t="s">
+      <c r="C6" s="377" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="376" t="s">
+      <c r="D6" s="379" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="130" t="s">
@@ -9092,8 +9169,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B7" s="13"/>
-      <c r="C7" s="375"/>
-      <c r="D7" s="361"/>
+      <c r="C7" s="378"/>
+      <c r="D7" s="380"/>
       <c r="E7" s="223" t="s">
         <v>100</v>
       </c>
@@ -9498,45 +9575,45 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A2" s="359" t="s">
+      <c r="A2" s="363" t="s">
         <v>1516</v>
       </c>
-      <c r="B2" s="359"/>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
+      <c r="B2" s="363"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
     </row>
     <row r="3" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A3" s="359"/>
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
+      <c r="A3" s="363"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
     </row>
     <row r="4" spans="1:11" ht="16.95" customHeight="1">
-      <c r="A4" s="359"/>
-      <c r="B4" s="359"/>
-      <c r="C4" s="359"/>
-      <c r="D4" s="359"/>
-      <c r="E4" s="359"/>
-      <c r="F4" s="359"/>
-      <c r="G4" s="359"/>
-      <c r="H4" s="359"/>
-      <c r="I4" s="359"/>
-      <c r="J4" s="359"/>
-      <c r="K4" s="359"/>
+      <c r="A4" s="363"/>
+      <c r="B4" s="363"/>
+      <c r="C4" s="363"/>
+      <c r="D4" s="363"/>
+      <c r="E4" s="363"/>
+      <c r="F4" s="363"/>
+      <c r="G4" s="363"/>
+      <c r="H4" s="363"/>
+      <c r="I4" s="363"/>
+      <c r="J4" s="363"/>
+      <c r="K4" s="363"/>
     </row>
     <row r="5" spans="1:11" ht="16.95" customHeight="1">
       <c r="A5" s="111"/>
@@ -9553,10 +9630,10 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="360" t="s">
+      <c r="B6" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="360" t="s">
+      <c r="C6" s="364" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="112" t="s">
@@ -9574,8 +9651,8 @@
     </row>
     <row r="7" spans="1:11" ht="21">
       <c r="A7" s="13"/>
-      <c r="B7" s="360"/>
-      <c r="C7" s="360"/>
+      <c r="B7" s="364"/>
+      <c r="C7" s="364"/>
       <c r="D7" s="112" t="s">
         <v>100</v>
       </c>
@@ -9687,32 +9764,32 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1524</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
-      <c r="L2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
+      <c r="L2" s="363"/>
     </row>
     <row r="3" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+      <c r="L3" s="363"/>
     </row>
     <row r="4" spans="2:12" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -9722,10 +9799,10 @@
     <row r="5" spans="2:12" ht="19.05" customHeight="1" thickBot="1"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="374" t="s">
+      <c r="C6" s="377" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="376" t="s">
+      <c r="D6" s="379" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="130" t="s">
@@ -9736,8 +9813,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B7" s="13"/>
-      <c r="C7" s="375"/>
-      <c r="D7" s="361"/>
+      <c r="C7" s="378"/>
+      <c r="D7" s="380"/>
       <c r="E7" s="223" t="s">
         <v>100</v>
       </c>
@@ -10244,32 +10321,32 @@
       <c r="K1" s="164"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="377" t="s">
+      <c r="A2" s="381" t="s">
         <v>1529</v>
       </c>
-      <c r="B2" s="377"/>
-      <c r="C2" s="377"/>
-      <c r="D2" s="377"/>
-      <c r="E2" s="377"/>
-      <c r="F2" s="377"/>
-      <c r="G2" s="377"/>
-      <c r="H2" s="377"/>
-      <c r="I2" s="377"/>
-      <c r="J2" s="377"/>
-      <c r="K2" s="377"/>
+      <c r="B2" s="381"/>
+      <c r="C2" s="381"/>
+      <c r="D2" s="381"/>
+      <c r="E2" s="381"/>
+      <c r="F2" s="381"/>
+      <c r="G2" s="381"/>
+      <c r="H2" s="381"/>
+      <c r="I2" s="381"/>
+      <c r="J2" s="381"/>
+      <c r="K2" s="381"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="377"/>
-      <c r="B3" s="377"/>
-      <c r="C3" s="377"/>
-      <c r="D3" s="377"/>
-      <c r="E3" s="377"/>
-      <c r="F3" s="377"/>
-      <c r="G3" s="377"/>
-      <c r="H3" s="377"/>
-      <c r="I3" s="377"/>
-      <c r="J3" s="377"/>
-      <c r="K3" s="377"/>
+      <c r="A3" s="381"/>
+      <c r="B3" s="381"/>
+      <c r="C3" s="381"/>
+      <c r="D3" s="381"/>
+      <c r="E3" s="381"/>
+      <c r="F3" s="381"/>
+      <c r="G3" s="381"/>
+      <c r="H3" s="381"/>
+      <c r="I3" s="381"/>
+      <c r="J3" s="381"/>
+      <c r="K3" s="381"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="164" t="s">
@@ -10301,10 +10378,10 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="374" t="s">
+      <c r="B6" s="377" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="376" t="s">
+      <c r="C6" s="379" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="167" t="s">
@@ -10320,8 +10397,8 @@
     </row>
     <row r="7" spans="1:11" ht="21.6" thickBot="1">
       <c r="A7" s="13"/>
-      <c r="B7" s="375"/>
-      <c r="C7" s="361"/>
+      <c r="B7" s="378"/>
+      <c r="C7" s="380"/>
       <c r="D7" s="178" t="s">
         <v>100</v>
       </c>
@@ -10618,24 +10695,24 @@
   <sheetData>
     <row r="1" spans="2:10" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:10" ht="19.05" customHeight="1">
-      <c r="B2" s="362" t="s">
+      <c r="B2" s="365" t="s">
         <v>1530</v>
       </c>
-      <c r="C2" s="362"/>
-      <c r="D2" s="362"/>
-      <c r="E2" s="362"/>
-      <c r="F2" s="362"/>
+      <c r="C2" s="365"/>
+      <c r="D2" s="365"/>
+      <c r="E2" s="365"/>
+      <c r="F2" s="365"/>
       <c r="G2" s="38"/>
       <c r="H2" s="38"/>
       <c r="I2" s="38"/>
       <c r="J2" s="38"/>
     </row>
     <row r="3" spans="2:10" ht="19.05" customHeight="1">
-      <c r="B3" s="362"/>
-      <c r="C3" s="362"/>
-      <c r="D3" s="362"/>
-      <c r="E3" s="362"/>
-      <c r="F3" s="362"/>
+      <c r="B3" s="365"/>
+      <c r="C3" s="365"/>
+      <c r="D3" s="365"/>
+      <c r="E3" s="365"/>
+      <c r="F3" s="365"/>
       <c r="G3" s="38"/>
       <c r="H3" s="38"/>
       <c r="I3" s="38"/>
@@ -10659,7 +10736,7 @@
     </row>
     <row r="6" spans="2:10" s="35" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="33"/>
-      <c r="C6" s="378" t="s">
+      <c r="C6" s="382" t="s">
         <v>99</v>
       </c>
       <c r="D6" s="179" t="s">
@@ -10667,7 +10744,7 @@
       </c>
       <c r="E6" s="180"/>
       <c r="F6" s="181"/>
-      <c r="G6" s="378" t="s">
+      <c r="G6" s="382" t="s">
         <v>99</v>
       </c>
       <c r="H6" s="179" t="s">
@@ -10676,13 +10753,13 @@
     </row>
     <row r="7" spans="2:10" s="35" customFormat="1" ht="19.05" customHeight="1">
       <c r="B7" s="33"/>
-      <c r="C7" s="378"/>
+      <c r="C7" s="382"/>
       <c r="D7" s="179" t="s">
         <v>98</v>
       </c>
       <c r="E7" s="180"/>
       <c r="F7" s="181"/>
-      <c r="G7" s="378"/>
+      <c r="G7" s="382"/>
       <c r="H7" s="179" t="s">
         <v>100</v>
       </c>
@@ -11613,32 +11690,32 @@
       <c r="K1" s="164"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="377" t="s">
+      <c r="A2" s="381" t="s">
         <v>1531</v>
       </c>
-      <c r="B2" s="377"/>
-      <c r="C2" s="377"/>
-      <c r="D2" s="377"/>
-      <c r="E2" s="377"/>
-      <c r="F2" s="377"/>
-      <c r="G2" s="377"/>
-      <c r="H2" s="377"/>
-      <c r="I2" s="377"/>
-      <c r="J2" s="377"/>
-      <c r="K2" s="377"/>
+      <c r="B2" s="381"/>
+      <c r="C2" s="381"/>
+      <c r="D2" s="381"/>
+      <c r="E2" s="381"/>
+      <c r="F2" s="381"/>
+      <c r="G2" s="381"/>
+      <c r="H2" s="381"/>
+      <c r="I2" s="381"/>
+      <c r="J2" s="381"/>
+      <c r="K2" s="381"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="377"/>
-      <c r="B3" s="377"/>
-      <c r="C3" s="377"/>
-      <c r="D3" s="377"/>
-      <c r="E3" s="377"/>
-      <c r="F3" s="377"/>
-      <c r="G3" s="377"/>
-      <c r="H3" s="377"/>
-      <c r="I3" s="377"/>
-      <c r="J3" s="377"/>
-      <c r="K3" s="377"/>
+      <c r="A3" s="381"/>
+      <c r="B3" s="381"/>
+      <c r="C3" s="381"/>
+      <c r="D3" s="381"/>
+      <c r="E3" s="381"/>
+      <c r="F3" s="381"/>
+      <c r="G3" s="381"/>
+      <c r="H3" s="381"/>
+      <c r="I3" s="381"/>
+      <c r="J3" s="381"/>
+      <c r="K3" s="381"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="164" t="s">
@@ -11670,10 +11747,10 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="360" t="s">
+      <c r="B6" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="360" t="s">
+      <c r="C6" s="364" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="270" t="s">
@@ -11689,8 +11766,8 @@
     </row>
     <row r="7" spans="1:11" ht="21.6" thickBot="1">
       <c r="A7" s="13"/>
-      <c r="B7" s="361"/>
-      <c r="C7" s="361"/>
+      <c r="B7" s="380"/>
+      <c r="C7" s="380"/>
       <c r="D7" s="271" t="s">
         <v>100</v>
       </c>
@@ -12000,32 +12077,32 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1532</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
-      <c r="L2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
+      <c r="L2" s="363"/>
     </row>
     <row r="3" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+      <c r="L3" s="363"/>
     </row>
     <row r="4" spans="2:12" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -12035,10 +12112,10 @@
     <row r="5" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="360" t="s">
+      <c r="C6" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="360" t="s">
+      <c r="D6" s="364" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="112" t="s">
@@ -12049,8 +12126,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B7" s="13"/>
-      <c r="C7" s="360"/>
-      <c r="D7" s="360"/>
+      <c r="C7" s="364"/>
+      <c r="D7" s="364"/>
       <c r="E7" s="112" t="s">
         <v>100</v>
       </c>
@@ -12576,32 +12653,32 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1533</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
-      <c r="L2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
+      <c r="L2" s="363"/>
     </row>
     <row r="3" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+      <c r="L3" s="363"/>
     </row>
     <row r="4" spans="2:12" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -12611,10 +12688,10 @@
     <row r="5" spans="2:12" ht="19.05" customHeight="1" thickBot="1"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="374" t="s">
+      <c r="C6" s="377" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="376" t="s">
+      <c r="D6" s="379" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="130" t="s">
@@ -12627,8 +12704,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B7" s="13"/>
-      <c r="C7" s="375"/>
-      <c r="D7" s="361"/>
+      <c r="C7" s="378"/>
+      <c r="D7" s="380"/>
       <c r="E7" s="223" t="s">
         <v>100</v>
       </c>
@@ -13147,21 +13224,21 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="16.95" customHeight="1">
-      <c r="B2" s="380" t="s">
+      <c r="B2" s="384" t="s">
         <v>1534</v>
       </c>
-      <c r="C2" s="380"/>
+      <c r="C2" s="384"/>
     </row>
     <row r="3" spans="1:12" ht="16.95" customHeight="1">
-      <c r="B3" s="380"/>
-      <c r="C3" s="380"/>
+      <c r="B3" s="384"/>
+      <c r="C3" s="384"/>
     </row>
     <row r="6" spans="1:12" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="360" t="s">
+      <c r="B6" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="360" t="s">
+      <c r="C6" s="364" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="149" t="s">
@@ -13180,8 +13257,8 @@
     </row>
     <row r="7" spans="1:12" ht="21.6" thickBot="1">
       <c r="A7" s="13"/>
-      <c r="B7" s="361"/>
-      <c r="C7" s="361"/>
+      <c r="B7" s="380"/>
+      <c r="C7" s="380"/>
       <c r="D7" s="172" t="s">
         <v>1011</v>
       </c>
@@ -13746,12 +13823,12 @@
       <c r="E43" s="162"/>
     </row>
     <row r="44" spans="2:5" ht="25.05" customHeight="1" thickBot="1">
-      <c r="B44" s="379" t="s">
+      <c r="B44" s="383" t="s">
         <v>979</v>
       </c>
-      <c r="C44" s="379"/>
-      <c r="D44" s="379"/>
-      <c r="E44" s="379"/>
+      <c r="C44" s="383"/>
+      <c r="D44" s="383"/>
+      <c r="E44" s="383"/>
     </row>
     <row r="45" spans="2:5" ht="21">
       <c r="B45" s="278" t="s">
@@ -13867,32 +13944,32 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1589</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
-      <c r="L2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
+      <c r="L2" s="363"/>
     </row>
     <row r="3" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+      <c r="L3" s="363"/>
     </row>
     <row r="4" spans="2:12" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -13902,10 +13979,10 @@
     <row r="5" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="360" t="s">
+      <c r="C6" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="360" t="s">
+      <c r="D6" s="364" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="112" t="s">
@@ -13916,8 +13993,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B7" s="13"/>
-      <c r="C7" s="360"/>
-      <c r="D7" s="360"/>
+      <c r="C7" s="364"/>
+      <c r="D7" s="364"/>
       <c r="E7" s="112" t="s">
         <v>100</v>
       </c>
@@ -14389,45 +14466,45 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A2" s="359" t="s">
+      <c r="A2" s="363" t="s">
         <v>1515</v>
       </c>
-      <c r="B2" s="359"/>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
+      <c r="B2" s="363"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
     </row>
     <row r="3" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A3" s="359"/>
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
+      <c r="A3" s="363"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
     </row>
     <row r="4" spans="1:11" ht="16.95" customHeight="1">
-      <c r="A4" s="359"/>
-      <c r="B4" s="359"/>
-      <c r="C4" s="359"/>
-      <c r="D4" s="359"/>
-      <c r="E4" s="359"/>
-      <c r="F4" s="359"/>
-      <c r="G4" s="359"/>
-      <c r="H4" s="359"/>
-      <c r="I4" s="359"/>
-      <c r="J4" s="359"/>
-      <c r="K4" s="359"/>
+      <c r="A4" s="363"/>
+      <c r="B4" s="363"/>
+      <c r="C4" s="363"/>
+      <c r="D4" s="363"/>
+      <c r="E4" s="363"/>
+      <c r="F4" s="363"/>
+      <c r="G4" s="363"/>
+      <c r="H4" s="363"/>
+      <c r="I4" s="363"/>
+      <c r="J4" s="363"/>
+      <c r="K4" s="363"/>
     </row>
     <row r="5" spans="1:11" ht="16.95" customHeight="1">
       <c r="A5" s="111"/>
@@ -14444,10 +14521,10 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="360" t="s">
+      <c r="B6" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="360" t="s">
+      <c r="C6" s="364" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="112" t="s">
@@ -14465,8 +14542,8 @@
     </row>
     <row r="7" spans="1:11" ht="21">
       <c r="A7" s="13"/>
-      <c r="B7" s="360"/>
-      <c r="C7" s="360"/>
+      <c r="B7" s="364"/>
+      <c r="C7" s="364"/>
       <c r="D7" s="112" t="s">
         <v>100</v>
       </c>
@@ -14764,45 +14841,45 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1741</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
-      <c r="L2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
+      <c r="L2" s="363"/>
     </row>
     <row r="3" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+      <c r="L3" s="363"/>
     </row>
     <row r="4" spans="2:12" ht="19.05" customHeight="1">
       <c r="B4" t="s">
-        <v>1742</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="360" t="s">
+      <c r="C6" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="360" t="s">
+      <c r="D6" s="364" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="112" t="s">
@@ -14813,8 +14890,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
       <c r="B7" s="13"/>
-      <c r="C7" s="361"/>
-      <c r="D7" s="361"/>
+      <c r="C7" s="380"/>
+      <c r="D7" s="380"/>
       <c r="E7" s="149" t="s">
         <v>100</v>
       </c>
@@ -14823,84 +14900,84 @@
     </row>
     <row r="8" spans="2:12" s="7" customFormat="1" ht="19.05" customHeight="1">
       <c r="C8" s="278" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="D8" s="268" t="s">
         <v>809</v>
       </c>
       <c r="E8" s="193">
-        <v>19.456737672351057</v>
+        <v>15.420625086052597</v>
       </c>
       <c r="G8" s="12"/>
     </row>
     <row r="9" spans="2:12" s="7" customFormat="1" ht="19.05" customHeight="1">
       <c r="C9" s="243" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="D9" s="122"/>
       <c r="E9" s="194">
-        <v>4.6134025687929032</v>
+        <v>4.0026750063924794</v>
       </c>
       <c r="G9" s="12"/>
     </row>
     <row r="10" spans="2:12" s="7" customFormat="1" ht="19.05" customHeight="1">
       <c r="C10" s="243" t="s">
+        <v>1744</v>
+      </c>
+      <c r="D10" s="122" t="s">
         <v>1745</v>
       </c>
-      <c r="D10" s="122" t="s">
-        <v>1746</v>
-      </c>
       <c r="E10" s="194">
-        <v>12.092602427174919</v>
+        <v>9.7559056666863366</v>
       </c>
       <c r="G10" s="12"/>
     </row>
     <row r="11" spans="2:12" s="7" customFormat="1" ht="19.05" customHeight="1">
       <c r="C11" s="243" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="D11" s="122" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="E11" s="194">
-        <v>13.013119332821939</v>
+        <v>10.46399559410712</v>
       </c>
       <c r="G11" s="12"/>
     </row>
     <row r="12" spans="2:12" s="7" customFormat="1" ht="19.05" customHeight="1">
       <c r="C12" s="243" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="D12" s="122" t="s">
         <v>83</v>
       </c>
       <c r="E12" s="194">
-        <v>10.251568615880885</v>
+        <v>8.3397258118447706</v>
       </c>
       <c r="G12" s="12"/>
     </row>
     <row r="13" spans="2:12" s="7" customFormat="1" ht="19.05" customHeight="1">
       <c r="C13" s="243" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="D13" s="122" t="s">
         <v>83</v>
       </c>
       <c r="E13" s="194">
-        <v>11.172085521527901</v>
+        <v>9.0478157392655536</v>
       </c>
       <c r="G13" s="12"/>
     </row>
     <row r="14" spans="2:12" ht="19.05" customHeight="1">
       <c r="B14" s="1"/>
       <c r="C14" s="243" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="D14" s="122" t="s">
         <v>105</v>
       </c>
       <c r="E14" s="194">
-        <v>12.092602427174919</v>
+        <v>9.7559056666863366</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="2"/>
@@ -14908,13 +14985,13 @@
     <row r="15" spans="2:12" ht="19.05" customHeight="1">
       <c r="B15" s="1"/>
       <c r="C15" s="243" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="D15" s="122" t="s">
         <v>83</v>
       </c>
       <c r="E15" s="194">
-        <v>10.251568615880885</v>
+        <v>8.3397258118447706</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="2"/>
@@ -14922,13 +14999,13 @@
     <row r="16" spans="2:12" ht="19.05" customHeight="1">
       <c r="B16" s="1"/>
       <c r="C16" s="243" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="D16" s="122" t="s">
         <v>83</v>
       </c>
       <c r="E16" s="194">
-        <v>10.251568615880885</v>
+        <v>8.3397258118447706</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="2"/>
@@ -14936,13 +15013,13 @@
     <row r="17" spans="2:7" ht="19.05" customHeight="1">
       <c r="B17" s="1"/>
       <c r="C17" s="243" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="D17" s="122" t="s">
         <v>83</v>
       </c>
       <c r="E17" s="194">
-        <v>11.172085521527901</v>
+        <v>9.0478157392655536</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="2"/>
@@ -14950,13 +15027,13 @@
     <row r="18" spans="2:7" ht="19.05" customHeight="1" thickBot="1">
       <c r="B18" s="1"/>
       <c r="C18" s="244" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="D18" s="211" t="s">
         <v>83</v>
       </c>
       <c r="E18" s="195">
-        <v>10.251568615880885</v>
+        <v>8.3397258118447706</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="2"/>
@@ -15278,11 +15355,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:7" ht="33.6">
-      <c r="D1" s="381" t="s">
+      <c r="D1" s="385" t="s">
         <v>1136</v>
       </c>
-      <c r="E1" s="381"/>
-      <c r="F1" s="381"/>
+      <c r="E1" s="385"/>
+      <c r="F1" s="385"/>
     </row>
     <row r="2" spans="3:7" ht="28.8">
       <c r="D2" s="203"/>
@@ -15301,10 +15378,10 @@
     </row>
     <row r="5" spans="3:7" ht="21">
       <c r="C5" s="13"/>
-      <c r="D5" s="367" t="s">
+      <c r="D5" s="370" t="s">
         <v>102</v>
       </c>
-      <c r="E5" s="367" t="s">
+      <c r="E5" s="370" t="s">
         <v>0</v>
       </c>
       <c r="F5" s="8" t="s">
@@ -15314,8 +15391,8 @@
     </row>
     <row r="6" spans="3:7" ht="21">
       <c r="C6" s="13"/>
-      <c r="D6" s="368"/>
-      <c r="E6" s="368"/>
+      <c r="D6" s="371"/>
+      <c r="E6" s="371"/>
       <c r="F6" s="16" t="s">
         <v>100</v>
       </c>
@@ -15323,18 +15400,18 @@
     </row>
     <row r="7" spans="3:7" ht="22.95" customHeight="1">
       <c r="C7" s="13"/>
-      <c r="D7" s="394" t="s">
+      <c r="D7" s="398" t="s">
         <v>924</v>
       </c>
-      <c r="E7" s="395"/>
-      <c r="F7" s="396"/>
+      <c r="E7" s="399"/>
+      <c r="F7" s="400"/>
       <c r="G7" s="13"/>
     </row>
     <row r="8" spans="3:7" ht="22.95" customHeight="1">
       <c r="C8" s="13"/>
-      <c r="D8" s="397"/>
-      <c r="E8" s="398"/>
-      <c r="F8" s="399"/>
+      <c r="D8" s="401"/>
+      <c r="E8" s="402"/>
+      <c r="F8" s="403"/>
       <c r="G8" s="13"/>
     </row>
     <row r="9" spans="3:7" ht="20.399999999999999">
@@ -15665,16 +15742,16 @@
       </c>
     </row>
     <row r="38" spans="4:6" ht="19.05" customHeight="1">
-      <c r="D38" s="382" t="s">
+      <c r="D38" s="386" t="s">
         <v>925</v>
       </c>
-      <c r="E38" s="400"/>
-      <c r="F38" s="401"/>
+      <c r="E38" s="404"/>
+      <c r="F38" s="405"/>
     </row>
     <row r="39" spans="4:6" ht="19.05" customHeight="1">
-      <c r="D39" s="402"/>
-      <c r="E39" s="403"/>
-      <c r="F39" s="404"/>
+      <c r="D39" s="406"/>
+      <c r="E39" s="407"/>
+      <c r="F39" s="408"/>
     </row>
     <row r="40" spans="4:6" ht="18">
       <c r="D40" s="156" t="s">
@@ -15765,16 +15842,16 @@
       </c>
     </row>
     <row r="48" spans="4:6" ht="19.05" customHeight="1">
-      <c r="D48" s="388" t="s">
+      <c r="D48" s="392" t="s">
         <v>926</v>
       </c>
-      <c r="E48" s="389"/>
-      <c r="F48" s="390"/>
+      <c r="E48" s="393"/>
+      <c r="F48" s="394"/>
     </row>
     <row r="49" spans="4:6" ht="19.05" customHeight="1">
-      <c r="D49" s="391"/>
-      <c r="E49" s="392"/>
-      <c r="F49" s="393"/>
+      <c r="D49" s="395"/>
+      <c r="E49" s="396"/>
+      <c r="F49" s="397"/>
     </row>
     <row r="50" spans="4:6" ht="18">
       <c r="D50" s="156" t="s">
@@ -15920,16 +15997,16 @@
       </c>
     </row>
     <row r="63" spans="4:6" ht="24" customHeight="1">
-      <c r="D63" s="382" t="s">
+      <c r="D63" s="386" t="s">
         <v>927</v>
       </c>
-      <c r="E63" s="383"/>
-      <c r="F63" s="384"/>
+      <c r="E63" s="387"/>
+      <c r="F63" s="388"/>
     </row>
     <row r="64" spans="4:6" ht="24" customHeight="1">
-      <c r="D64" s="385"/>
-      <c r="E64" s="386"/>
-      <c r="F64" s="387"/>
+      <c r="D64" s="389"/>
+      <c r="E64" s="390"/>
+      <c r="F64" s="391"/>
     </row>
     <row r="65" spans="4:6" ht="18">
       <c r="D65" s="156" t="s">
@@ -15987,16 +16064,16 @@
       </c>
     </row>
     <row r="70" spans="4:6" ht="19.05" customHeight="1">
-      <c r="D70" s="388" t="s">
+      <c r="D70" s="392" t="s">
         <v>928</v>
       </c>
-      <c r="E70" s="389"/>
-      <c r="F70" s="390"/>
+      <c r="E70" s="393"/>
+      <c r="F70" s="394"/>
     </row>
     <row r="71" spans="4:6" ht="19.05" customHeight="1">
-      <c r="D71" s="391"/>
-      <c r="E71" s="392"/>
-      <c r="F71" s="393"/>
+      <c r="D71" s="395"/>
+      <c r="E71" s="396"/>
+      <c r="F71" s="397"/>
     </row>
     <row r="72" spans="4:6" ht="18">
       <c r="D72" s="156" t="s">
@@ -16109,16 +16186,16 @@
       </c>
     </row>
     <row r="82" spans="4:6" ht="19.05" customHeight="1">
-      <c r="D82" s="388" t="s">
+      <c r="D82" s="392" t="s">
         <v>929</v>
       </c>
-      <c r="E82" s="389"/>
-      <c r="F82" s="390"/>
+      <c r="E82" s="393"/>
+      <c r="F82" s="394"/>
     </row>
     <row r="83" spans="4:6" ht="19.05" customHeight="1">
-      <c r="D83" s="391"/>
-      <c r="E83" s="392"/>
-      <c r="F83" s="393"/>
+      <c r="D83" s="395"/>
+      <c r="E83" s="396"/>
+      <c r="F83" s="397"/>
     </row>
     <row r="84" spans="4:6" ht="18">
       <c r="D84" s="156" t="s">
@@ -16286,16 +16363,16 @@
       </c>
     </row>
     <row r="99" spans="4:6" ht="19.05" customHeight="1">
-      <c r="D99" s="388" t="s">
+      <c r="D99" s="392" t="s">
         <v>930</v>
       </c>
-      <c r="E99" s="389"/>
-      <c r="F99" s="390"/>
+      <c r="E99" s="393"/>
+      <c r="F99" s="394"/>
     </row>
     <row r="100" spans="4:6" ht="19.05" customHeight="1">
-      <c r="D100" s="391"/>
-      <c r="E100" s="392"/>
-      <c r="F100" s="393"/>
+      <c r="D100" s="395"/>
+      <c r="E100" s="396"/>
+      <c r="F100" s="397"/>
     </row>
     <row r="101" spans="4:6" ht="18">
       <c r="D101" s="156" t="s">
@@ -16364,41 +16441,41 @@
       </c>
     </row>
     <row r="2" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1134</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
-      <c r="L2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
+      <c r="L2" s="363"/>
     </row>
     <row r="3" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+      <c r="L3" s="363"/>
     </row>
     <row r="4" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="5" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="360" t="s">
+      <c r="C6" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="360" t="s">
+      <c r="D6" s="364" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="112" t="s">
@@ -16409,8 +16486,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B7" s="13"/>
-      <c r="C7" s="361"/>
-      <c r="D7" s="361"/>
+      <c r="C7" s="380"/>
+      <c r="D7" s="380"/>
       <c r="E7" s="149" t="s">
         <v>100</v>
       </c>
@@ -16857,32 +16934,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="405" t="s">
+      <c r="A1" s="409" t="s">
         <v>1542</v>
       </c>
-      <c r="B1" s="405"/>
-      <c r="C1" s="405"/>
-      <c r="D1" s="405"/>
-      <c r="E1" s="405"/>
-      <c r="F1" s="405"/>
-      <c r="G1" s="405"/>
-      <c r="H1" s="405"/>
-      <c r="I1" s="405"/>
-      <c r="J1" s="405"/>
-      <c r="K1" s="405"/>
+      <c r="B1" s="409"/>
+      <c r="C1" s="409"/>
+      <c r="D1" s="409"/>
+      <c r="E1" s="409"/>
+      <c r="F1" s="409"/>
+      <c r="G1" s="409"/>
+      <c r="H1" s="409"/>
+      <c r="I1" s="409"/>
+      <c r="J1" s="409"/>
+      <c r="K1" s="409"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="405"/>
-      <c r="B2" s="405"/>
-      <c r="C2" s="405"/>
-      <c r="D2" s="405"/>
-      <c r="E2" s="405"/>
-      <c r="F2" s="405"/>
-      <c r="G2" s="405"/>
-      <c r="H2" s="405"/>
-      <c r="I2" s="405"/>
-      <c r="J2" s="405"/>
-      <c r="K2" s="405"/>
+      <c r="A2" s="409"/>
+      <c r="B2" s="409"/>
+      <c r="C2" s="409"/>
+      <c r="D2" s="409"/>
+      <c r="E2" s="409"/>
+      <c r="F2" s="409"/>
+      <c r="G2" s="409"/>
+      <c r="H2" s="409"/>
+      <c r="I2" s="409"/>
+      <c r="J2" s="409"/>
+      <c r="K2" s="409"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
@@ -16891,10 +16968,10 @@
     </row>
     <row r="5" spans="1:11" ht="21">
       <c r="A5" s="13"/>
-      <c r="B5" s="360" t="s">
+      <c r="B5" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="360" t="s">
+      <c r="C5" s="364" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="112" t="s">
@@ -16910,8 +16987,8 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="360"/>
-      <c r="C6" s="360"/>
+      <c r="B6" s="364"/>
+      <c r="C6" s="364"/>
       <c r="D6" s="112" t="s">
         <v>100</v>
       </c>
@@ -17070,39 +17147,39 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A3" s="405" t="s">
+      <c r="A3" s="409" t="s">
         <v>1623</v>
       </c>
-      <c r="B3" s="405"/>
-      <c r="C3" s="405"/>
-      <c r="D3" s="405"/>
-      <c r="E3" s="405"/>
-      <c r="F3" s="405"/>
-      <c r="G3" s="405"/>
-      <c r="H3" s="405"/>
-      <c r="I3" s="405"/>
-      <c r="J3" s="405"/>
-      <c r="K3" s="405"/>
+      <c r="B3" s="409"/>
+      <c r="C3" s="409"/>
+      <c r="D3" s="409"/>
+      <c r="E3" s="409"/>
+      <c r="F3" s="409"/>
+      <c r="G3" s="409"/>
+      <c r="H3" s="409"/>
+      <c r="I3" s="409"/>
+      <c r="J3" s="409"/>
+      <c r="K3" s="409"/>
     </row>
     <row r="4" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A4" s="405"/>
-      <c r="B4" s="405"/>
-      <c r="C4" s="405"/>
-      <c r="D4" s="405"/>
-      <c r="E4" s="405"/>
-      <c r="F4" s="405"/>
-      <c r="G4" s="405"/>
-      <c r="H4" s="405"/>
-      <c r="I4" s="405"/>
-      <c r="J4" s="405"/>
-      <c r="K4" s="405"/>
+      <c r="A4" s="409"/>
+      <c r="B4" s="409"/>
+      <c r="C4" s="409"/>
+      <c r="D4" s="409"/>
+      <c r="E4" s="409"/>
+      <c r="F4" s="409"/>
+      <c r="G4" s="409"/>
+      <c r="H4" s="409"/>
+      <c r="I4" s="409"/>
+      <c r="J4" s="409"/>
+      <c r="K4" s="409"/>
     </row>
     <row r="7" spans="1:11" ht="21">
       <c r="A7" s="13"/>
-      <c r="B7" s="360" t="s">
+      <c r="B7" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="C7" s="360" t="s">
+      <c r="C7" s="364" t="s">
         <v>0</v>
       </c>
       <c r="D7" s="112" t="s">
@@ -17118,8 +17195,8 @@
     </row>
     <row r="8" spans="1:11" ht="21">
       <c r="A8" s="13"/>
-      <c r="B8" s="361"/>
-      <c r="C8" s="361"/>
+      <c r="B8" s="380"/>
+      <c r="C8" s="380"/>
       <c r="D8" s="149" t="s">
         <v>100</v>
       </c>
@@ -17394,39 +17471,39 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A3" s="405" t="s">
+      <c r="A3" s="409" t="s">
         <v>1594</v>
       </c>
-      <c r="B3" s="405"/>
-      <c r="C3" s="405"/>
-      <c r="D3" s="405"/>
-      <c r="E3" s="405"/>
-      <c r="F3" s="405"/>
-      <c r="G3" s="405"/>
-      <c r="H3" s="405"/>
-      <c r="I3" s="405"/>
-      <c r="J3" s="405"/>
-      <c r="K3" s="405"/>
+      <c r="B3" s="409"/>
+      <c r="C3" s="409"/>
+      <c r="D3" s="409"/>
+      <c r="E3" s="409"/>
+      <c r="F3" s="409"/>
+      <c r="G3" s="409"/>
+      <c r="H3" s="409"/>
+      <c r="I3" s="409"/>
+      <c r="J3" s="409"/>
+      <c r="K3" s="409"/>
     </row>
     <row r="4" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A4" s="405"/>
-      <c r="B4" s="405"/>
-      <c r="C4" s="405"/>
-      <c r="D4" s="405"/>
-      <c r="E4" s="405"/>
-      <c r="F4" s="405"/>
-      <c r="G4" s="405"/>
-      <c r="H4" s="405"/>
-      <c r="I4" s="405"/>
-      <c r="J4" s="405"/>
-      <c r="K4" s="405"/>
+      <c r="A4" s="409"/>
+      <c r="B4" s="409"/>
+      <c r="C4" s="409"/>
+      <c r="D4" s="409"/>
+      <c r="E4" s="409"/>
+      <c r="F4" s="409"/>
+      <c r="G4" s="409"/>
+      <c r="H4" s="409"/>
+      <c r="I4" s="409"/>
+      <c r="J4" s="409"/>
+      <c r="K4" s="409"/>
     </row>
     <row r="7" spans="1:11" ht="21">
       <c r="A7" s="13"/>
-      <c r="B7" s="360" t="s">
+      <c r="B7" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="C7" s="360" t="s">
+      <c r="C7" s="364" t="s">
         <v>0</v>
       </c>
       <c r="D7" s="112" t="s">
@@ -17442,8 +17519,8 @@
     </row>
     <row r="8" spans="1:11" ht="21">
       <c r="A8" s="13"/>
-      <c r="B8" s="360"/>
-      <c r="C8" s="360"/>
+      <c r="B8" s="364"/>
+      <c r="C8" s="364"/>
       <c r="D8" s="112" t="s">
         <v>100</v>
       </c>
@@ -17669,32 +17746,32 @@
   <sheetData>
     <row r="1" spans="2:16" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:16" ht="19.05" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1553</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
-      <c r="L2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
+      <c r="L2" s="363"/>
     </row>
     <row r="3" spans="2:16" ht="19.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+      <c r="L3" s="363"/>
     </row>
     <row r="4" spans="2:16" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -17704,10 +17781,10 @@
     <row r="5" spans="2:16" ht="19.05" customHeight="1"/>
     <row r="6" spans="2:16" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="360" t="s">
+      <c r="C6" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="360" t="s">
+      <c r="D6" s="364" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="120" t="s">
@@ -17717,8 +17794,8 @@
     </row>
     <row r="7" spans="2:16" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B7" s="13"/>
-      <c r="C7" s="361"/>
-      <c r="D7" s="361"/>
+      <c r="C7" s="380"/>
+      <c r="D7" s="380"/>
       <c r="E7" s="123" t="s">
         <v>100</v>
       </c>
@@ -18245,41 +18322,41 @@
       </c>
     </row>
     <row r="2" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1557</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
-      <c r="L2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
+      <c r="L2" s="363"/>
     </row>
     <row r="3" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+      <c r="L3" s="363"/>
     </row>
     <row r="4" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="5" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="360" t="s">
+      <c r="C6" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="360" t="s">
+      <c r="D6" s="364" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="112" t="s">
@@ -18290,8 +18367,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B7" s="13"/>
-      <c r="C7" s="361"/>
-      <c r="D7" s="361"/>
+      <c r="C7" s="380"/>
+      <c r="D7" s="380"/>
       <c r="E7" s="149" t="s">
         <v>100</v>
       </c>
@@ -18690,41 +18767,41 @@
       </c>
     </row>
     <row r="2" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1558</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
-      <c r="L2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
+      <c r="L2" s="363"/>
     </row>
     <row r="3" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+      <c r="L3" s="363"/>
     </row>
     <row r="4" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="5" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="360" t="s">
+      <c r="C6" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="360" t="s">
+      <c r="D6" s="364" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="112" t="s">
@@ -18735,8 +18812,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B7" s="13"/>
-      <c r="C7" s="360"/>
-      <c r="D7" s="360"/>
+      <c r="C7" s="364"/>
+      <c r="D7" s="364"/>
       <c r="E7" s="112" t="s">
         <v>100</v>
       </c>
@@ -19085,32 +19162,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="405" t="s">
+      <c r="A1" s="409" t="s">
         <v>1559</v>
       </c>
-      <c r="B1" s="405"/>
-      <c r="C1" s="405"/>
-      <c r="D1" s="405"/>
-      <c r="E1" s="405"/>
-      <c r="F1" s="405"/>
-      <c r="G1" s="405"/>
-      <c r="H1" s="405"/>
-      <c r="I1" s="405"/>
-      <c r="J1" s="405"/>
-      <c r="K1" s="405"/>
+      <c r="B1" s="409"/>
+      <c r="C1" s="409"/>
+      <c r="D1" s="409"/>
+      <c r="E1" s="409"/>
+      <c r="F1" s="409"/>
+      <c r="G1" s="409"/>
+      <c r="H1" s="409"/>
+      <c r="I1" s="409"/>
+      <c r="J1" s="409"/>
+      <c r="K1" s="409"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="405"/>
-      <c r="B2" s="405"/>
-      <c r="C2" s="405"/>
-      <c r="D2" s="405"/>
-      <c r="E2" s="405"/>
-      <c r="F2" s="405"/>
-      <c r="G2" s="405"/>
-      <c r="H2" s="405"/>
-      <c r="I2" s="405"/>
-      <c r="J2" s="405"/>
-      <c r="K2" s="405"/>
+      <c r="A2" s="409"/>
+      <c r="B2" s="409"/>
+      <c r="C2" s="409"/>
+      <c r="D2" s="409"/>
+      <c r="E2" s="409"/>
+      <c r="F2" s="409"/>
+      <c r="G2" s="409"/>
+      <c r="H2" s="409"/>
+      <c r="I2" s="409"/>
+      <c r="J2" s="409"/>
+      <c r="K2" s="409"/>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
@@ -19119,10 +19196,10 @@
     </row>
     <row r="5" spans="1:11" ht="21">
       <c r="A5" s="13"/>
-      <c r="B5" s="360" t="s">
+      <c r="B5" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="360" t="s">
+      <c r="C5" s="364" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="112" t="s">
@@ -19140,8 +19217,8 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="360"/>
-      <c r="C6" s="360"/>
+      <c r="B6" s="364"/>
+      <c r="C6" s="364"/>
       <c r="D6" s="112" t="s">
         <v>100</v>
       </c>
@@ -19303,45 +19380,45 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A2" s="359" t="s">
+      <c r="A2" s="363" t="s">
         <v>1517</v>
       </c>
-      <c r="B2" s="359"/>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
+      <c r="B2" s="363"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
     </row>
     <row r="3" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A3" s="359"/>
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
+      <c r="A3" s="363"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
     </row>
     <row r="4" spans="1:11" ht="16.95" customHeight="1">
-      <c r="A4" s="359"/>
-      <c r="B4" s="359"/>
-      <c r="C4" s="359"/>
-      <c r="D4" s="359"/>
-      <c r="E4" s="359"/>
-      <c r="F4" s="359"/>
-      <c r="G4" s="359"/>
-      <c r="H4" s="359"/>
-      <c r="I4" s="359"/>
-      <c r="J4" s="359"/>
-      <c r="K4" s="359"/>
+      <c r="A4" s="363"/>
+      <c r="B4" s="363"/>
+      <c r="C4" s="363"/>
+      <c r="D4" s="363"/>
+      <c r="E4" s="363"/>
+      <c r="F4" s="363"/>
+      <c r="G4" s="363"/>
+      <c r="H4" s="363"/>
+      <c r="I4" s="363"/>
+      <c r="J4" s="363"/>
+      <c r="K4" s="363"/>
     </row>
     <row r="5" spans="1:11" ht="16.95" customHeight="1" thickBot="1">
       <c r="A5" s="111"/>
@@ -19358,10 +19435,10 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="365" t="s">
+      <c r="B6" s="368" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="367" t="s">
+      <c r="C6" s="370" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="14" t="s">
@@ -19377,8 +19454,8 @@
     </row>
     <row r="7" spans="1:11" ht="21">
       <c r="A7" s="13"/>
-      <c r="B7" s="366"/>
-      <c r="C7" s="368"/>
+      <c r="B7" s="369"/>
+      <c r="C7" s="371"/>
       <c r="D7" s="177" t="s">
         <v>100</v>
       </c>
@@ -19520,25 +19597,25 @@
       <c r="B1" s="176"/>
     </row>
     <row r="2" spans="2:10" ht="19.05" customHeight="1">
-      <c r="B2" s="407" t="s">
+      <c r="B2" s="411" t="s">
         <v>1564</v>
       </c>
-      <c r="C2" s="407"/>
-      <c r="D2" s="408"/>
-      <c r="E2" s="408"/>
-      <c r="F2" s="408"/>
-      <c r="G2" s="409"/>
+      <c r="C2" s="411"/>
+      <c r="D2" s="412"/>
+      <c r="E2" s="412"/>
+      <c r="F2" s="412"/>
+      <c r="G2" s="413"/>
       <c r="H2" s="38"/>
       <c r="I2" s="38"/>
       <c r="J2" s="38"/>
     </row>
     <row r="3" spans="2:10" ht="19.05" customHeight="1">
-      <c r="B3" s="408"/>
-      <c r="C3" s="408"/>
-      <c r="D3" s="408"/>
-      <c r="E3" s="408"/>
-      <c r="F3" s="408"/>
-      <c r="G3" s="409"/>
+      <c r="B3" s="412"/>
+      <c r="C3" s="412"/>
+      <c r="D3" s="412"/>
+      <c r="E3" s="412"/>
+      <c r="F3" s="412"/>
+      <c r="G3" s="413"/>
       <c r="H3" s="38"/>
       <c r="I3" s="38"/>
       <c r="J3" s="38"/>
@@ -19559,13 +19636,13 @@
       <c r="E5" s="296"/>
     </row>
     <row r="6" spans="2:10" ht="19.05" customHeight="1">
-      <c r="B6" s="363" t="s">
+      <c r="B6" s="366" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="363" t="s">
+      <c r="C6" s="366" t="s">
         <v>106</v>
       </c>
-      <c r="D6" s="363" t="s">
+      <c r="D6" s="366" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="106" t="s">
@@ -19576,9 +19653,9 @@
       </c>
     </row>
     <row r="7" spans="2:10" ht="19.05" customHeight="1" thickBot="1">
-      <c r="B7" s="410"/>
-      <c r="C7" s="410"/>
-      <c r="D7" s="410"/>
+      <c r="B7" s="414"/>
+      <c r="C7" s="414"/>
+      <c r="D7" s="414"/>
       <c r="E7" s="308" t="s">
         <v>100</v>
       </c>
@@ -19658,10 +19735,10 @@
         <v>5.3645417412455823</v>
       </c>
       <c r="F12" s="354"/>
-      <c r="G12" s="406"/>
-      <c r="H12" s="406"/>
-      <c r="I12" s="406"/>
-      <c r="J12" s="406"/>
+      <c r="G12" s="410"/>
+      <c r="H12" s="410"/>
+      <c r="I12" s="410"/>
+      <c r="J12" s="410"/>
     </row>
     <row r="13" spans="2:10" ht="19.05" customHeight="1">
       <c r="B13" s="329" t="s">
@@ -19677,10 +19754,10 @@
         <v>14.217082013860205</v>
       </c>
       <c r="F13" s="354"/>
-      <c r="G13" s="406"/>
-      <c r="H13" s="406"/>
-      <c r="I13" s="406"/>
-      <c r="J13" s="406"/>
+      <c r="G13" s="410"/>
+      <c r="H13" s="410"/>
+      <c r="I13" s="410"/>
+      <c r="J13" s="410"/>
     </row>
     <row r="14" spans="2:10" ht="19.05" customHeight="1">
       <c r="B14" s="329" t="s">
@@ -20497,11 +20574,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="25.5" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1565</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
       <c r="E2" s="48"/>
       <c r="F2" s="48"/>
       <c r="G2" s="48"/>
@@ -20512,9 +20589,9 @@
       <c r="L2" s="48"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
       <c r="E3" s="48"/>
       <c r="F3" s="48"/>
       <c r="G3" s="48"/>
@@ -20531,10 +20608,10 @@
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1"/>
     <row r="6" spans="1:12" ht="21">
-      <c r="B6" s="411" t="s">
+      <c r="B6" s="415" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="413" t="s">
+      <c r="C6" s="417" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="49" t="s">
@@ -20542,8 +20619,8 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="21">
-      <c r="B7" s="412"/>
-      <c r="C7" s="414"/>
+      <c r="B7" s="416"/>
+      <c r="C7" s="418"/>
       <c r="D7" s="124" t="s">
         <v>100</v>
       </c>
@@ -20681,32 +20758,32 @@
       <c r="K1" s="164"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="377" t="s">
+      <c r="A2" s="381" t="s">
         <v>1566</v>
       </c>
-      <c r="B2" s="377"/>
-      <c r="C2" s="377"/>
-      <c r="D2" s="377"/>
-      <c r="E2" s="377"/>
-      <c r="F2" s="377"/>
-      <c r="G2" s="377"/>
-      <c r="H2" s="377"/>
-      <c r="I2" s="377"/>
-      <c r="J2" s="377"/>
-      <c r="K2" s="377"/>
+      <c r="B2" s="381"/>
+      <c r="C2" s="381"/>
+      <c r="D2" s="381"/>
+      <c r="E2" s="381"/>
+      <c r="F2" s="381"/>
+      <c r="G2" s="381"/>
+      <c r="H2" s="381"/>
+      <c r="I2" s="381"/>
+      <c r="J2" s="381"/>
+      <c r="K2" s="381"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="377"/>
-      <c r="B3" s="377"/>
-      <c r="C3" s="377"/>
-      <c r="D3" s="377"/>
-      <c r="E3" s="377"/>
-      <c r="F3" s="377"/>
-      <c r="G3" s="377"/>
-      <c r="H3" s="377"/>
-      <c r="I3" s="377"/>
-      <c r="J3" s="377"/>
-      <c r="K3" s="377"/>
+      <c r="A3" s="381"/>
+      <c r="B3" s="381"/>
+      <c r="C3" s="381"/>
+      <c r="D3" s="381"/>
+      <c r="E3" s="381"/>
+      <c r="F3" s="381"/>
+      <c r="G3" s="381"/>
+      <c r="H3" s="381"/>
+      <c r="I3" s="381"/>
+      <c r="J3" s="381"/>
+      <c r="K3" s="381"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="164" t="s">
@@ -20738,10 +20815,10 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="374" t="s">
+      <c r="B6" s="377" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="376" t="s">
+      <c r="C6" s="379" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="167" t="s">
@@ -20757,8 +20834,8 @@
     </row>
     <row r="7" spans="1:11" ht="21">
       <c r="A7" s="13"/>
-      <c r="B7" s="375"/>
-      <c r="C7" s="361"/>
+      <c r="B7" s="378"/>
+      <c r="C7" s="380"/>
       <c r="D7" s="178" t="s">
         <v>100</v>
       </c>
@@ -21072,32 +21149,32 @@
       <c r="K1" s="164"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="377" t="s">
+      <c r="A2" s="381" t="s">
         <v>1135</v>
       </c>
-      <c r="B2" s="377"/>
-      <c r="C2" s="377"/>
-      <c r="D2" s="377"/>
-      <c r="E2" s="377"/>
-      <c r="F2" s="377"/>
-      <c r="G2" s="377"/>
-      <c r="H2" s="377"/>
-      <c r="I2" s="377"/>
-      <c r="J2" s="377"/>
-      <c r="K2" s="377"/>
+      <c r="B2" s="381"/>
+      <c r="C2" s="381"/>
+      <c r="D2" s="381"/>
+      <c r="E2" s="381"/>
+      <c r="F2" s="381"/>
+      <c r="G2" s="381"/>
+      <c r="H2" s="381"/>
+      <c r="I2" s="381"/>
+      <c r="J2" s="381"/>
+      <c r="K2" s="381"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="377"/>
-      <c r="B3" s="377"/>
-      <c r="C3" s="377"/>
-      <c r="D3" s="377"/>
-      <c r="E3" s="377"/>
-      <c r="F3" s="377"/>
-      <c r="G3" s="377"/>
-      <c r="H3" s="377"/>
-      <c r="I3" s="377"/>
-      <c r="J3" s="377"/>
-      <c r="K3" s="377"/>
+      <c r="A3" s="381"/>
+      <c r="B3" s="381"/>
+      <c r="C3" s="381"/>
+      <c r="D3" s="381"/>
+      <c r="E3" s="381"/>
+      <c r="F3" s="381"/>
+      <c r="G3" s="381"/>
+      <c r="H3" s="381"/>
+      <c r="I3" s="381"/>
+      <c r="J3" s="381"/>
+      <c r="K3" s="381"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="164" t="s">
@@ -21129,10 +21206,10 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="374" t="s">
+      <c r="B6" s="377" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="376" t="s">
+      <c r="C6" s="379" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="167" t="s">
@@ -21148,8 +21225,8 @@
     </row>
     <row r="7" spans="1:11" ht="21">
       <c r="A7" s="13"/>
-      <c r="B7" s="415"/>
-      <c r="C7" s="360"/>
+      <c r="B7" s="419"/>
+      <c r="C7" s="364"/>
       <c r="D7" s="168" t="s">
         <v>100</v>
       </c>
@@ -21356,32 +21433,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12">
-      <c r="B2" s="405" t="s">
+      <c r="B2" s="409" t="s">
         <v>1567</v>
       </c>
-      <c r="C2" s="405"/>
-      <c r="D2" s="405"/>
-      <c r="E2" s="405"/>
-      <c r="F2" s="405"/>
-      <c r="G2" s="405"/>
-      <c r="H2" s="405"/>
-      <c r="I2" s="405"/>
-      <c r="J2" s="405"/>
-      <c r="K2" s="405"/>
-      <c r="L2" s="405"/>
+      <c r="C2" s="409"/>
+      <c r="D2" s="409"/>
+      <c r="E2" s="409"/>
+      <c r="F2" s="409"/>
+      <c r="G2" s="409"/>
+      <c r="H2" s="409"/>
+      <c r="I2" s="409"/>
+      <c r="J2" s="409"/>
+      <c r="K2" s="409"/>
+      <c r="L2" s="409"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="B3" s="405"/>
-      <c r="C3" s="405"/>
-      <c r="D3" s="405"/>
-      <c r="E3" s="405"/>
-      <c r="F3" s="405"/>
-      <c r="G3" s="405"/>
-      <c r="H3" s="405"/>
-      <c r="I3" s="405"/>
-      <c r="J3" s="405"/>
-      <c r="K3" s="405"/>
-      <c r="L3" s="405"/>
+      <c r="B3" s="409"/>
+      <c r="C3" s="409"/>
+      <c r="D3" s="409"/>
+      <c r="E3" s="409"/>
+      <c r="F3" s="409"/>
+      <c r="G3" s="409"/>
+      <c r="H3" s="409"/>
+      <c r="I3" s="409"/>
+      <c r="J3" s="409"/>
+      <c r="K3" s="409"/>
+      <c r="L3" s="409"/>
     </row>
     <row r="4" spans="1:12">
       <c r="B4" t="s">
@@ -21391,10 +21468,10 @@
     <row r="6" spans="1:12" ht="21">
       <c r="A6" s="9"/>
       <c r="B6" s="13"/>
-      <c r="C6" s="360" t="s">
+      <c r="C6" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="360" t="s">
+      <c r="D6" s="364" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="112" t="s">
@@ -21411,8 +21488,8 @@
     <row r="7" spans="1:12" ht="21">
       <c r="A7" s="9"/>
       <c r="B7" s="13"/>
-      <c r="C7" s="360"/>
-      <c r="D7" s="360"/>
+      <c r="C7" s="364"/>
+      <c r="D7" s="364"/>
       <c r="E7" s="112" t="s">
         <v>100</v>
       </c>
@@ -21542,18 +21619,18 @@
       <c r="B1" s="176"/>
     </row>
     <row r="2" spans="2:5" ht="19.05" customHeight="1">
-      <c r="B2" s="416" t="s">
+      <c r="B2" s="420" t="s">
         <v>1642</v>
       </c>
-      <c r="C2" s="416"/>
-      <c r="D2" s="417"/>
-      <c r="E2" s="417"/>
+      <c r="C2" s="420"/>
+      <c r="D2" s="421"/>
+      <c r="E2" s="421"/>
     </row>
     <row r="3" spans="2:5" ht="19.05" customHeight="1">
-      <c r="B3" s="417"/>
-      <c r="C3" s="417"/>
-      <c r="D3" s="417"/>
-      <c r="E3" s="417"/>
+      <c r="B3" s="421"/>
+      <c r="C3" s="421"/>
+      <c r="D3" s="421"/>
+      <c r="E3" s="421"/>
     </row>
     <row r="4" spans="2:5" ht="19.05" customHeight="1">
       <c r="B4" s="134" t="s">
@@ -21570,13 +21647,13 @@
       <c r="E5" s="296"/>
     </row>
     <row r="6" spans="2:5" ht="19.05" customHeight="1">
-      <c r="B6" s="363" t="s">
+      <c r="B6" s="366" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="363" t="s">
+      <c r="C6" s="366" t="s">
         <v>106</v>
       </c>
-      <c r="D6" s="363" t="s">
+      <c r="D6" s="366" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="106" t="s">
@@ -21584,9 +21661,9 @@
       </c>
     </row>
     <row r="7" spans="2:5" ht="19.05" customHeight="1">
-      <c r="B7" s="363"/>
-      <c r="C7" s="363"/>
-      <c r="D7" s="363"/>
+      <c r="B7" s="366"/>
+      <c r="C7" s="366"/>
+      <c r="D7" s="366"/>
       <c r="E7" s="106" t="s">
         <v>100</v>
       </c>
@@ -21815,32 +21892,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="359" t="s">
+      <c r="A1" s="363" t="s">
         <v>1606</v>
       </c>
-      <c r="B1" s="359"/>
-      <c r="C1" s="359"/>
-      <c r="D1" s="359"/>
-      <c r="E1" s="359"/>
-      <c r="F1" s="359"/>
-      <c r="G1" s="359"/>
-      <c r="H1" s="359"/>
-      <c r="I1" s="359"/>
-      <c r="J1" s="359"/>
-      <c r="K1" s="359"/>
+      <c r="B1" s="363"/>
+      <c r="C1" s="363"/>
+      <c r="D1" s="363"/>
+      <c r="E1" s="363"/>
+      <c r="F1" s="363"/>
+      <c r="G1" s="363"/>
+      <c r="H1" s="363"/>
+      <c r="I1" s="363"/>
+      <c r="J1" s="363"/>
+      <c r="K1" s="363"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="359"/>
-      <c r="B2" s="359"/>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
+      <c r="A2" s="363"/>
+      <c r="B2" s="363"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
@@ -21849,10 +21926,10 @@
     </row>
     <row r="5" spans="1:11" ht="21">
       <c r="A5" s="13"/>
-      <c r="B5" s="360" t="s">
+      <c r="B5" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="360" t="s">
+      <c r="C5" s="364" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="112" t="s">
@@ -21868,8 +21945,8 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="360"/>
-      <c r="C6" s="360"/>
+      <c r="B6" s="364"/>
+      <c r="C6" s="364"/>
       <c r="D6" s="112" t="s">
         <v>100</v>
       </c>
@@ -22098,32 +22175,32 @@
       <c r="K1" s="164"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="377" t="s">
+      <c r="A2" s="381" t="s">
         <v>1568</v>
       </c>
-      <c r="B2" s="377"/>
-      <c r="C2" s="377"/>
-      <c r="D2" s="377"/>
-      <c r="E2" s="377"/>
-      <c r="F2" s="377"/>
-      <c r="G2" s="377"/>
-      <c r="H2" s="377"/>
-      <c r="I2" s="377"/>
-      <c r="J2" s="377"/>
-      <c r="K2" s="377"/>
+      <c r="B2" s="381"/>
+      <c r="C2" s="381"/>
+      <c r="D2" s="381"/>
+      <c r="E2" s="381"/>
+      <c r="F2" s="381"/>
+      <c r="G2" s="381"/>
+      <c r="H2" s="381"/>
+      <c r="I2" s="381"/>
+      <c r="J2" s="381"/>
+      <c r="K2" s="381"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="377"/>
-      <c r="B3" s="377"/>
-      <c r="C3" s="377"/>
-      <c r="D3" s="377"/>
-      <c r="E3" s="377"/>
-      <c r="F3" s="377"/>
-      <c r="G3" s="377"/>
-      <c r="H3" s="377"/>
-      <c r="I3" s="377"/>
-      <c r="J3" s="377"/>
-      <c r="K3" s="377"/>
+      <c r="A3" s="381"/>
+      <c r="B3" s="381"/>
+      <c r="C3" s="381"/>
+      <c r="D3" s="381"/>
+      <c r="E3" s="381"/>
+      <c r="F3" s="381"/>
+      <c r="G3" s="381"/>
+      <c r="H3" s="381"/>
+      <c r="I3" s="381"/>
+      <c r="J3" s="381"/>
+      <c r="K3" s="381"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="164" t="s">
@@ -22155,10 +22232,10 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="360" t="s">
+      <c r="B6" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="360" t="s">
+      <c r="C6" s="364" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="270" t="s">
@@ -22176,8 +22253,8 @@
     </row>
     <row r="7" spans="1:11" ht="21">
       <c r="A7" s="13"/>
-      <c r="B7" s="360"/>
-      <c r="C7" s="360"/>
+      <c r="B7" s="364"/>
+      <c r="C7" s="364"/>
       <c r="D7" s="270" t="s">
         <v>100</v>
       </c>
@@ -22582,6 +22659,441 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30D681F0-C677-FD45-B510-4E4CDB98FA81}">
+  <dimension ref="B1:K67"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="3.5" customWidth="1"/>
+    <col min="3" max="3" width="39.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:11" ht="19.05" customHeight="1"/>
+    <row r="2" spans="2:11" ht="19.05" customHeight="1">
+      <c r="B2" s="363" t="s">
+        <v>1752</v>
+      </c>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
+    </row>
+    <row r="3" spans="2:11" ht="19.05" customHeight="1">
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+    </row>
+    <row r="4" spans="2:11" ht="19.05" customHeight="1">
+      <c r="B4" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" ht="19.05" customHeight="1" thickBot="1"/>
+    <row r="6" spans="2:11" s="9" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B6" s="13"/>
+      <c r="C6" s="370" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" s="370" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+    </row>
+    <row r="7" spans="2:11" s="9" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B7" s="13"/>
+      <c r="C7" s="371"/>
+      <c r="D7" s="371"/>
+      <c r="E7" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+    </row>
+    <row r="8" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="C8" s="122" t="s">
+        <v>1753</v>
+      </c>
+      <c r="D8" s="122" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="189">
+        <v>16.374579571605601</v>
+      </c>
+      <c r="G8" s="12"/>
+    </row>
+    <row r="9" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="C9" s="122" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D9" s="122" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="189">
+        <v>19.295450522216324</v>
+      </c>
+      <c r="G9" s="12"/>
+    </row>
+    <row r="10" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="C10" s="122" t="s">
+        <v>1755</v>
+      </c>
+      <c r="D10" s="122" t="s">
+        <v>1756</v>
+      </c>
+      <c r="E10" s="189">
+        <v>14.75187348793297</v>
+      </c>
+      <c r="G10" s="12"/>
+    </row>
+    <row r="11" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="C11" s="122" t="s">
+        <v>1757</v>
+      </c>
+      <c r="D11" s="122" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" s="189">
+        <v>19.295450522216324</v>
+      </c>
+      <c r="G11" s="12"/>
+    </row>
+    <row r="12" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="E12" s="201"/>
+      <c r="G12" s="12"/>
+    </row>
+    <row r="13" spans="2:11" ht="19.05" customHeight="1">
+      <c r="B13" s="1"/>
+      <c r="C13" s="2"/>
+      <c r="E13" s="139"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="2:11" ht="19.05" customHeight="1">
+      <c r="B14" s="1"/>
+      <c r="C14" s="2"/>
+      <c r="E14" s="139"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="2:11" ht="19.05" customHeight="1">
+      <c r="B15" s="1"/>
+      <c r="C15" s="2"/>
+      <c r="E15" s="139"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="2:11" ht="19.05" customHeight="1">
+      <c r="B16" s="1"/>
+      <c r="C16" s="2"/>
+      <c r="E16" s="139"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B17" s="1"/>
+      <c r="C17" s="2"/>
+      <c r="E17" s="139"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B18" s="1"/>
+      <c r="C18" s="2"/>
+      <c r="E18" s="139"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B19" s="1"/>
+      <c r="C19" s="2"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B20" s="1"/>
+      <c r="C20" s="2"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B21" s="1"/>
+      <c r="C21" s="2"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B22" s="1"/>
+      <c r="C22" s="2"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B23" s="1"/>
+      <c r="C23" s="2"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B24" s="1"/>
+      <c r="C24" s="2"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B25" s="1"/>
+      <c r="C25" s="2"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B26" s="1"/>
+      <c r="C26" s="2"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B27" s="1"/>
+      <c r="C27" s="2"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B28" s="1"/>
+      <c r="C28" s="2"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B29" s="1"/>
+      <c r="C29" s="2"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B30" s="1"/>
+      <c r="C30" s="2"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B31" s="1"/>
+      <c r="C31" s="2"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B32" s="1"/>
+      <c r="C32" s="2"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B33" s="1"/>
+      <c r="C33" s="2"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="2"/>
+    </row>
+    <row r="34" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B34" s="1"/>
+      <c r="C34" s="2"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B35" s="1"/>
+      <c r="C35" s="2"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="2"/>
+    </row>
+    <row r="36" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B36" s="1"/>
+      <c r="C36" s="2"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B37" s="1"/>
+      <c r="C37" s="2"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="2"/>
+    </row>
+    <row r="38" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B38" s="1"/>
+      <c r="C38" s="2"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B39" s="1"/>
+      <c r="C39" s="2"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="2"/>
+    </row>
+    <row r="40" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B40" s="1"/>
+      <c r="C40" s="2"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="2"/>
+    </row>
+    <row r="41" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B41" s="1"/>
+      <c r="C41" s="2"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="2"/>
+    </row>
+    <row r="42" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B42" s="1"/>
+      <c r="C42" s="2"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="2"/>
+    </row>
+    <row r="43" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B43" s="1"/>
+      <c r="C43" s="2"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="2"/>
+    </row>
+    <row r="44" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B44" s="1"/>
+      <c r="C44" s="2"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="2"/>
+    </row>
+    <row r="45" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B45" s="1"/>
+      <c r="C45" s="2"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="2"/>
+    </row>
+    <row r="46" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B46" s="1"/>
+      <c r="C46" s="2"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="2"/>
+    </row>
+    <row r="47" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B47" s="1"/>
+      <c r="C47" s="2"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="2"/>
+    </row>
+    <row r="48" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B48" s="1"/>
+      <c r="C48" s="2"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="2"/>
+    </row>
+    <row r="49" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B49" s="1"/>
+      <c r="C49" s="2"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="2"/>
+    </row>
+    <row r="50" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B50" s="1"/>
+      <c r="C50" s="2"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="2"/>
+    </row>
+    <row r="51" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B51" s="1"/>
+      <c r="C51" s="2"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="2"/>
+    </row>
+    <row r="52" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B52" s="1"/>
+      <c r="C52" s="2"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="2"/>
+    </row>
+    <row r="53" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B53" s="1"/>
+      <c r="C53" s="2"/>
+    </row>
+    <row r="54" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B54" s="1"/>
+      <c r="C54" s="2"/>
+    </row>
+    <row r="55" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B55" s="1"/>
+      <c r="C55" s="2"/>
+    </row>
+    <row r="56" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B56" s="1"/>
+      <c r="C56" s="2"/>
+    </row>
+    <row r="57" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B57" s="1"/>
+      <c r="C57" s="2"/>
+    </row>
+    <row r="58" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B58" s="1"/>
+      <c r="C58" s="2"/>
+    </row>
+    <row r="59" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B59" s="1"/>
+      <c r="C59" s="2"/>
+    </row>
+    <row r="60" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B60" s="3"/>
+      <c r="C60" s="2"/>
+    </row>
+    <row r="61" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B61" s="1"/>
+      <c r="C61" s="2"/>
+    </row>
+    <row r="62" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B62" s="1"/>
+      <c r="C62" s="2"/>
+    </row>
+    <row r="63" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B63" s="1"/>
+      <c r="C63" s="2"/>
+    </row>
+    <row r="64" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B64" s="1"/>
+      <c r="C64" s="2"/>
+    </row>
+    <row r="65" spans="2:3" ht="19.05" customHeight="1">
+      <c r="B65" s="1"/>
+      <c r="C65" s="2"/>
+    </row>
+    <row r="66" spans="2:3" ht="19.05" customHeight="1">
+      <c r="B66" s="1"/>
+      <c r="C66" s="2"/>
+    </row>
+    <row r="67" spans="2:3" ht="19.05" customHeight="1">
+      <c r="B67" s="1"/>
+      <c r="C67" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B2:K3"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC53565C-0D4B-F642-9CFF-865ED2FE591E}">
   <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6"/>
@@ -22596,45 +23108,45 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A2" s="359" t="s">
+      <c r="A2" s="363" t="s">
         <v>1569</v>
       </c>
-      <c r="B2" s="359"/>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
+      <c r="B2" s="363"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
     </row>
     <row r="3" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A3" s="359"/>
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
+      <c r="A3" s="363"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
     </row>
     <row r="4" spans="1:11" ht="16.95" customHeight="1">
-      <c r="A4" s="359"/>
-      <c r="B4" s="359"/>
-      <c r="C4" s="359"/>
-      <c r="D4" s="359"/>
-      <c r="E4" s="359"/>
-      <c r="F4" s="359"/>
-      <c r="G4" s="359"/>
-      <c r="H4" s="359"/>
-      <c r="I4" s="359"/>
-      <c r="J4" s="359"/>
-      <c r="K4" s="359"/>
+      <c r="A4" s="363"/>
+      <c r="B4" s="363"/>
+      <c r="C4" s="363"/>
+      <c r="D4" s="363"/>
+      <c r="E4" s="363"/>
+      <c r="F4" s="363"/>
+      <c r="G4" s="363"/>
+      <c r="H4" s="363"/>
+      <c r="I4" s="363"/>
+      <c r="J4" s="363"/>
+      <c r="K4" s="363"/>
     </row>
     <row r="5" spans="1:11" ht="16.95" customHeight="1" thickBot="1">
       <c r="A5" s="111"/>
@@ -22651,10 +23163,10 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="374" t="s">
+      <c r="B6" s="377" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="376" t="s">
+      <c r="C6" s="379" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="130" t="s">
@@ -22670,8 +23182,8 @@
     </row>
     <row r="7" spans="1:11" ht="21">
       <c r="A7" s="13"/>
-      <c r="B7" s="415"/>
-      <c r="C7" s="360"/>
+      <c r="B7" s="419"/>
+      <c r="C7" s="364"/>
       <c r="D7" s="312" t="s">
         <v>100</v>
       </c>
@@ -22883,7 +23395,386 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D779D1C-8F42-C64E-B34F-79AD626C6510}">
+  <dimension ref="A1:K30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6"/>
+  <cols>
+    <col min="2" max="2" width="46.19921875" customWidth="1"/>
+    <col min="3" max="3" width="13.19921875" customWidth="1"/>
+    <col min="4" max="4" width="13.796875" customWidth="1"/>
+    <col min="5" max="5" width="15.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="363" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B2" s="363"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="363"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="363"/>
+      <c r="B4" s="363"/>
+      <c r="C4" s="363"/>
+      <c r="D4" s="363"/>
+      <c r="E4" s="363"/>
+      <c r="F4" s="363"/>
+      <c r="G4" s="363"/>
+      <c r="H4" s="363"/>
+      <c r="I4" s="363"/>
+      <c r="J4" s="363"/>
+      <c r="K4" s="363"/>
+    </row>
+    <row r="5" spans="1:11" ht="45">
+      <c r="A5" s="111"/>
+      <c r="B5" s="111"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="111"/>
+      <c r="E5" s="111"/>
+      <c r="F5" s="111"/>
+      <c r="G5" s="111"/>
+      <c r="H5" s="111"/>
+      <c r="I5" s="111"/>
+      <c r="J5" s="111"/>
+      <c r="K5" s="111"/>
+    </row>
+    <row r="6" spans="1:11" ht="21">
+      <c r="A6" s="13"/>
+      <c r="B6" s="364" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="364" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="112" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" s="163" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" s="13"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+    </row>
+    <row r="7" spans="1:11" ht="21">
+      <c r="A7" s="13"/>
+      <c r="B7" s="364"/>
+      <c r="C7" s="364"/>
+      <c r="D7" s="112" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="163" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" s="13"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+    </row>
+    <row r="8" spans="1:11" ht="21">
+      <c r="A8" s="7"/>
+      <c r="B8" s="113" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C8" s="113" t="s">
+        <v>858</v>
+      </c>
+      <c r="D8" s="189">
+        <v>42.671953738124735</v>
+      </c>
+      <c r="E8" s="129"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+    </row>
+    <row r="9" spans="1:11" ht="21">
+      <c r="A9" s="7"/>
+      <c r="B9" s="113" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C9" s="113" t="s">
+        <v>865</v>
+      </c>
+      <c r="D9" s="189">
+        <v>40.087567121024371</v>
+      </c>
+      <c r="E9" s="129"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+    </row>
+    <row r="10" spans="1:11" ht="21">
+      <c r="A10" s="7"/>
+      <c r="B10" s="113" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C10" s="113" t="s">
+        <v>895</v>
+      </c>
+      <c r="D10" s="189">
+        <v>36.563403552251138</v>
+      </c>
+      <c r="E10" s="129"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+    </row>
+    <row r="11" spans="1:11" ht="21">
+      <c r="B11" s="113" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C11" s="113" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" s="189">
+        <v>36.563403552251138</v>
+      </c>
+      <c r="E11" s="105"/>
+    </row>
+    <row r="12" spans="1:11" ht="21">
+      <c r="B12" s="113" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C12" s="113" t="s">
+        <v>858</v>
+      </c>
+      <c r="D12" s="189">
+        <v>24.111358942585699</v>
+      </c>
+      <c r="E12" s="105"/>
+    </row>
+    <row r="13" spans="1:11" ht="21">
+      <c r="B13" s="113" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C13" s="113" t="s">
+        <v>895</v>
+      </c>
+      <c r="D13" s="189">
+        <v>21.996860801321763</v>
+      </c>
+      <c r="E13" s="105"/>
+    </row>
+    <row r="14" spans="1:11" ht="21">
+      <c r="B14" s="113" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C14" s="113" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14" s="189">
+        <v>20.822139611730687</v>
+      </c>
+      <c r="E14" s="105"/>
+    </row>
+    <row r="15" spans="1:11" ht="21">
+      <c r="B15" s="113" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C15" s="113" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="189">
+        <v>19.647418422139612</v>
+      </c>
+      <c r="E15" s="105"/>
+    </row>
+    <row r="16" spans="1:11" ht="21">
+      <c r="B16" s="113" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C16" s="113" t="s">
+        <v>858</v>
+      </c>
+      <c r="D16" s="189">
+        <v>75.246972325485345</v>
+      </c>
+      <c r="E16" s="105"/>
+    </row>
+    <row r="17" spans="2:5" ht="21">
+      <c r="B17" s="113" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C17" s="113" t="s">
+        <v>895</v>
+      </c>
+      <c r="D17" s="189">
+        <v>64.051879388682366</v>
+      </c>
+      <c r="E17" s="105"/>
+    </row>
+    <row r="18" spans="2:5" ht="21">
+      <c r="B18" s="113" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C18" s="113" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" s="189">
+        <v>68.280875671210239</v>
+      </c>
+      <c r="E18" s="105"/>
+    </row>
+    <row r="19" spans="2:5" ht="21">
+      <c r="B19" s="113" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C19" s="113" t="s">
+        <v>858</v>
+      </c>
+      <c r="D19" s="189">
+        <v>17.063031805039241</v>
+      </c>
+      <c r="E19" s="105"/>
+    </row>
+    <row r="20" spans="2:5" ht="21">
+      <c r="B20" s="113" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C20" s="113" t="s">
+        <v>895</v>
+      </c>
+      <c r="D20" s="189">
+        <v>14.948533663775299</v>
+      </c>
+      <c r="E20" s="105"/>
+    </row>
+    <row r="21" spans="2:5" ht="21">
+      <c r="B21" s="113" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C21" s="113" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" s="189">
+        <v>13.77381247418422</v>
+      </c>
+      <c r="E21" s="105"/>
+    </row>
+    <row r="22" spans="2:5" ht="21">
+      <c r="B22" s="113" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C22" s="113" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="189">
+        <v>12.599091284593142</v>
+      </c>
+      <c r="E22" s="105"/>
+    </row>
+    <row r="23" spans="2:5" ht="21">
+      <c r="B23" s="113" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C23" s="113" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D23" s="189">
+        <v>14.713589425857082</v>
+      </c>
+      <c r="E23" s="105"/>
+    </row>
+    <row r="24" spans="2:5" ht="21">
+      <c r="B24" s="105"/>
+      <c r="C24" s="105"/>
+      <c r="D24" s="207"/>
+      <c r="E24" s="105"/>
+    </row>
+    <row r="25" spans="2:5" ht="21">
+      <c r="B25" s="105" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C25" s="105" t="s">
+        <v>858</v>
+      </c>
+      <c r="D25" s="207"/>
+      <c r="E25" s="105">
+        <v>8.85</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="21">
+      <c r="B26" s="105"/>
+      <c r="C26" s="105"/>
+      <c r="D26" s="207"/>
+      <c r="E26" s="105"/>
+    </row>
+    <row r="27" spans="2:5" ht="21">
+      <c r="B27" s="105"/>
+      <c r="C27" s="105"/>
+      <c r="D27" s="207"/>
+      <c r="E27" s="105"/>
+    </row>
+    <row r="28" spans="2:5" ht="21">
+      <c r="B28" s="105"/>
+      <c r="C28" s="105"/>
+      <c r="D28" s="207"/>
+      <c r="E28" s="105"/>
+    </row>
+    <row r="29" spans="2:5" ht="21">
+      <c r="B29" s="105"/>
+      <c r="C29" s="105"/>
+      <c r="D29" s="207"/>
+      <c r="E29" s="105"/>
+    </row>
+    <row r="30" spans="2:5" ht="21">
+      <c r="B30" s="113"/>
+      <c r="C30" s="113"/>
+      <c r="D30" s="105"/>
+      <c r="E30" s="105"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:K4"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AECF0B3-8484-4395-A4E9-AC5E8051C752}">
   <dimension ref="B1:K67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -22895,30 +23786,30 @@
   <sheetData>
     <row r="1" spans="2:11" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:11" ht="19.05" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1570</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
     </row>
     <row r="3" spans="2:11" ht="19.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
     </row>
     <row r="4" spans="2:11" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -22928,10 +23819,10 @@
     <row r="5" spans="2:11" ht="19.05" customHeight="1" thickBot="1"/>
     <row r="6" spans="2:11" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="367" t="s">
+      <c r="C6" s="370" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="367" t="s">
+      <c r="D6" s="370" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="8" t="s">
@@ -22942,8 +23833,8 @@
     </row>
     <row r="7" spans="2:11" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B7" s="13"/>
-      <c r="C7" s="368"/>
-      <c r="D7" s="368"/>
+      <c r="C7" s="371"/>
+      <c r="D7" s="371"/>
       <c r="E7" s="16" t="s">
         <v>100</v>
       </c>
@@ -23319,386 +24210,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D779D1C-8F42-C64E-B34F-79AD626C6510}">
-  <dimension ref="A1:K30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6"/>
-  <cols>
-    <col min="2" max="2" width="46.19921875" customWidth="1"/>
-    <col min="3" max="3" width="13.19921875" customWidth="1"/>
-    <col min="4" max="4" width="13.796875" customWidth="1"/>
-    <col min="5" max="5" width="15.19921875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>1670</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="359" t="s">
-        <v>1691</v>
-      </c>
-      <c r="B2" s="359"/>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="359"/>
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="359"/>
-      <c r="B4" s="359"/>
-      <c r="C4" s="359"/>
-      <c r="D4" s="359"/>
-      <c r="E4" s="359"/>
-      <c r="F4" s="359"/>
-      <c r="G4" s="359"/>
-      <c r="H4" s="359"/>
-      <c r="I4" s="359"/>
-      <c r="J4" s="359"/>
-      <c r="K4" s="359"/>
-    </row>
-    <row r="5" spans="1:11" ht="45">
-      <c r="A5" s="111"/>
-      <c r="B5" s="111"/>
-      <c r="C5" s="111"/>
-      <c r="D5" s="111"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="111"/>
-      <c r="G5" s="111"/>
-      <c r="H5" s="111"/>
-      <c r="I5" s="111"/>
-      <c r="J5" s="111"/>
-      <c r="K5" s="111"/>
-    </row>
-    <row r="6" spans="1:11" ht="21">
-      <c r="A6" s="13"/>
-      <c r="B6" s="360" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="360" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="112" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" s="163" t="s">
-        <v>84</v>
-      </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-    </row>
-    <row r="7" spans="1:11" ht="21">
-      <c r="A7" s="13"/>
-      <c r="B7" s="360"/>
-      <c r="C7" s="360"/>
-      <c r="D7" s="112" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" s="163" t="s">
-        <v>98</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-    </row>
-    <row r="8" spans="1:11" ht="21">
-      <c r="A8" s="7"/>
-      <c r="B8" s="113" t="s">
-        <v>1692</v>
-      </c>
-      <c r="C8" s="113" t="s">
-        <v>858</v>
-      </c>
-      <c r="D8" s="189">
-        <v>42.671953738124735</v>
-      </c>
-      <c r="E8" s="129"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-    </row>
-    <row r="9" spans="1:11" ht="21">
-      <c r="A9" s="7"/>
-      <c r="B9" s="113" t="s">
-        <v>1692</v>
-      </c>
-      <c r="C9" s="113" t="s">
-        <v>865</v>
-      </c>
-      <c r="D9" s="189">
-        <v>40.087567121024371</v>
-      </c>
-      <c r="E9" s="129"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-    </row>
-    <row r="10" spans="1:11" ht="21">
-      <c r="A10" s="7"/>
-      <c r="B10" s="113" t="s">
-        <v>1692</v>
-      </c>
-      <c r="C10" s="113" t="s">
-        <v>895</v>
-      </c>
-      <c r="D10" s="189">
-        <v>36.563403552251138</v>
-      </c>
-      <c r="E10" s="129"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-    </row>
-    <row r="11" spans="1:11" ht="21">
-      <c r="B11" s="113" t="s">
-        <v>1692</v>
-      </c>
-      <c r="C11" s="113" t="s">
-        <v>111</v>
-      </c>
-      <c r="D11" s="189">
-        <v>36.563403552251138</v>
-      </c>
-      <c r="E11" s="105"/>
-    </row>
-    <row r="12" spans="1:11" ht="21">
-      <c r="B12" s="113" t="s">
-        <v>1693</v>
-      </c>
-      <c r="C12" s="113" t="s">
-        <v>858</v>
-      </c>
-      <c r="D12" s="189">
-        <v>24.111358942585699</v>
-      </c>
-      <c r="E12" s="105"/>
-    </row>
-    <row r="13" spans="1:11" ht="21">
-      <c r="B13" s="113" t="s">
-        <v>1693</v>
-      </c>
-      <c r="C13" s="113" t="s">
-        <v>895</v>
-      </c>
-      <c r="D13" s="189">
-        <v>21.996860801321763</v>
-      </c>
-      <c r="E13" s="105"/>
-    </row>
-    <row r="14" spans="1:11" ht="21">
-      <c r="B14" s="113" t="s">
-        <v>1693</v>
-      </c>
-      <c r="C14" s="113" t="s">
-        <v>111</v>
-      </c>
-      <c r="D14" s="189">
-        <v>20.822139611730687</v>
-      </c>
-      <c r="E14" s="105"/>
-    </row>
-    <row r="15" spans="1:11" ht="21">
-      <c r="B15" s="113" t="s">
-        <v>1693</v>
-      </c>
-      <c r="C15" s="113" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="189">
-        <v>19.647418422139612</v>
-      </c>
-      <c r="E15" s="105"/>
-    </row>
-    <row r="16" spans="1:11" ht="21">
-      <c r="B16" s="113" t="s">
-        <v>1694</v>
-      </c>
-      <c r="C16" s="113" t="s">
-        <v>858</v>
-      </c>
-      <c r="D16" s="189">
-        <v>75.246972325485345</v>
-      </c>
-      <c r="E16" s="105"/>
-    </row>
-    <row r="17" spans="2:5" ht="21">
-      <c r="B17" s="113" t="s">
-        <v>1694</v>
-      </c>
-      <c r="C17" s="113" t="s">
-        <v>895</v>
-      </c>
-      <c r="D17" s="189">
-        <v>64.051879388682366</v>
-      </c>
-      <c r="E17" s="105"/>
-    </row>
-    <row r="18" spans="2:5" ht="21">
-      <c r="B18" s="113" t="s">
-        <v>1694</v>
-      </c>
-      <c r="C18" s="113" t="s">
-        <v>111</v>
-      </c>
-      <c r="D18" s="189">
-        <v>68.280875671210239</v>
-      </c>
-      <c r="E18" s="105"/>
-    </row>
-    <row r="19" spans="2:5" ht="21">
-      <c r="B19" s="113" t="s">
-        <v>1695</v>
-      </c>
-      <c r="C19" s="113" t="s">
-        <v>858</v>
-      </c>
-      <c r="D19" s="189">
-        <v>17.063031805039241</v>
-      </c>
-      <c r="E19" s="105"/>
-    </row>
-    <row r="20" spans="2:5" ht="21">
-      <c r="B20" s="113" t="s">
-        <v>1695</v>
-      </c>
-      <c r="C20" s="113" t="s">
-        <v>895</v>
-      </c>
-      <c r="D20" s="189">
-        <v>14.948533663775299</v>
-      </c>
-      <c r="E20" s="105"/>
-    </row>
-    <row r="21" spans="2:5" ht="21">
-      <c r="B21" s="113" t="s">
-        <v>1695</v>
-      </c>
-      <c r="C21" s="113" t="s">
-        <v>111</v>
-      </c>
-      <c r="D21" s="189">
-        <v>13.77381247418422</v>
-      </c>
-      <c r="E21" s="105"/>
-    </row>
-    <row r="22" spans="2:5" ht="21">
-      <c r="B22" s="113" t="s">
-        <v>1696</v>
-      </c>
-      <c r="C22" s="113" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" s="189">
-        <v>12.599091284593142</v>
-      </c>
-      <c r="E22" s="105"/>
-    </row>
-    <row r="23" spans="2:5" ht="21">
-      <c r="B23" s="113" t="s">
-        <v>1696</v>
-      </c>
-      <c r="C23" s="113" t="s">
-        <v>1697</v>
-      </c>
-      <c r="D23" s="189">
-        <v>14.713589425857082</v>
-      </c>
-      <c r="E23" s="105"/>
-    </row>
-    <row r="24" spans="2:5" ht="21">
-      <c r="B24" s="105"/>
-      <c r="C24" s="105"/>
-      <c r="D24" s="207"/>
-      <c r="E24" s="105"/>
-    </row>
-    <row r="25" spans="2:5" ht="21">
-      <c r="B25" s="105" t="s">
-        <v>1698</v>
-      </c>
-      <c r="C25" s="105" t="s">
-        <v>858</v>
-      </c>
-      <c r="D25" s="207"/>
-      <c r="E25" s="105">
-        <v>8.85</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" ht="21">
-      <c r="B26" s="105"/>
-      <c r="C26" s="105"/>
-      <c r="D26" s="207"/>
-      <c r="E26" s="105"/>
-    </row>
-    <row r="27" spans="2:5" ht="21">
-      <c r="B27" s="105"/>
-      <c r="C27" s="105"/>
-      <c r="D27" s="207"/>
-      <c r="E27" s="105"/>
-    </row>
-    <row r="28" spans="2:5" ht="21">
-      <c r="B28" s="105"/>
-      <c r="C28" s="105"/>
-      <c r="D28" s="207"/>
-      <c r="E28" s="105"/>
-    </row>
-    <row r="29" spans="2:5" ht="21">
-      <c r="B29" s="105"/>
-      <c r="C29" s="105"/>
-      <c r="D29" s="207"/>
-      <c r="E29" s="105"/>
-    </row>
-    <row r="30" spans="2:5" ht="21">
-      <c r="B30" s="113"/>
-      <c r="C30" s="113"/>
-      <c r="D30" s="105"/>
-      <c r="E30" s="105"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:K4"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{325547DD-C65B-B444-908A-9F3B67A97AD2}">
   <dimension ref="B1:K34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -23713,30 +24225,30 @@
   <sheetData>
     <row r="1" spans="2:11" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:11" ht="19.05" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1514</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
     </row>
     <row r="3" spans="2:11" ht="19.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
     </row>
     <row r="4" spans="2:11" ht="19.05" customHeight="1"/>
     <row r="5" spans="2:11" ht="19.05" customHeight="1" thickBot="1">
@@ -23746,13 +24258,13 @@
     </row>
     <row r="6" spans="2:11" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="367" t="s">
+      <c r="C6" s="370" t="s">
         <v>102</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="E6" s="367" t="s">
+      <c r="E6" s="370" t="s">
         <v>0</v>
       </c>
       <c r="F6" s="8" t="s">
@@ -23763,11 +24275,11 @@
     </row>
     <row r="7" spans="2:11" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B7" s="13"/>
-      <c r="C7" s="368"/>
+      <c r="C7" s="371"/>
       <c r="D7" s="16" t="s">
         <v>1507</v>
       </c>
-      <c r="E7" s="368"/>
+      <c r="E7" s="371"/>
       <c r="F7" s="16" t="s">
         <v>100</v>
       </c>
@@ -23969,7 +24481,299 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AFECCCB-D572-1841-9994-71F02FAD27B6}">
+  <dimension ref="B1:J25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="3.5" customWidth="1"/>
+    <col min="3" max="3" width="75.296875" customWidth="1"/>
+    <col min="4" max="4" width="12.19921875" style="71" customWidth="1"/>
+    <col min="5" max="5" width="13.69921875" customWidth="1"/>
+    <col min="13" max="13" width="31.796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:10" ht="19.05" customHeight="1"/>
+    <row r="2" spans="2:10" ht="19.05" customHeight="1">
+      <c r="B2" s="363" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+    </row>
+    <row r="3" spans="2:10" ht="19.05" customHeight="1">
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+    </row>
+    <row r="4" spans="2:10" ht="19.05" customHeight="1">
+      <c r="B4" s="334"/>
+      <c r="C4" s="334"/>
+      <c r="D4" s="334"/>
+      <c r="E4" s="334"/>
+      <c r="F4" s="334"/>
+      <c r="G4" s="334"/>
+      <c r="H4" s="334"/>
+      <c r="I4" s="334"/>
+      <c r="J4" s="334"/>
+    </row>
+    <row r="5" spans="2:10" ht="19.05" customHeight="1">
+      <c r="B5" s="334"/>
+      <c r="C5" s="334"/>
+      <c r="D5" s="334"/>
+      <c r="E5" s="334"/>
+      <c r="F5" s="334"/>
+      <c r="G5" s="334"/>
+      <c r="H5" s="334"/>
+      <c r="I5" s="334"/>
+      <c r="J5" s="334"/>
+    </row>
+    <row r="6" spans="2:10" ht="19.05" customHeight="1">
+      <c r="C6" s="362" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="19.05" customHeight="1">
+      <c r="B7" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" s="9" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B8" s="13"/>
+      <c r="C8" s="364" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="364" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="112" t="s">
+        <v>84</v>
+      </c>
+      <c r="F8" s="361" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="13"/>
+    </row>
+    <row r="9" spans="2:10" s="9" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B9" s="13"/>
+      <c r="C9" s="364"/>
+      <c r="D9" s="364"/>
+      <c r="E9" s="112" t="s">
+        <v>100</v>
+      </c>
+      <c r="F9" s="361" t="s">
+        <v>1125</v>
+      </c>
+      <c r="G9" s="13"/>
+    </row>
+    <row r="10" spans="2:10" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="C10" s="105" t="s">
+        <v>1760</v>
+      </c>
+      <c r="D10" s="105" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="309">
+        <v>36.155858460691178</v>
+      </c>
+      <c r="F10" s="129"/>
+      <c r="G10" s="12"/>
+    </row>
+    <row r="11" spans="2:10" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="C11" s="105" t="s">
+        <v>1761</v>
+      </c>
+      <c r="D11" s="105" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="309">
+        <v>44</v>
+      </c>
+      <c r="F11" s="129"/>
+      <c r="G11" s="12"/>
+    </row>
+    <row r="12" spans="2:10" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="C12" s="105" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D12" s="105" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" s="309">
+        <v>37.973289274404515</v>
+      </c>
+      <c r="F12" s="129"/>
+      <c r="G12" s="12"/>
+    </row>
+    <row r="13" spans="2:10" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="C13" s="105" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D13" s="105" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="309">
+        <v>47</v>
+      </c>
+      <c r="F13" s="129"/>
+      <c r="G13" s="12"/>
+    </row>
+    <row r="14" spans="2:10" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="C14" s="105" t="s">
+        <v>1764</v>
+      </c>
+      <c r="D14" s="105" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="309">
+        <v>40.69943549497453</v>
+      </c>
+      <c r="F14" s="129"/>
+      <c r="G14" s="12"/>
+    </row>
+    <row r="15" spans="2:10" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="C15" s="105" t="s">
+        <v>1765</v>
+      </c>
+      <c r="D15" s="105" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="309">
+        <v>49</v>
+      </c>
+      <c r="F15" s="129"/>
+      <c r="G15" s="12"/>
+      <c r="I15" s="360"/>
+    </row>
+    <row r="16" spans="2:10" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="C16" s="105"/>
+      <c r="D16" s="105"/>
+      <c r="E16" s="309"/>
+      <c r="F16" s="129"/>
+      <c r="G16" s="12"/>
+    </row>
+    <row r="17" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="C17" s="105" t="s">
+        <v>1760</v>
+      </c>
+      <c r="D17" s="105" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="309"/>
+      <c r="F17" s="359">
+        <v>389</v>
+      </c>
+      <c r="G17" s="12"/>
+    </row>
+    <row r="18" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="C18" s="105" t="s">
+        <v>1761</v>
+      </c>
+      <c r="D18" s="105" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" s="309"/>
+      <c r="F18" s="359">
+        <v>473</v>
+      </c>
+      <c r="G18" s="12"/>
+    </row>
+    <row r="19" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="C19" s="105" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D19" s="105" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" s="309"/>
+      <c r="F19" s="359">
+        <v>408</v>
+      </c>
+      <c r="G19" s="12"/>
+    </row>
+    <row r="20" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="C20" s="105" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D20" s="105" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="309"/>
+      <c r="F20" s="359">
+        <v>505</v>
+      </c>
+      <c r="G20" s="12"/>
+    </row>
+    <row r="21" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="C21" s="105" t="s">
+        <v>1764</v>
+      </c>
+      <c r="D21" s="105" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="309"/>
+      <c r="F21" s="359">
+        <v>438</v>
+      </c>
+      <c r="G21" s="12"/>
+    </row>
+    <row r="22" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="C22" s="105" t="s">
+        <v>1765</v>
+      </c>
+      <c r="D22" s="105" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" s="212"/>
+      <c r="F22" s="359">
+        <v>527</v>
+      </c>
+      <c r="G22" s="12"/>
+    </row>
+    <row r="23" spans="2:7" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="C23" s="105"/>
+      <c r="D23" s="105"/>
+      <c r="E23" s="212"/>
+      <c r="F23" s="129"/>
+      <c r="G23" s="12"/>
+    </row>
+    <row r="24" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B24" s="1"/>
+      <c r="C24" s="105"/>
+      <c r="D24" s="105"/>
+      <c r="E24" s="212"/>
+      <c r="F24" s="129"/>
+    </row>
+    <row r="25" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B25" s="1"/>
+      <c r="C25" s="105"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="212"/>
+      <c r="F25" s="129"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B2:J3"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="B1:J60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -23983,28 +24787,28 @@
   <sheetData>
     <row r="1" spans="2:10" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:10" ht="19.05" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1593</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
     </row>
     <row r="3" spans="2:10" ht="19.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
     </row>
     <row r="4" spans="2:10" ht="19.05" customHeight="1"/>
     <row r="5" spans="2:10" ht="19.05" customHeight="1" thickBot="1">
@@ -24014,10 +24818,10 @@
     </row>
     <row r="6" spans="2:10" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="367" t="s">
+      <c r="C6" s="370" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="367" t="s">
+      <c r="D6" s="370" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="8" t="s">
@@ -24028,8 +24832,8 @@
     </row>
     <row r="7" spans="2:10" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B7" s="13"/>
-      <c r="C7" s="368"/>
-      <c r="D7" s="368"/>
+      <c r="C7" s="371"/>
+      <c r="D7" s="371"/>
       <c r="E7" s="16" t="s">
         <v>100</v>
       </c>
@@ -24554,7 +25358,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1990C61-06D6-BE49-B26D-A3A937C622B8}">
   <dimension ref="B1:J23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -24568,28 +25372,28 @@
   <sheetData>
     <row r="1" spans="2:10" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:10" ht="19.05" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1571</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
     </row>
     <row r="3" spans="2:10" ht="19.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
     </row>
     <row r="4" spans="2:10" ht="19.05" customHeight="1"/>
     <row r="5" spans="2:10" ht="19.05" customHeight="1">
@@ -24599,10 +25403,10 @@
     </row>
     <row r="6" spans="2:10" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="360" t="s">
+      <c r="C6" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="360" t="s">
+      <c r="D6" s="364" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="112" t="s">
@@ -24615,8 +25419,8 @@
     </row>
     <row r="7" spans="2:10" s="9" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
       <c r="B7" s="13"/>
-      <c r="C7" s="361"/>
-      <c r="D7" s="361"/>
+      <c r="C7" s="380"/>
+      <c r="D7" s="380"/>
       <c r="E7" s="149" t="s">
         <v>100</v>
       </c>
@@ -24843,7 +25647,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="B1:P128"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -24859,34 +25663,34 @@
   <sheetData>
     <row r="1" spans="2:13" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:13" ht="19.05" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1572</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
-      <c r="L2" s="359"/>
-      <c r="M2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
+      <c r="L2" s="363"/>
+      <c r="M2" s="363"/>
     </row>
     <row r="3" spans="2:13" ht="19.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
-      <c r="M3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+      <c r="L3" s="363"/>
+      <c r="M3" s="363"/>
     </row>
     <row r="4" spans="2:13" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -24895,14 +25699,14 @@
     </row>
     <row r="5" spans="2:13" ht="19.05" customHeight="1" thickBot="1"/>
     <row r="6" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B6" s="367" t="s">
+      <c r="B6" s="370" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="21" t="s">
         <v>101</v>
       </c>
       <c r="D6" s="9"/>
-      <c r="E6" s="367" t="s">
+      <c r="E6" s="370" t="s">
         <v>99</v>
       </c>
       <c r="F6" s="21" t="s">
@@ -24911,12 +25715,12 @@
       <c r="G6" s="11"/>
     </row>
     <row r="7" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
-      <c r="B7" s="369"/>
+      <c r="B7" s="372"/>
       <c r="C7" s="22" t="s">
         <v>100</v>
       </c>
       <c r="D7" s="9"/>
-      <c r="E7" s="369"/>
+      <c r="E7" s="372"/>
       <c r="F7" s="22" t="s">
         <v>100</v>
       </c>
@@ -24966,11 +25770,11 @@
         <v>40.304575703336546</v>
       </c>
       <c r="G10" s="12"/>
-      <c r="I10" s="418" t="s">
+      <c r="I10" s="422" t="s">
         <v>97</v>
       </c>
-      <c r="J10" s="419"/>
-      <c r="K10" s="420"/>
+      <c r="J10" s="423"/>
+      <c r="K10" s="424"/>
       <c r="L10" s="23"/>
     </row>
     <row r="11" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1">
@@ -24987,10 +25791,10 @@
         <v>43.338181651291933</v>
       </c>
       <c r="G11" s="12"/>
-      <c r="I11" s="418" t="s">
+      <c r="I11" s="422" t="s">
         <v>103</v>
       </c>
-      <c r="J11" s="422" t="s">
+      <c r="J11" s="426" t="s">
         <v>0</v>
       </c>
       <c r="K11" s="24" t="s">
@@ -25011,8 +25815,8 @@
         <v>43.345021799990811</v>
       </c>
       <c r="G12" s="12"/>
-      <c r="I12" s="421"/>
-      <c r="J12" s="423"/>
+      <c r="I12" s="425"/>
+      <c r="J12" s="427"/>
       <c r="K12" s="25" t="s">
         <v>100</v>
       </c>
@@ -25944,7 +26748,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1027015D-487D-DD4F-8ABF-780817ED8D59}">
   <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6"/>
@@ -25960,45 +26764,45 @@
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="359" t="s">
+      <c r="A2" s="363" t="s">
         <v>1573</v>
       </c>
-      <c r="B2" s="359"/>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
+      <c r="B2" s="363"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="359"/>
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
+      <c r="A3" s="363"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="359"/>
-      <c r="B4" s="359"/>
-      <c r="C4" s="359"/>
-      <c r="D4" s="359"/>
-      <c r="E4" s="359"/>
-      <c r="F4" s="359"/>
-      <c r="G4" s="359"/>
-      <c r="H4" s="359"/>
-      <c r="I4" s="359"/>
-      <c r="J4" s="359"/>
-      <c r="K4" s="359"/>
+      <c r="A4" s="363"/>
+      <c r="B4" s="363"/>
+      <c r="C4" s="363"/>
+      <c r="D4" s="363"/>
+      <c r="E4" s="363"/>
+      <c r="F4" s="363"/>
+      <c r="G4" s="363"/>
+      <c r="H4" s="363"/>
+      <c r="I4" s="363"/>
+      <c r="J4" s="363"/>
+      <c r="K4" s="363"/>
     </row>
     <row r="5" spans="1:11" ht="45.6" thickBot="1">
       <c r="A5" s="111"/>
@@ -26015,10 +26819,10 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="424" t="s">
+      <c r="B6" s="428" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="426" t="s">
+      <c r="C6" s="430" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="282" t="s">
@@ -26034,8 +26838,8 @@
     </row>
     <row r="7" spans="1:11" ht="21">
       <c r="A7" s="13"/>
-      <c r="B7" s="425"/>
-      <c r="C7" s="427"/>
+      <c r="B7" s="429"/>
+      <c r="C7" s="431"/>
       <c r="D7" s="284" t="s">
         <v>100</v>
       </c>
@@ -26187,7 +26991,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25506AED-C7DA-1E4E-801C-D8A7E27EA3F8}">
   <dimension ref="B1:I68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -26203,26 +27007,26 @@
   <sheetData>
     <row r="1" spans="2:9" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:9" ht="19.05" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1574</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
     </row>
     <row r="3" spans="2:9" ht="19.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
     </row>
     <row r="4" spans="2:9" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -26231,14 +27035,14 @@
     </row>
     <row r="5" spans="2:9" ht="19.05" customHeight="1" thickBot="1"/>
     <row r="6" spans="2:9" s="9" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B6" s="367" t="s">
+      <c r="B6" s="370" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>101</v>
       </c>
       <c r="E6" s="96"/>
-      <c r="G6" s="367" t="s">
+      <c r="G6" s="370" t="s">
         <v>99</v>
       </c>
       <c r="H6" s="8" t="s">
@@ -26246,12 +27050,12 @@
       </c>
     </row>
     <row r="7" spans="2:9" s="9" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B7" s="368"/>
+      <c r="B7" s="371"/>
       <c r="C7" s="16" t="s">
         <v>98</v>
       </c>
       <c r="E7" s="96"/>
-      <c r="G7" s="368"/>
+      <c r="G7" s="371"/>
       <c r="H7" s="16" t="s">
         <v>100</v>
       </c>
@@ -27001,7 +27805,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D7A3D9-D001-F74F-A815-3F376934A37D}">
   <dimension ref="B1:L71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -27017,26 +27821,26 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1581</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
     </row>
     <row r="3" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
     </row>
     <row r="4" spans="2:12" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -27137,14 +27941,14 @@
     </row>
     <row r="12" spans="2:12" ht="19.05" customHeight="1" thickBot="1"/>
     <row r="13" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B13" s="367" t="s">
+      <c r="B13" s="370" t="s">
         <v>99</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>101</v>
       </c>
       <c r="E13" s="96"/>
-      <c r="G13" s="367" t="s">
+      <c r="G13" s="370" t="s">
         <v>99</v>
       </c>
       <c r="H13" s="8" t="s">
@@ -27152,12 +27956,12 @@
       </c>
     </row>
     <row r="14" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B14" s="368"/>
+      <c r="B14" s="371"/>
       <c r="C14" s="16" t="s">
         <v>98</v>
       </c>
       <c r="E14" s="96"/>
-      <c r="G14" s="368"/>
+      <c r="G14" s="371"/>
       <c r="H14" s="16" t="s">
         <v>100</v>
       </c>
@@ -27939,7 +28743,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F69F168-0057-494C-B3B1-139AA2E7447A}">
   <dimension ref="B1:H106"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -27954,24 +28758,24 @@
   <sheetData>
     <row r="1" spans="2:8" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:8" ht="19.05" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1580</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
     </row>
     <row r="3" spans="2:8" ht="19.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
     </row>
     <row r="4" spans="2:8" ht="19.05" customHeight="1">
       <c r="B4" s="334"/>
@@ -27989,15 +28793,15 @@
     </row>
     <row r="6" spans="2:8" ht="10.95" customHeight="1" thickBot="1"/>
     <row r="7" spans="2:8" ht="19.05" customHeight="1">
-      <c r="B7" s="429" t="s">
+      <c r="B7" s="433" t="s">
         <v>1703</v>
       </c>
-      <c r="C7" s="430"/>
-      <c r="D7" s="430"/>
-      <c r="E7" s="430"/>
-      <c r="F7" s="430"/>
-      <c r="G7" s="430"/>
-      <c r="H7" s="431"/>
+      <c r="C7" s="434"/>
+      <c r="D7" s="434"/>
+      <c r="E7" s="434"/>
+      <c r="F7" s="434"/>
+      <c r="G7" s="434"/>
+      <c r="H7" s="435"/>
     </row>
     <row r="8" spans="2:8" ht="19.05" customHeight="1">
       <c r="B8" s="243"/>
@@ -28082,14 +28886,14 @@
       <c r="H14" s="295"/>
     </row>
     <row r="15" spans="2:8" s="9" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B15" s="367" t="s">
+      <c r="B15" s="370" t="s">
         <v>99</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>101</v>
       </c>
       <c r="E15" s="96"/>
-      <c r="G15" s="367" t="s">
+      <c r="G15" s="370" t="s">
         <v>99</v>
       </c>
       <c r="H15" s="8" t="s">
@@ -28097,12 +28901,12 @@
       </c>
     </row>
     <row r="16" spans="2:8" s="9" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B16" s="428"/>
+      <c r="B16" s="432"/>
       <c r="C16" s="16" t="s">
         <v>98</v>
       </c>
       <c r="E16" s="96"/>
-      <c r="G16" s="428"/>
+      <c r="G16" s="432"/>
       <c r="H16" s="16" t="s">
         <v>100</v>
       </c>
@@ -29207,302 +30011,6 @@
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="G15:G16"/>
     <mergeCell ref="B7:H7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7A41C34-9EE6-EE42-B14E-F1FBC76BE6C3}">
-  <dimension ref="A1:K12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6"/>
-  <cols>
-    <col min="2" max="2" width="5.69921875" customWidth="1"/>
-    <col min="3" max="3" width="46.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="10.050000000000001" customHeight="1"/>
-    <row r="2" spans="1:11" ht="16.05" customHeight="1">
-      <c r="B2" s="359" t="s">
-        <v>1699</v>
-      </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
-    </row>
-    <row r="3" spans="1:11" ht="16.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-    </row>
-    <row r="4" spans="1:11" ht="16.05" customHeight="1">
-      <c r="B4" t="s">
-        <v>1701</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="16.2" thickBot="1"/>
-    <row r="6" spans="1:11" ht="21">
-      <c r="A6" s="9"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="367" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" s="367" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-    </row>
-    <row r="7" spans="1:11" ht="21">
-      <c r="A7" s="9"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="368"/>
-      <c r="D7" s="368"/>
-      <c r="E7" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-    </row>
-    <row r="8" spans="1:11" ht="21">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="105" t="s">
-        <v>1700</v>
-      </c>
-      <c r="D8" s="105" t="s">
-        <v>83</v>
-      </c>
-      <c r="E8" s="207">
-        <v>8.26</v>
-      </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-    </row>
-    <row r="9" spans="1:11" ht="21">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="105"/>
-      <c r="D9" s="105"/>
-      <c r="E9" s="207"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-    </row>
-    <row r="10" spans="1:11" ht="21">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="105"/>
-      <c r="D10" s="105"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-    </row>
-    <row r="11" spans="1:11" ht="21">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="155"/>
-      <c r="D11" s="68"/>
-      <c r="E11" s="189"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-    </row>
-    <row r="12" spans="1:11" ht="21">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="201"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B2:K3"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-  </mergeCells>
-  <phoneticPr fontId="41" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{342BD54F-5826-E245-8B48-014A4A3D6F1C}">
-  <dimension ref="A2:K11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6"/>
-  <cols>
-    <col min="3" max="3" width="46.5" customWidth="1"/>
-    <col min="4" max="4" width="15.19921875" customWidth="1"/>
-    <col min="5" max="5" width="17.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:11" ht="12" customHeight="1"/>
-    <row r="3" spans="1:11">
-      <c r="B3" s="359" t="s">
-        <v>1582</v>
-      </c>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="B4" s="359"/>
-      <c r="C4" s="359"/>
-      <c r="D4" s="359"/>
-      <c r="E4" s="359"/>
-      <c r="F4" s="359"/>
-      <c r="G4" s="359"/>
-      <c r="H4" s="359"/>
-      <c r="I4" s="359"/>
-      <c r="J4" s="359"/>
-      <c r="K4" s="359"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="B5" t="s">
-        <v>1670</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="16.2" thickBot="1"/>
-    <row r="7" spans="1:11" ht="21">
-      <c r="A7" s="9"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="367" t="s">
-        <v>102</v>
-      </c>
-      <c r="D7" s="367" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-    </row>
-    <row r="8" spans="1:11" ht="21.6" thickBot="1">
-      <c r="A8" s="9"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="369"/>
-      <c r="D8" s="368"/>
-      <c r="E8" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-    </row>
-    <row r="9" spans="1:11" ht="21">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="110" t="s">
-        <v>738</v>
-      </c>
-      <c r="D9" s="146" t="s">
-        <v>739</v>
-      </c>
-      <c r="E9" s="148">
-        <v>8.91</v>
-      </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-    </row>
-    <row r="10" spans="1:11" ht="21">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="110" t="s">
-        <v>740</v>
-      </c>
-      <c r="D10" s="147" t="s">
-        <v>739</v>
-      </c>
-      <c r="E10" s="148">
-        <v>8.91</v>
-      </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-    </row>
-    <row r="11" spans="1:11" ht="21">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B3:K4"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -29528,38 +30036,38 @@
   <sheetData>
     <row r="1" spans="2:15" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:15" ht="19.05" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1123</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
-      <c r="L2" s="359"/>
-      <c r="M2" s="359"/>
-      <c r="N2" s="359"/>
-      <c r="O2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
+      <c r="L2" s="363"/>
+      <c r="M2" s="363"/>
+      <c r="N2" s="363"/>
+      <c r="O2" s="363"/>
     </row>
     <row r="3" spans="2:15" ht="19.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
-      <c r="M3" s="359"/>
-      <c r="N3" s="359"/>
-      <c r="O3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+      <c r="L3" s="363"/>
+      <c r="M3" s="363"/>
+      <c r="N3" s="363"/>
+      <c r="O3" s="363"/>
     </row>
     <row r="4" spans="2:15" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -29568,32 +30076,32 @@
     </row>
     <row r="5" spans="2:15" ht="19.05" customHeight="1" thickBot="1"/>
     <row r="6" spans="2:15" s="9" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B6" s="367" t="s">
+      <c r="B6" s="370" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="E6" s="367" t="s">
+      <c r="E6" s="370" t="s">
         <v>99</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>101</v>
       </c>
       <c r="G6" s="96"/>
-      <c r="H6" s="367" t="s">
+      <c r="H6" s="370" t="s">
         <v>99</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="K6" s="367" t="s">
+      <c r="K6" s="370" t="s">
         <v>99</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="N6" s="367" t="s">
+      <c r="N6" s="370" t="s">
         <v>99</v>
       </c>
       <c r="O6" s="8" t="s">
@@ -29601,24 +30109,24 @@
       </c>
     </row>
     <row r="7" spans="2:15" s="9" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
-      <c r="B7" s="369"/>
+      <c r="B7" s="372"/>
       <c r="C7" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="E7" s="369"/>
+      <c r="E7" s="372"/>
       <c r="F7" s="10" t="s">
         <v>98</v>
       </c>
       <c r="G7" s="96"/>
-      <c r="H7" s="368"/>
+      <c r="H7" s="371"/>
       <c r="I7" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="K7" s="369"/>
+      <c r="K7" s="372"/>
       <c r="L7" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="N7" s="369"/>
+      <c r="N7" s="372"/>
       <c r="O7" s="10" t="s">
         <v>100</v>
       </c>
@@ -30811,6 +31319,302 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7A41C34-9EE6-EE42-B14E-F1FBC76BE6C3}">
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6"/>
+  <cols>
+    <col min="2" max="2" width="5.69921875" customWidth="1"/>
+    <col min="3" max="3" width="46.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="10.050000000000001" customHeight="1"/>
+    <row r="2" spans="1:11" ht="16.05" customHeight="1">
+      <c r="B2" s="363" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
+    </row>
+    <row r="3" spans="1:11" ht="16.05" customHeight="1">
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+    </row>
+    <row r="4" spans="1:11" ht="16.05" customHeight="1">
+      <c r="B4" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="16.2" thickBot="1"/>
+    <row r="6" spans="1:11" ht="21">
+      <c r="A6" s="9"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="370" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" s="370" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+    </row>
+    <row r="7" spans="1:11" ht="21">
+      <c r="A7" s="9"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="371"/>
+      <c r="D7" s="371"/>
+      <c r="E7" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+    </row>
+    <row r="8" spans="1:11" ht="21">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="105" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D8" s="105" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="207">
+        <v>8.26</v>
+      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+    </row>
+    <row r="9" spans="1:11" ht="21">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="207"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+    </row>
+    <row r="10" spans="1:11" ht="21">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="207"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+    </row>
+    <row r="11" spans="1:11" ht="21">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="155"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="189"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="1:11" ht="21">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="201"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B2:K3"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+  </mergeCells>
+  <phoneticPr fontId="41" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{342BD54F-5826-E245-8B48-014A4A3D6F1C}">
+  <dimension ref="A2:K11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6"/>
+  <cols>
+    <col min="3" max="3" width="46.5" customWidth="1"/>
+    <col min="4" max="4" width="15.19921875" customWidth="1"/>
+    <col min="5" max="5" width="17.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:11" ht="12" customHeight="1"/>
+    <row r="3" spans="1:11">
+      <c r="B3" s="363" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="B4" s="363"/>
+      <c r="C4" s="363"/>
+      <c r="D4" s="363"/>
+      <c r="E4" s="363"/>
+      <c r="F4" s="363"/>
+      <c r="G4" s="363"/>
+      <c r="H4" s="363"/>
+      <c r="I4" s="363"/>
+      <c r="J4" s="363"/>
+      <c r="K4" s="363"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="B5" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="16.2" thickBot="1"/>
+    <row r="7" spans="1:11" ht="21">
+      <c r="A7" s="9"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="370" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" s="370" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+    </row>
+    <row r="8" spans="1:11" ht="21.6" thickBot="1">
+      <c r="A8" s="9"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="372"/>
+      <c r="D8" s="371"/>
+      <c r="E8" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+    </row>
+    <row r="9" spans="1:11" ht="21">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="110" t="s">
+        <v>738</v>
+      </c>
+      <c r="D9" s="146" t="s">
+        <v>739</v>
+      </c>
+      <c r="E9" s="148">
+        <v>8.91</v>
+      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+    </row>
+    <row r="10" spans="1:11" ht="21">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="110" t="s">
+        <v>740</v>
+      </c>
+      <c r="D10" s="147" t="s">
+        <v>739</v>
+      </c>
+      <c r="E10" s="148">
+        <v>8.91</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+    </row>
+    <row r="11" spans="1:11" ht="21">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B3:K4"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{647F77A2-7587-0B49-88B6-ABA2DBD12474}">
   <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6"/>
@@ -30826,45 +31630,45 @@
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="359" t="s">
+      <c r="A2" s="363" t="s">
         <v>1730</v>
       </c>
-      <c r="B2" s="359"/>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
+      <c r="B2" s="363"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="359"/>
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
+      <c r="A3" s="363"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="359"/>
-      <c r="B4" s="359"/>
-      <c r="C4" s="359"/>
-      <c r="D4" s="359"/>
-      <c r="E4" s="359"/>
-      <c r="F4" s="359"/>
-      <c r="G4" s="359"/>
-      <c r="H4" s="359"/>
-      <c r="I4" s="359"/>
-      <c r="J4" s="359"/>
-      <c r="K4" s="359"/>
+      <c r="A4" s="363"/>
+      <c r="B4" s="363"/>
+      <c r="C4" s="363"/>
+      <c r="D4" s="363"/>
+      <c r="E4" s="363"/>
+      <c r="F4" s="363"/>
+      <c r="G4" s="363"/>
+      <c r="H4" s="363"/>
+      <c r="I4" s="363"/>
+      <c r="J4" s="363"/>
+      <c r="K4" s="363"/>
     </row>
     <row r="5" spans="1:11" ht="45.6" thickBot="1">
       <c r="A5" s="111"/>
@@ -30881,10 +31685,10 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="424" t="s">
+      <c r="B6" s="428" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="426" t="s">
+      <c r="C6" s="430" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="282" t="s">
@@ -30900,8 +31704,8 @@
     </row>
     <row r="7" spans="1:11" ht="21">
       <c r="A7" s="13"/>
-      <c r="B7" s="425"/>
-      <c r="C7" s="427"/>
+      <c r="B7" s="429"/>
+      <c r="C7" s="431"/>
       <c r="D7" s="284" t="s">
         <v>100</v>
       </c>
@@ -31041,7 +31845,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{736167A2-EDF5-41C9-A1FA-A4E74C9A4DE0}">
   <dimension ref="B1:M58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -31053,34 +31857,34 @@
   <sheetData>
     <row r="1" spans="2:13" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:13" ht="19.05" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1583</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
-      <c r="L2" s="359"/>
-      <c r="M2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
+      <c r="L2" s="363"/>
+      <c r="M2" s="363"/>
     </row>
     <row r="3" spans="2:13" ht="19.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
-      <c r="M3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+      <c r="L3" s="363"/>
+      <c r="M3" s="363"/>
     </row>
     <row r="4" spans="2:13" ht="19.05" customHeight="1">
       <c r="B4" s="4" t="s">
@@ -31103,14 +31907,14 @@
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="2:13" ht="19.05" customHeight="1">
-      <c r="B6" s="432" t="s">
+      <c r="B6" s="436" t="s">
         <v>1728</v>
       </c>
-      <c r="C6" s="432"/>
-      <c r="D6" s="432"/>
-      <c r="E6" s="432"/>
-      <c r="F6" s="432"/>
-      <c r="G6" s="432"/>
+      <c r="C6" s="436"/>
+      <c r="D6" s="436"/>
+      <c r="E6" s="436"/>
+      <c r="F6" s="436"/>
+      <c r="G6" s="436"/>
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="2:13" ht="19.05" customHeight="1" thickBot="1">
@@ -31123,7 +31927,7 @@
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B8" s="365" t="s">
+      <c r="B8" s="368" t="s">
         <v>99</v>
       </c>
       <c r="C8" s="8" t="s">
@@ -31131,7 +31935,7 @@
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="18"/>
-      <c r="F8" s="365" t="s">
+      <c r="F8" s="368" t="s">
         <v>99</v>
       </c>
       <c r="G8" s="8" t="s">
@@ -31140,13 +31944,13 @@
       <c r="H8" s="19"/>
     </row>
     <row r="9" spans="2:13" s="7" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
-      <c r="B9" s="371"/>
+      <c r="B9" s="374"/>
       <c r="C9" s="10" t="s">
         <v>98</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
-      <c r="F9" s="371"/>
+      <c r="F9" s="374"/>
       <c r="G9" s="10" t="s">
         <v>100</v>
       </c>
@@ -31871,7 +32675,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="B1:M71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -31884,34 +32688,34 @@
   <sheetData>
     <row r="1" spans="2:13" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:13" ht="19.05" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1584</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
-      <c r="L2" s="359"/>
-      <c r="M2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
+      <c r="L2" s="363"/>
+      <c r="M2" s="363"/>
     </row>
     <row r="3" spans="2:13" ht="19.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
-      <c r="M3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+      <c r="L3" s="363"/>
+      <c r="M3" s="363"/>
     </row>
     <row r="4" spans="2:13" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -31921,10 +32725,10 @@
     <row r="5" spans="2:13" ht="19.05" customHeight="1" thickBot="1"/>
     <row r="6" spans="2:13" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="367" t="s">
+      <c r="C6" s="370" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="367" t="s">
+      <c r="D6" s="370" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="8" t="s">
@@ -31934,8 +32738,8 @@
       <c r="G6" s="13"/>
     </row>
     <row r="7" spans="2:13" s="9" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
-      <c r="C7" s="368"/>
-      <c r="D7" s="368"/>
+      <c r="C7" s="371"/>
+      <c r="D7" s="371"/>
       <c r="E7" s="16" t="s">
         <v>100</v>
       </c>
@@ -32349,7 +33153,424 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C35F84F-DE74-8F4D-A793-8E56C94260EB}">
+  <dimension ref="B1:K67"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="3.5" customWidth="1"/>
+    <col min="3" max="3" width="39.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:11" ht="19.05" customHeight="1"/>
+    <row r="2" spans="2:11" ht="19.05" customHeight="1">
+      <c r="B2" s="363" t="s">
+        <v>1758</v>
+      </c>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
+    </row>
+    <row r="3" spans="2:11" ht="19.05" customHeight="1">
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+    </row>
+    <row r="4" spans="2:11" ht="19.05" customHeight="1">
+      <c r="B4" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" ht="19.05" customHeight="1" thickBot="1"/>
+    <row r="6" spans="2:11" s="9" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B6" s="13"/>
+      <c r="C6" s="370" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" s="370" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+    </row>
+    <row r="7" spans="2:11" s="9" customFormat="1" ht="19.05" customHeight="1">
+      <c r="B7" s="13"/>
+      <c r="C7" s="371"/>
+      <c r="D7" s="371"/>
+      <c r="E7" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+    </row>
+    <row r="8" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="C8" s="113" t="s">
+        <v>1759</v>
+      </c>
+      <c r="D8" s="113" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="207">
+        <v>58</v>
+      </c>
+      <c r="G8" s="12"/>
+    </row>
+    <row r="9" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="C9" s="105"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="207"/>
+      <c r="G9" s="12"/>
+    </row>
+    <row r="10" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="C10" s="105"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="207"/>
+      <c r="G10" s="12"/>
+    </row>
+    <row r="11" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="C11" s="155"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="189"/>
+      <c r="G11" s="12"/>
+    </row>
+    <row r="12" spans="2:11" s="7" customFormat="1" ht="19.05" customHeight="1">
+      <c r="E12" s="201"/>
+      <c r="G12" s="12"/>
+    </row>
+    <row r="13" spans="2:11" ht="19.05" customHeight="1">
+      <c r="B13" s="1"/>
+      <c r="C13" s="2"/>
+      <c r="E13" s="139"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="2:11" ht="19.05" customHeight="1">
+      <c r="B14" s="1"/>
+      <c r="C14" s="2"/>
+      <c r="E14" s="139"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="2:11" ht="19.05" customHeight="1">
+      <c r="B15" s="1"/>
+      <c r="C15" s="2"/>
+      <c r="E15" s="139"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="2:11" ht="19.05" customHeight="1">
+      <c r="B16" s="1"/>
+      <c r="C16" s="2"/>
+      <c r="E16" s="139"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B17" s="1"/>
+      <c r="C17" s="2"/>
+      <c r="E17" s="139"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B18" s="1"/>
+      <c r="C18" s="2"/>
+      <c r="E18" s="139"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B19" s="1"/>
+      <c r="C19" s="2"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B20" s="1"/>
+      <c r="C20" s="2"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B21" s="1"/>
+      <c r="C21" s="2"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B22" s="1"/>
+      <c r="C22" s="2"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B23" s="1"/>
+      <c r="C23" s="2"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B24" s="1"/>
+      <c r="C24" s="2"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B25" s="1"/>
+      <c r="C25" s="2"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B26" s="1"/>
+      <c r="C26" s="2"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B27" s="1"/>
+      <c r="C27" s="2"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B28" s="1"/>
+      <c r="C28" s="2"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B29" s="1"/>
+      <c r="C29" s="2"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B30" s="1"/>
+      <c r="C30" s="2"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B31" s="1"/>
+      <c r="C31" s="2"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B32" s="1"/>
+      <c r="C32" s="2"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B33" s="1"/>
+      <c r="C33" s="2"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="2"/>
+    </row>
+    <row r="34" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B34" s="1"/>
+      <c r="C34" s="2"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B35" s="1"/>
+      <c r="C35" s="2"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="2"/>
+    </row>
+    <row r="36" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B36" s="1"/>
+      <c r="C36" s="2"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B37" s="1"/>
+      <c r="C37" s="2"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="2"/>
+    </row>
+    <row r="38" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B38" s="1"/>
+      <c r="C38" s="2"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B39" s="1"/>
+      <c r="C39" s="2"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="2"/>
+    </row>
+    <row r="40" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B40" s="1"/>
+      <c r="C40" s="2"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="2"/>
+    </row>
+    <row r="41" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B41" s="1"/>
+      <c r="C41" s="2"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="2"/>
+    </row>
+    <row r="42" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B42" s="1"/>
+      <c r="C42" s="2"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="2"/>
+    </row>
+    <row r="43" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B43" s="1"/>
+      <c r="C43" s="2"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="2"/>
+    </row>
+    <row r="44" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B44" s="1"/>
+      <c r="C44" s="2"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="2"/>
+    </row>
+    <row r="45" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B45" s="1"/>
+      <c r="C45" s="2"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="2"/>
+    </row>
+    <row r="46" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B46" s="1"/>
+      <c r="C46" s="2"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="2"/>
+    </row>
+    <row r="47" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B47" s="1"/>
+      <c r="C47" s="2"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="2"/>
+    </row>
+    <row r="48" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B48" s="1"/>
+      <c r="C48" s="2"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="2"/>
+    </row>
+    <row r="49" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B49" s="1"/>
+      <c r="C49" s="2"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="2"/>
+    </row>
+    <row r="50" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B50" s="1"/>
+      <c r="C50" s="2"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="2"/>
+    </row>
+    <row r="51" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B51" s="1"/>
+      <c r="C51" s="2"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="2"/>
+    </row>
+    <row r="52" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B52" s="1"/>
+      <c r="C52" s="2"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="2"/>
+    </row>
+    <row r="53" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B53" s="1"/>
+      <c r="C53" s="2"/>
+    </row>
+    <row r="54" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B54" s="1"/>
+      <c r="C54" s="2"/>
+    </row>
+    <row r="55" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B55" s="1"/>
+      <c r="C55" s="2"/>
+    </row>
+    <row r="56" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B56" s="1"/>
+      <c r="C56" s="2"/>
+    </row>
+    <row r="57" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B57" s="1"/>
+      <c r="C57" s="2"/>
+    </row>
+    <row r="58" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B58" s="1"/>
+      <c r="C58" s="2"/>
+    </row>
+    <row r="59" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B59" s="1"/>
+      <c r="C59" s="2"/>
+    </row>
+    <row r="60" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B60" s="3"/>
+      <c r="C60" s="2"/>
+    </row>
+    <row r="61" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B61" s="1"/>
+      <c r="C61" s="2"/>
+    </row>
+    <row r="62" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B62" s="1"/>
+      <c r="C62" s="2"/>
+    </row>
+    <row r="63" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B63" s="1"/>
+      <c r="C63" s="2"/>
+    </row>
+    <row r="64" spans="2:7" ht="19.05" customHeight="1">
+      <c r="B64" s="1"/>
+      <c r="C64" s="2"/>
+    </row>
+    <row r="65" spans="2:3" ht="19.05" customHeight="1">
+      <c r="B65" s="1"/>
+      <c r="C65" s="2"/>
+    </row>
+    <row r="66" spans="2:3" ht="19.05" customHeight="1">
+      <c r="B66" s="1"/>
+      <c r="C66" s="2"/>
+    </row>
+    <row r="67" spans="2:3" ht="19.05" customHeight="1">
+      <c r="B67" s="1"/>
+      <c r="C67" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B2:K3"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C2C75B-4790-49ED-A41E-FB92946CE1CB}">
   <dimension ref="B1:M71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -32362,34 +33583,34 @@
   <sheetData>
     <row r="1" spans="2:13" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:13" ht="19.05" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1585</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
-      <c r="L2" s="359"/>
-      <c r="M2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
+      <c r="L2" s="363"/>
+      <c r="M2" s="363"/>
     </row>
     <row r="3" spans="2:13" ht="19.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
-      <c r="M3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+      <c r="L3" s="363"/>
+      <c r="M3" s="363"/>
     </row>
     <row r="4" spans="2:13" ht="19.05" customHeight="1"/>
     <row r="5" spans="2:13" ht="19.05" customHeight="1">
@@ -32399,10 +33620,10 @@
     </row>
     <row r="6" spans="2:13" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="360" t="s">
+      <c r="C6" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="360" t="s">
+      <c r="D6" s="364" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="112" t="s">
@@ -32412,8 +33633,8 @@
       <c r="G6" s="13"/>
     </row>
     <row r="7" spans="2:13" s="9" customFormat="1" ht="19.05" customHeight="1">
-      <c r="C7" s="360"/>
-      <c r="D7" s="360"/>
+      <c r="C7" s="364"/>
+      <c r="D7" s="364"/>
       <c r="E7" s="112" t="s">
         <v>100</v>
       </c>
@@ -32964,7 +34185,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7164E7E1-0C1D-DF47-AE8C-983858CE43BE}">
   <dimension ref="B1:L68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -32981,41 +34202,41 @@
       </c>
     </row>
     <row r="2" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1588</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
-      <c r="L2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
+      <c r="L2" s="363"/>
     </row>
     <row r="3" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+      <c r="L3" s="363"/>
     </row>
     <row r="4" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="5" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="360" t="s">
+      <c r="C6" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="360" t="s">
+      <c r="D6" s="364" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="112" t="s">
@@ -33026,8 +34247,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B7" s="13"/>
-      <c r="C7" s="360"/>
-      <c r="D7" s="360"/>
+      <c r="C7" s="364"/>
+      <c r="D7" s="364"/>
       <c r="E7" s="112" t="s">
         <v>100</v>
       </c>
@@ -33394,7 +34615,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
   <dimension ref="B1:L70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -33408,32 +34629,32 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.95" customHeight="1"/>
     <row r="2" spans="2:12" ht="19.95" customHeight="1">
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="363" t="s">
         <v>1586</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
-      <c r="L2" s="359"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
+      <c r="L2" s="363"/>
     </row>
     <row r="3" spans="2:12" ht="19.95" customHeight="1">
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+      <c r="L3" s="363"/>
     </row>
     <row r="4" spans="2:12" ht="19.95" customHeight="1">
       <c r="B4" t="s">
@@ -33443,10 +34664,10 @@
     <row r="5" spans="2:12" ht="19.95" customHeight="1" thickBot="1"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19.95" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="367" t="s">
+      <c r="C6" s="370" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="367" t="s">
+      <c r="D6" s="370" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="14" t="s">
@@ -33454,10 +34675,10 @@
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
-      <c r="H6" s="367" t="s">
+      <c r="H6" s="370" t="s">
         <v>102</v>
       </c>
-      <c r="I6" s="367" t="s">
+      <c r="I6" s="370" t="s">
         <v>0</v>
       </c>
       <c r="J6" s="8" t="s">
@@ -33465,14 +34686,14 @@
       </c>
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
-      <c r="C7" s="369"/>
-      <c r="D7" s="369"/>
+      <c r="C7" s="372"/>
+      <c r="D7" s="372"/>
       <c r="E7" s="15" t="s">
         <v>98</v>
       </c>
       <c r="G7" s="20"/>
-      <c r="H7" s="368"/>
-      <c r="I7" s="368"/>
+      <c r="H7" s="371"/>
+      <c r="I7" s="371"/>
       <c r="J7" s="16" t="s">
         <v>100</v>
       </c>
@@ -33896,7 +35117,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
   <dimension ref="B1:Y81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
@@ -33922,55 +35143,55 @@
   <sheetData>
     <row r="1" spans="2:25" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:25" ht="19.05" customHeight="1">
-      <c r="B2" s="438" t="s">
+      <c r="B2" s="442" t="s">
         <v>1587</v>
       </c>
-      <c r="C2" s="438"/>
-      <c r="D2" s="438"/>
-      <c r="E2" s="438"/>
-      <c r="F2" s="438"/>
-      <c r="G2" s="438"/>
-      <c r="H2" s="438"/>
-      <c r="I2" s="438"/>
-      <c r="J2" s="438"/>
-      <c r="K2" s="438"/>
-      <c r="L2" s="438"/>
-      <c r="M2" s="438"/>
-      <c r="P2" s="437" t="s">
+      <c r="C2" s="442"/>
+      <c r="D2" s="442"/>
+      <c r="E2" s="442"/>
+      <c r="F2" s="442"/>
+      <c r="G2" s="442"/>
+      <c r="H2" s="442"/>
+      <c r="I2" s="442"/>
+      <c r="J2" s="442"/>
+      <c r="K2" s="442"/>
+      <c r="L2" s="442"/>
+      <c r="M2" s="442"/>
+      <c r="P2" s="441" t="s">
         <v>1587</v>
       </c>
-      <c r="Q2" s="437"/>
-      <c r="R2" s="437"/>
-      <c r="S2" s="437"/>
-      <c r="T2" s="437"/>
-      <c r="U2" s="437"/>
-      <c r="V2" s="437"/>
-      <c r="W2" s="437"/>
-      <c r="X2" s="437"/>
+      <c r="Q2" s="441"/>
+      <c r="R2" s="441"/>
+      <c r="S2" s="441"/>
+      <c r="T2" s="441"/>
+      <c r="U2" s="441"/>
+      <c r="V2" s="441"/>
+      <c r="W2" s="441"/>
+      <c r="X2" s="441"/>
       <c r="Y2" s="47"/>
     </row>
     <row r="3" spans="2:25" ht="19.05" customHeight="1">
-      <c r="B3" s="438"/>
-      <c r="C3" s="438"/>
-      <c r="D3" s="438"/>
-      <c r="E3" s="438"/>
-      <c r="F3" s="438"/>
-      <c r="G3" s="438"/>
-      <c r="H3" s="438"/>
-      <c r="I3" s="438"/>
-      <c r="J3" s="438"/>
-      <c r="K3" s="438"/>
-      <c r="L3" s="438"/>
-      <c r="M3" s="438"/>
-      <c r="P3" s="437"/>
-      <c r="Q3" s="437"/>
-      <c r="R3" s="437"/>
-      <c r="S3" s="437"/>
-      <c r="T3" s="437"/>
-      <c r="U3" s="437"/>
-      <c r="V3" s="437"/>
-      <c r="W3" s="437"/>
-      <c r="X3" s="437"/>
+      <c r="B3" s="442"/>
+      <c r="C3" s="442"/>
+      <c r="D3" s="442"/>
+      <c r="E3" s="442"/>
+      <c r="F3" s="442"/>
+      <c r="G3" s="442"/>
+      <c r="H3" s="442"/>
+      <c r="I3" s="442"/>
+      <c r="J3" s="442"/>
+      <c r="K3" s="442"/>
+      <c r="L3" s="442"/>
+      <c r="M3" s="442"/>
+      <c r="P3" s="441"/>
+      <c r="Q3" s="441"/>
+      <c r="R3" s="441"/>
+      <c r="S3" s="441"/>
+      <c r="T3" s="441"/>
+      <c r="U3" s="441"/>
+      <c r="V3" s="441"/>
+      <c r="W3" s="441"/>
+      <c r="X3" s="441"/>
       <c r="Y3" s="47"/>
     </row>
     <row r="4" spans="2:25" ht="19.05" customHeight="1">
@@ -33980,20 +35201,20 @@
     </row>
     <row r="5" spans="2:25" ht="19.05" customHeight="1" thickBot="1"/>
     <row r="6" spans="2:25" s="9" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B6" s="367" t="s">
+      <c r="B6" s="370" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="E6" s="367" t="s">
+      <c r="E6" s="370" t="s">
         <v>99</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>101</v>
       </c>
       <c r="G6" s="13"/>
-      <c r="H6" s="374" t="s">
+      <c r="H6" s="377" t="s">
         <v>99</v>
       </c>
       <c r="I6" s="319" t="s">
@@ -34001,16 +35222,16 @@
       </c>
     </row>
     <row r="7" spans="2:25" s="9" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
-      <c r="B7" s="369"/>
+      <c r="B7" s="372"/>
       <c r="C7" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E7" s="369"/>
+      <c r="E7" s="372"/>
       <c r="F7" s="15" t="s">
         <v>98</v>
       </c>
       <c r="G7" s="20"/>
-      <c r="H7" s="415"/>
+      <c r="H7" s="419"/>
       <c r="I7" s="320" t="s">
         <v>100</v>
       </c>
@@ -34035,11 +35256,11 @@
       <c r="I8" s="87">
         <v>5.1866317866813541</v>
       </c>
-      <c r="P8" s="418" t="s">
+      <c r="P8" s="422" t="s">
         <v>82</v>
       </c>
-      <c r="Q8" s="419"/>
-      <c r="R8" s="420"/>
+      <c r="Q8" s="423"/>
+      <c r="R8" s="424"/>
     </row>
     <row r="9" spans="2:25" s="7" customFormat="1" ht="19.05" customHeight="1" thickBot="1">
       <c r="B9" s="314">
@@ -34061,9 +35282,9 @@
       <c r="I9" s="87">
         <v>5.7095231538849882</v>
       </c>
-      <c r="P9" s="434"/>
-      <c r="Q9" s="435"/>
-      <c r="R9" s="436"/>
+      <c r="P9" s="438"/>
+      <c r="Q9" s="439"/>
+      <c r="R9" s="440"/>
     </row>
     <row r="10" spans="2:25" s="7" customFormat="1" ht="19.05" customHeight="1">
       <c r="B10" s="315">
@@ -34115,10 +35336,10 @@
       <c r="I11" s="87">
         <v>7.9196512001468626</v>
       </c>
-      <c r="P11" s="433" t="s">
+      <c r="P11" s="437" t="s">
         <v>440</v>
       </c>
-      <c r="Q11" s="433"/>
+      <c r="Q11" s="437"/>
       <c r="R11" s="189">
         <v>10.080053500127852</v>
       </c>
@@ -34143,10 +35364,10 @@
       <c r="I12" s="87">
         <v>5.7824847400064252</v>
       </c>
-      <c r="P12" s="433" t="s">
+      <c r="P12" s="437" t="s">
         <v>441</v>
       </c>
-      <c r="Q12" s="433"/>
+      <c r="Q12" s="437"/>
       <c r="R12" s="189">
         <v>8.0737987057689669</v>
       </c>
@@ -34171,10 +35392,10 @@
       <c r="I13" s="87">
         <v>6.0682509523153891</v>
       </c>
-      <c r="P13" s="433" t="s">
+      <c r="P13" s="437" t="s">
         <v>442</v>
       </c>
-      <c r="Q13" s="433"/>
+      <c r="Q13" s="437"/>
       <c r="R13" s="189">
         <v>7.9935485139946119</v>
       </c>
@@ -34199,10 +35420,10 @@
       <c r="I14" s="87">
         <v>6.1868135297627243</v>
       </c>
-      <c r="P14" s="433" t="s">
+      <c r="P14" s="437" t="s">
         <v>443</v>
       </c>
-      <c r="Q14" s="433"/>
+      <c r="Q14" s="437"/>
       <c r="R14" s="189">
         <v>7.3515469797997683</v>
       </c>
@@ -35179,38 +36400,38 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14">
-      <c r="A2" s="359" t="s">
+      <c r="A2" s="363" t="s">
         <v>1518</v>
       </c>
-      <c r="B2" s="359"/>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
-      <c r="L2" s="359"/>
-      <c r="M2" s="359"/>
-      <c r="N2" s="359"/>
+      <c r="B2" s="363"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
+      <c r="L2" s="363"/>
+      <c r="M2" s="363"/>
+      <c r="N2" s="363"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="359"/>
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
-      <c r="M3" s="359"/>
-      <c r="N3" s="359"/>
+      <c r="A3" s="363"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+      <c r="L3" s="363"/>
+      <c r="M3" s="363"/>
+      <c r="N3" s="363"/>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
@@ -35219,35 +36440,35 @@
     </row>
     <row r="5" spans="1:14" ht="16.2" thickBot="1"/>
     <row r="6" spans="1:14" ht="21">
-      <c r="A6" s="367" t="s">
+      <c r="A6" s="370" t="s">
         <v>99</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>101</v>
       </c>
       <c r="C6" s="9"/>
-      <c r="D6" s="367" t="s">
+      <c r="D6" s="370" t="s">
         <v>99</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>101</v>
       </c>
       <c r="F6" s="96"/>
-      <c r="G6" s="367" t="s">
+      <c r="G6" s="370" t="s">
         <v>99</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>101</v>
       </c>
       <c r="I6" s="9"/>
-      <c r="J6" s="367" t="s">
+      <c r="J6" s="370" t="s">
         <v>99</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>101</v>
       </c>
       <c r="L6" s="9"/>
-      <c r="M6" s="367" t="s">
+      <c r="M6" s="370" t="s">
         <v>99</v>
       </c>
       <c r="N6" s="43" t="s">
@@ -35255,27 +36476,27 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="21.6" thickBot="1">
-      <c r="A7" s="369"/>
+      <c r="A7" s="372"/>
       <c r="B7" s="10" t="s">
         <v>98</v>
       </c>
       <c r="C7" s="9"/>
-      <c r="D7" s="369"/>
+      <c r="D7" s="372"/>
       <c r="E7" s="10" t="s">
         <v>98</v>
       </c>
       <c r="F7" s="96"/>
-      <c r="G7" s="369"/>
+      <c r="G7" s="372"/>
       <c r="H7" s="10" t="s">
         <v>98</v>
       </c>
       <c r="I7" s="9"/>
-      <c r="J7" s="369"/>
+      <c r="J7" s="372"/>
       <c r="K7" s="10" t="s">
         <v>100</v>
       </c>
       <c r="L7" s="9"/>
-      <c r="M7" s="369"/>
+      <c r="M7" s="372"/>
       <c r="N7" s="44" t="s">
         <v>100</v>
       </c>
@@ -37535,13 +38756,13 @@
     <row r="78" spans="1:14" ht="21">
       <c r="D78" s="136"/>
       <c r="E78" s="209"/>
-      <c r="J78" s="370" t="s">
+      <c r="J78" s="373" t="s">
         <v>731</v>
       </c>
-      <c r="K78" s="370"/>
-      <c r="L78" s="370"/>
-      <c r="M78" s="370"/>
-      <c r="N78" s="370"/>
+      <c r="K78" s="373"/>
+      <c r="L78" s="373"/>
+      <c r="M78" s="373"/>
+      <c r="N78" s="373"/>
     </row>
     <row r="79" spans="1:14">
       <c r="D79" s="136"/>
@@ -37640,45 +38861,45 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A2" s="359" t="s">
+      <c r="A2" s="363" t="s">
         <v>1519</v>
       </c>
-      <c r="B2" s="359"/>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
+      <c r="B2" s="363"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
+      <c r="I2" s="363"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="363"/>
     </row>
     <row r="3" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A3" s="359"/>
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
+      <c r="A3" s="363"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
     </row>
     <row r="4" spans="1:11" ht="16.95" customHeight="1">
-      <c r="A4" s="359"/>
-      <c r="B4" s="359"/>
-      <c r="C4" s="359"/>
-      <c r="D4" s="359"/>
-      <c r="E4" s="359"/>
-      <c r="F4" s="359"/>
-      <c r="G4" s="359"/>
-      <c r="H4" s="359"/>
-      <c r="I4" s="359"/>
-      <c r="J4" s="359"/>
-      <c r="K4" s="359"/>
+      <c r="A4" s="363"/>
+      <c r="B4" s="363"/>
+      <c r="C4" s="363"/>
+      <c r="D4" s="363"/>
+      <c r="E4" s="363"/>
+      <c r="F4" s="363"/>
+      <c r="G4" s="363"/>
+      <c r="H4" s="363"/>
+      <c r="I4" s="363"/>
+      <c r="J4" s="363"/>
+      <c r="K4" s="363"/>
     </row>
     <row r="5" spans="1:11" ht="16.95" customHeight="1" thickBot="1">
       <c r="A5" s="111"/>
@@ -37695,10 +38916,10 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="365" t="s">
+      <c r="B6" s="368" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="367" t="s">
+      <c r="C6" s="370" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="14" t="s">
@@ -37714,8 +38935,8 @@
     </row>
     <row r="7" spans="1:11" ht="21.6" thickBot="1">
       <c r="A7" s="13"/>
-      <c r="B7" s="371"/>
-      <c r="C7" s="369"/>
+      <c r="B7" s="374"/>
+      <c r="C7" s="372"/>
       <c r="D7" s="15" t="s">
         <v>100</v>
       </c>
@@ -37815,25 +39036,25 @@
       </c>
     </row>
     <row r="2" spans="2:17" ht="19.05" customHeight="1">
-      <c r="B2" s="362" t="s">
+      <c r="B2" s="365" t="s">
         <v>1520</v>
       </c>
-      <c r="C2" s="362"/>
-      <c r="D2" s="362"/>
-      <c r="E2" s="362"/>
-      <c r="F2" s="362"/>
-      <c r="G2" s="362"/>
-      <c r="H2" s="362"/>
+      <c r="C2" s="365"/>
+      <c r="D2" s="365"/>
+      <c r="E2" s="365"/>
+      <c r="F2" s="365"/>
+      <c r="G2" s="365"/>
+      <c r="H2" s="365"/>
       <c r="I2" s="38"/>
     </row>
     <row r="3" spans="2:17" ht="19.05" customHeight="1">
-      <c r="B3" s="362"/>
-      <c r="C3" s="362"/>
-      <c r="D3" s="362"/>
-      <c r="E3" s="362"/>
-      <c r="F3" s="362"/>
-      <c r="G3" s="362"/>
-      <c r="H3" s="362"/>
+      <c r="B3" s="365"/>
+      <c r="C3" s="365"/>
+      <c r="D3" s="365"/>
+      <c r="E3" s="365"/>
+      <c r="F3" s="365"/>
+      <c r="G3" s="365"/>
+      <c r="H3" s="365"/>
       <c r="I3" s="38"/>
     </row>
     <row r="4" spans="2:17" ht="19.05" customHeight="1"/>
@@ -37843,10 +39064,10 @@
       <c r="Q5" s="41"/>
     </row>
     <row r="6" spans="2:17" ht="19.05" customHeight="1">
-      <c r="B6" s="372" t="s">
+      <c r="B6" s="375" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="372" t="s">
+      <c r="C6" s="375" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="34" t="s">
@@ -37864,8 +39085,8 @@
       <c r="Q6" s="41"/>
     </row>
     <row r="7" spans="2:17" ht="19.05" customHeight="1" thickBot="1">
-      <c r="B7" s="373"/>
-      <c r="C7" s="373"/>
+      <c r="B7" s="376"/>
+      <c r="C7" s="376"/>
       <c r="D7" s="36" t="s">
         <v>104</v>
       </c>
@@ -37913,9 +39134,9 @@
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="32"/>
-      <c r="G9" s="364"/>
-      <c r="H9" s="364"/>
-      <c r="I9" s="364"/>
+      <c r="G9" s="367"/>
+      <c r="H9" s="367"/>
+      <c r="I9" s="367"/>
       <c r="J9" s="32"/>
       <c r="L9" s="31"/>
       <c r="M9" s="32"/>
@@ -37929,9 +39150,9 @@
       <c r="D10" s="53"/>
       <c r="E10" s="31"/>
       <c r="F10" s="32"/>
-      <c r="G10" s="364"/>
-      <c r="H10" s="364"/>
-      <c r="I10" s="364"/>
+      <c r="G10" s="367"/>
+      <c r="H10" s="367"/>
+      <c r="I10" s="367"/>
       <c r="J10" s="32"/>
       <c r="L10" s="31"/>
       <c r="M10" s="32"/>
@@ -38354,25 +39575,25 @@
       <c r="A1" s="333" t="s">
         <v>1701</v>
       </c>
-      <c r="B1" s="362" t="s">
+      <c r="B1" s="365" t="s">
         <v>1618</v>
       </c>
-      <c r="C1" s="362"/>
-      <c r="D1" s="362"/>
-      <c r="E1" s="362"/>
-      <c r="F1" s="362"/>
-      <c r="G1" s="362"/>
-      <c r="H1" s="362"/>
+      <c r="C1" s="365"/>
+      <c r="D1" s="365"/>
+      <c r="E1" s="365"/>
+      <c r="F1" s="365"/>
+      <c r="G1" s="365"/>
+      <c r="H1" s="365"/>
       <c r="I1" s="38"/>
     </row>
     <row r="2" spans="1:17" s="30" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B2" s="362"/>
-      <c r="C2" s="362"/>
-      <c r="D2" s="362"/>
-      <c r="E2" s="362"/>
-      <c r="F2" s="362"/>
-      <c r="G2" s="362"/>
-      <c r="H2" s="362"/>
+      <c r="B2" s="365"/>
+      <c r="C2" s="365"/>
+      <c r="D2" s="365"/>
+      <c r="E2" s="365"/>
+      <c r="F2" s="365"/>
+      <c r="G2" s="365"/>
+      <c r="H2" s="365"/>
       <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:17" s="30" customFormat="1" ht="19.05" customHeight="1"/>
@@ -38382,10 +39603,10 @@
       <c r="Q4" s="41"/>
     </row>
     <row r="5" spans="1:17" s="30" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B5" s="363" t="s">
+      <c r="B5" s="366" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="363" t="s">
+      <c r="C5" s="366" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="106" t="s">
@@ -38403,8 +39624,8 @@
       <c r="Q5" s="41"/>
     </row>
     <row r="6" spans="1:17" s="30" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B6" s="363"/>
-      <c r="C6" s="363"/>
+      <c r="B6" s="366"/>
+      <c r="C6" s="366"/>
       <c r="D6" s="106" t="s">
         <v>104</v>
       </c>
@@ -38452,9 +39673,9 @@
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="32"/>
-      <c r="G8" s="364"/>
-      <c r="H8" s="364"/>
-      <c r="I8" s="364"/>
+      <c r="G8" s="367"/>
+      <c r="H8" s="367"/>
+      <c r="I8" s="367"/>
       <c r="J8" s="32"/>
       <c r="L8" s="31"/>
       <c r="M8" s="32"/>
@@ -38474,9 +39695,9 @@
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="32"/>
-      <c r="G9" s="364"/>
-      <c r="H9" s="364"/>
-      <c r="I9" s="364"/>
+      <c r="G9" s="367"/>
+      <c r="H9" s="367"/>
+      <c r="I9" s="367"/>
       <c r="J9" s="32"/>
       <c r="L9" s="31"/>
       <c r="M9" s="32"/>

--- a/public/docs/tarifa-italgres.xlsx
+++ b/public/docs/tarifa-italgres.xlsx
@@ -8078,12 +8078,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="49" fillId="4" borderId="0" xfId="246" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -8092,6 +8086,12 @@
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="271" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8284,6 +8284,12 @@
     <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="60" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="54" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8293,12 +8299,6 @@
     </xf>
     <xf numFmtId="0" fontId="54" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="313">
@@ -8967,25 +8967,25 @@
       <c r="A1" s="333" t="s">
         <v>1701</v>
       </c>
-      <c r="B1" s="365" t="s">
+      <c r="B1" s="363" t="s">
         <v>1616</v>
       </c>
-      <c r="C1" s="365"/>
-      <c r="D1" s="365"/>
-      <c r="E1" s="365"/>
-      <c r="F1" s="365"/>
-      <c r="G1" s="365"/>
-      <c r="H1" s="365"/>
+      <c r="C1" s="363"/>
+      <c r="D1" s="363"/>
+      <c r="E1" s="363"/>
+      <c r="F1" s="363"/>
+      <c r="G1" s="363"/>
+      <c r="H1" s="363"/>
       <c r="I1" s="38"/>
     </row>
     <row r="2" spans="1:17" s="30" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B2" s="365"/>
-      <c r="C2" s="365"/>
-      <c r="D2" s="365"/>
-      <c r="E2" s="365"/>
-      <c r="F2" s="365"/>
-      <c r="G2" s="365"/>
-      <c r="H2" s="365"/>
+      <c r="B2" s="363"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
       <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:17" s="30" customFormat="1" ht="19.05" customHeight="1">
@@ -8999,10 +8999,10 @@
       <c r="Q4" s="41"/>
     </row>
     <row r="5" spans="1:17" s="30" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B5" s="366" t="s">
+      <c r="B5" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="366" t="s">
+      <c r="C5" s="364" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="106" t="s">
@@ -9020,8 +9020,8 @@
       <c r="Q5" s="41"/>
     </row>
     <row r="6" spans="1:17" s="30" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B6" s="366"/>
-      <c r="C6" s="366"/>
+      <c r="B6" s="364"/>
+      <c r="C6" s="364"/>
       <c r="D6" s="106" t="s">
         <v>104</v>
       </c>
@@ -9069,9 +9069,9 @@
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="32"/>
-      <c r="G8" s="367"/>
-      <c r="H8" s="367"/>
-      <c r="I8" s="367"/>
+      <c r="G8" s="365"/>
+      <c r="H8" s="365"/>
+      <c r="I8" s="365"/>
       <c r="J8" s="32"/>
       <c r="L8" s="31"/>
       <c r="M8" s="32"/>
@@ -9085,9 +9085,9 @@
       <c r="D9" s="189"/>
       <c r="E9" s="31"/>
       <c r="F9" s="32"/>
-      <c r="G9" s="367"/>
-      <c r="H9" s="367"/>
-      <c r="I9" s="367"/>
+      <c r="G9" s="365"/>
+      <c r="H9" s="365"/>
+      <c r="I9" s="365"/>
       <c r="J9" s="32"/>
       <c r="L9" s="31"/>
       <c r="M9" s="32"/>
@@ -9120,32 +9120,32 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1707</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
-      <c r="L2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
+      <c r="L2" s="366"/>
     </row>
     <row r="3" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
-      <c r="L3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
+      <c r="L3" s="366"/>
     </row>
     <row r="4" spans="2:12" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -9575,45 +9575,45 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A2" s="363" t="s">
+      <c r="A2" s="366" t="s">
         <v>1516</v>
       </c>
-      <c r="B2" s="363"/>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
+      <c r="B2" s="366"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
     </row>
     <row r="3" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A3" s="363"/>
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
+      <c r="A3" s="366"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
     </row>
     <row r="4" spans="1:11" ht="16.95" customHeight="1">
-      <c r="A4" s="363"/>
-      <c r="B4" s="363"/>
-      <c r="C4" s="363"/>
-      <c r="D4" s="363"/>
-      <c r="E4" s="363"/>
-      <c r="F4" s="363"/>
-      <c r="G4" s="363"/>
-      <c r="H4" s="363"/>
-      <c r="I4" s="363"/>
-      <c r="J4" s="363"/>
-      <c r="K4" s="363"/>
+      <c r="A4" s="366"/>
+      <c r="B4" s="366"/>
+      <c r="C4" s="366"/>
+      <c r="D4" s="366"/>
+      <c r="E4" s="366"/>
+      <c r="F4" s="366"/>
+      <c r="G4" s="366"/>
+      <c r="H4" s="366"/>
+      <c r="I4" s="366"/>
+      <c r="J4" s="366"/>
+      <c r="K4" s="366"/>
     </row>
     <row r="5" spans="1:11" ht="16.95" customHeight="1">
       <c r="A5" s="111"/>
@@ -9630,10 +9630,10 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="364" t="s">
+      <c r="B6" s="367" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="364" t="s">
+      <c r="C6" s="367" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="112" t="s">
@@ -9651,8 +9651,8 @@
     </row>
     <row r="7" spans="1:11" ht="21">
       <c r="A7" s="13"/>
-      <c r="B7" s="364"/>
-      <c r="C7" s="364"/>
+      <c r="B7" s="367"/>
+      <c r="C7" s="367"/>
       <c r="D7" s="112" t="s">
         <v>100</v>
       </c>
@@ -9764,32 +9764,32 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1524</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
-      <c r="L2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
+      <c r="L2" s="366"/>
     </row>
     <row r="3" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
-      <c r="L3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
+      <c r="L3" s="366"/>
     </row>
     <row r="4" spans="2:12" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -10695,24 +10695,24 @@
   <sheetData>
     <row r="1" spans="2:10" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:10" ht="19.05" customHeight="1">
-      <c r="B2" s="365" t="s">
+      <c r="B2" s="363" t="s">
         <v>1530</v>
       </c>
-      <c r="C2" s="365"/>
-      <c r="D2" s="365"/>
-      <c r="E2" s="365"/>
-      <c r="F2" s="365"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
       <c r="G2" s="38"/>
       <c r="H2" s="38"/>
       <c r="I2" s="38"/>
       <c r="J2" s="38"/>
     </row>
     <row r="3" spans="2:10" ht="19.05" customHeight="1">
-      <c r="B3" s="365"/>
-      <c r="C3" s="365"/>
-      <c r="D3" s="365"/>
-      <c r="E3" s="365"/>
-      <c r="F3" s="365"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
       <c r="G3" s="38"/>
       <c r="H3" s="38"/>
       <c r="I3" s="38"/>
@@ -11747,10 +11747,10 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="364" t="s">
+      <c r="B6" s="367" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="364" t="s">
+      <c r="C6" s="367" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="270" t="s">
@@ -12077,32 +12077,32 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1532</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
-      <c r="L2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
+      <c r="L2" s="366"/>
     </row>
     <row r="3" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
-      <c r="L3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
+      <c r="L3" s="366"/>
     </row>
     <row r="4" spans="2:12" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -12112,10 +12112,10 @@
     <row r="5" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="364" t="s">
+      <c r="C6" s="367" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="364" t="s">
+      <c r="D6" s="367" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="112" t="s">
@@ -12126,8 +12126,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B7" s="13"/>
-      <c r="C7" s="364"/>
-      <c r="D7" s="364"/>
+      <c r="C7" s="367"/>
+      <c r="D7" s="367"/>
       <c r="E7" s="112" t="s">
         <v>100</v>
       </c>
@@ -12653,32 +12653,32 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1533</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
-      <c r="L2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
+      <c r="L2" s="366"/>
     </row>
     <row r="3" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
-      <c r="L3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
+      <c r="L3" s="366"/>
     </row>
     <row r="4" spans="2:12" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -13235,10 +13235,10 @@
     </row>
     <row r="6" spans="1:12" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="364" t="s">
+      <c r="B6" s="367" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="364" t="s">
+      <c r="C6" s="367" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="149" t="s">
@@ -13944,32 +13944,32 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1589</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
-      <c r="L2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
+      <c r="L2" s="366"/>
     </row>
     <row r="3" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
-      <c r="L3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
+      <c r="L3" s="366"/>
     </row>
     <row r="4" spans="2:12" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -13979,10 +13979,10 @@
     <row r="5" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="364" t="s">
+      <c r="C6" s="367" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="364" t="s">
+      <c r="D6" s="367" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="112" t="s">
@@ -13993,8 +13993,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B7" s="13"/>
-      <c r="C7" s="364"/>
-      <c r="D7" s="364"/>
+      <c r="C7" s="367"/>
+      <c r="D7" s="367"/>
       <c r="E7" s="112" t="s">
         <v>100</v>
       </c>
@@ -14466,45 +14466,45 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A2" s="363" t="s">
+      <c r="A2" s="366" t="s">
         <v>1515</v>
       </c>
-      <c r="B2" s="363"/>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
+      <c r="B2" s="366"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
     </row>
     <row r="3" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A3" s="363"/>
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
+      <c r="A3" s="366"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
     </row>
     <row r="4" spans="1:11" ht="16.95" customHeight="1">
-      <c r="A4" s="363"/>
-      <c r="B4" s="363"/>
-      <c r="C4" s="363"/>
-      <c r="D4" s="363"/>
-      <c r="E4" s="363"/>
-      <c r="F4" s="363"/>
-      <c r="G4" s="363"/>
-      <c r="H4" s="363"/>
-      <c r="I4" s="363"/>
-      <c r="J4" s="363"/>
-      <c r="K4" s="363"/>
+      <c r="A4" s="366"/>
+      <c r="B4" s="366"/>
+      <c r="C4" s="366"/>
+      <c r="D4" s="366"/>
+      <c r="E4" s="366"/>
+      <c r="F4" s="366"/>
+      <c r="G4" s="366"/>
+      <c r="H4" s="366"/>
+      <c r="I4" s="366"/>
+      <c r="J4" s="366"/>
+      <c r="K4" s="366"/>
     </row>
     <row r="5" spans="1:11" ht="16.95" customHeight="1">
       <c r="A5" s="111"/>
@@ -14521,10 +14521,10 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="364" t="s">
+      <c r="B6" s="367" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="364" t="s">
+      <c r="C6" s="367" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="112" t="s">
@@ -14542,8 +14542,8 @@
     </row>
     <row r="7" spans="1:11" ht="21">
       <c r="A7" s="13"/>
-      <c r="B7" s="364"/>
-      <c r="C7" s="364"/>
+      <c r="B7" s="367"/>
+      <c r="C7" s="367"/>
       <c r="D7" s="112" t="s">
         <v>100</v>
       </c>
@@ -14841,32 +14841,32 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1741</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
-      <c r="L2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
+      <c r="L2" s="366"/>
     </row>
     <row r="3" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
-      <c r="L3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
+      <c r="L3" s="366"/>
     </row>
     <row r="4" spans="2:12" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -14876,10 +14876,10 @@
     <row r="5" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="364" t="s">
+      <c r="C6" s="367" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="364" t="s">
+      <c r="D6" s="367" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="112" t="s">
@@ -16441,41 +16441,41 @@
       </c>
     </row>
     <row r="2" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1134</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
-      <c r="L2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
+      <c r="L2" s="366"/>
     </row>
     <row r="3" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
-      <c r="L3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
+      <c r="L3" s="366"/>
     </row>
     <row r="4" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="5" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="364" t="s">
+      <c r="C6" s="367" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="364" t="s">
+      <c r="D6" s="367" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="112" t="s">
@@ -16968,10 +16968,10 @@
     </row>
     <row r="5" spans="1:11" ht="21">
       <c r="A5" s="13"/>
-      <c r="B5" s="364" t="s">
+      <c r="B5" s="367" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="364" t="s">
+      <c r="C5" s="367" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="112" t="s">
@@ -16987,8 +16987,8 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="364"/>
-      <c r="C6" s="364"/>
+      <c r="B6" s="367"/>
+      <c r="C6" s="367"/>
       <c r="D6" s="112" t="s">
         <v>100</v>
       </c>
@@ -17176,10 +17176,10 @@
     </row>
     <row r="7" spans="1:11" ht="21">
       <c r="A7" s="13"/>
-      <c r="B7" s="364" t="s">
+      <c r="B7" s="367" t="s">
         <v>102</v>
       </c>
-      <c r="C7" s="364" t="s">
+      <c r="C7" s="367" t="s">
         <v>0</v>
       </c>
       <c r="D7" s="112" t="s">
@@ -17500,10 +17500,10 @@
     </row>
     <row r="7" spans="1:11" ht="21">
       <c r="A7" s="13"/>
-      <c r="B7" s="364" t="s">
+      <c r="B7" s="367" t="s">
         <v>102</v>
       </c>
-      <c r="C7" s="364" t="s">
+      <c r="C7" s="367" t="s">
         <v>0</v>
       </c>
       <c r="D7" s="112" t="s">
@@ -17519,8 +17519,8 @@
     </row>
     <row r="8" spans="1:11" ht="21">
       <c r="A8" s="13"/>
-      <c r="B8" s="364"/>
-      <c r="C8" s="364"/>
+      <c r="B8" s="367"/>
+      <c r="C8" s="367"/>
       <c r="D8" s="112" t="s">
         <v>100</v>
       </c>
@@ -17746,32 +17746,32 @@
   <sheetData>
     <row r="1" spans="2:16" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:16" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1553</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
-      <c r="L2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
+      <c r="L2" s="366"/>
     </row>
     <row r="3" spans="2:16" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
-      <c r="L3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
+      <c r="L3" s="366"/>
     </row>
     <row r="4" spans="2:16" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -17781,10 +17781,10 @@
     <row r="5" spans="2:16" ht="19.05" customHeight="1"/>
     <row r="6" spans="2:16" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="364" t="s">
+      <c r="C6" s="367" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="364" t="s">
+      <c r="D6" s="367" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="120" t="s">
@@ -18322,41 +18322,41 @@
       </c>
     </row>
     <row r="2" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1557</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
-      <c r="L2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
+      <c r="L2" s="366"/>
     </row>
     <row r="3" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
-      <c r="L3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
+      <c r="L3" s="366"/>
     </row>
     <row r="4" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="5" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="364" t="s">
+      <c r="C6" s="367" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="364" t="s">
+      <c r="D6" s="367" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="112" t="s">
@@ -18767,41 +18767,41 @@
       </c>
     </row>
     <row r="2" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1558</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
-      <c r="L2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
+      <c r="L2" s="366"/>
     </row>
     <row r="3" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
-      <c r="L3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
+      <c r="L3" s="366"/>
     </row>
     <row r="4" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="5" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="364" t="s">
+      <c r="C6" s="367" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="364" t="s">
+      <c r="D6" s="367" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="112" t="s">
@@ -18812,8 +18812,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B7" s="13"/>
-      <c r="C7" s="364"/>
-      <c r="D7" s="364"/>
+      <c r="C7" s="367"/>
+      <c r="D7" s="367"/>
       <c r="E7" s="112" t="s">
         <v>100</v>
       </c>
@@ -19196,10 +19196,10 @@
     </row>
     <row r="5" spans="1:11" ht="21">
       <c r="A5" s="13"/>
-      <c r="B5" s="364" t="s">
+      <c r="B5" s="367" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="364" t="s">
+      <c r="C5" s="367" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="112" t="s">
@@ -19217,8 +19217,8 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="364"/>
-      <c r="C6" s="364"/>
+      <c r="B6" s="367"/>
+      <c r="C6" s="367"/>
       <c r="D6" s="112" t="s">
         <v>100</v>
       </c>
@@ -19380,45 +19380,45 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A2" s="363" t="s">
+      <c r="A2" s="366" t="s">
         <v>1517</v>
       </c>
-      <c r="B2" s="363"/>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
+      <c r="B2" s="366"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
     </row>
     <row r="3" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A3" s="363"/>
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
+      <c r="A3" s="366"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
     </row>
     <row r="4" spans="1:11" ht="16.95" customHeight="1">
-      <c r="A4" s="363"/>
-      <c r="B4" s="363"/>
-      <c r="C4" s="363"/>
-      <c r="D4" s="363"/>
-      <c r="E4" s="363"/>
-      <c r="F4" s="363"/>
-      <c r="G4" s="363"/>
-      <c r="H4" s="363"/>
-      <c r="I4" s="363"/>
-      <c r="J4" s="363"/>
-      <c r="K4" s="363"/>
+      <c r="A4" s="366"/>
+      <c r="B4" s="366"/>
+      <c r="C4" s="366"/>
+      <c r="D4" s="366"/>
+      <c r="E4" s="366"/>
+      <c r="F4" s="366"/>
+      <c r="G4" s="366"/>
+      <c r="H4" s="366"/>
+      <c r="I4" s="366"/>
+      <c r="J4" s="366"/>
+      <c r="K4" s="366"/>
     </row>
     <row r="5" spans="1:11" ht="16.95" customHeight="1" thickBot="1">
       <c r="A5" s="111"/>
@@ -19636,13 +19636,13 @@
       <c r="E5" s="296"/>
     </row>
     <row r="6" spans="2:10" ht="19.05" customHeight="1">
-      <c r="B6" s="366" t="s">
+      <c r="B6" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="366" t="s">
+      <c r="C6" s="364" t="s">
         <v>106</v>
       </c>
-      <c r="D6" s="366" t="s">
+      <c r="D6" s="364" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="106" t="s">
@@ -20574,11 +20574,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="25.5" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1565</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
       <c r="E2" s="48"/>
       <c r="F2" s="48"/>
       <c r="G2" s="48"/>
@@ -20589,9 +20589,9 @@
       <c r="L2" s="48"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
       <c r="E3" s="48"/>
       <c r="F3" s="48"/>
       <c r="G3" s="48"/>
@@ -21226,7 +21226,7 @@
     <row r="7" spans="1:11" ht="21">
       <c r="A7" s="13"/>
       <c r="B7" s="419"/>
-      <c r="C7" s="364"/>
+      <c r="C7" s="367"/>
       <c r="D7" s="168" t="s">
         <v>100</v>
       </c>
@@ -21468,10 +21468,10 @@
     <row r="6" spans="1:12" ht="21">
       <c r="A6" s="9"/>
       <c r="B6" s="13"/>
-      <c r="C6" s="364" t="s">
+      <c r="C6" s="367" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="364" t="s">
+      <c r="D6" s="367" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="112" t="s">
@@ -21488,8 +21488,8 @@
     <row r="7" spans="1:12" ht="21">
       <c r="A7" s="9"/>
       <c r="B7" s="13"/>
-      <c r="C7" s="364"/>
-      <c r="D7" s="364"/>
+      <c r="C7" s="367"/>
+      <c r="D7" s="367"/>
       <c r="E7" s="112" t="s">
         <v>100</v>
       </c>
@@ -21647,13 +21647,13 @@
       <c r="E5" s="296"/>
     </row>
     <row r="6" spans="2:5" ht="19.05" customHeight="1">
-      <c r="B6" s="366" t="s">
+      <c r="B6" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="366" t="s">
+      <c r="C6" s="364" t="s">
         <v>106</v>
       </c>
-      <c r="D6" s="366" t="s">
+      <c r="D6" s="364" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="106" t="s">
@@ -21661,9 +21661,9 @@
       </c>
     </row>
     <row r="7" spans="2:5" ht="19.05" customHeight="1">
-      <c r="B7" s="366"/>
-      <c r="C7" s="366"/>
-      <c r="D7" s="366"/>
+      <c r="B7" s="364"/>
+      <c r="C7" s="364"/>
+      <c r="D7" s="364"/>
       <c r="E7" s="106" t="s">
         <v>100</v>
       </c>
@@ -21892,32 +21892,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="363" t="s">
+      <c r="A1" s="366" t="s">
         <v>1606</v>
       </c>
-      <c r="B1" s="363"/>
-      <c r="C1" s="363"/>
-      <c r="D1" s="363"/>
-      <c r="E1" s="363"/>
-      <c r="F1" s="363"/>
-      <c r="G1" s="363"/>
-      <c r="H1" s="363"/>
-      <c r="I1" s="363"/>
-      <c r="J1" s="363"/>
-      <c r="K1" s="363"/>
+      <c r="B1" s="366"/>
+      <c r="C1" s="366"/>
+      <c r="D1" s="366"/>
+      <c r="E1" s="366"/>
+      <c r="F1" s="366"/>
+      <c r="G1" s="366"/>
+      <c r="H1" s="366"/>
+      <c r="I1" s="366"/>
+      <c r="J1" s="366"/>
+      <c r="K1" s="366"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="363"/>
-      <c r="B2" s="363"/>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
+      <c r="A2" s="366"/>
+      <c r="B2" s="366"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
@@ -21926,10 +21926,10 @@
     </row>
     <row r="5" spans="1:11" ht="21">
       <c r="A5" s="13"/>
-      <c r="B5" s="364" t="s">
+      <c r="B5" s="367" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="364" t="s">
+      <c r="C5" s="367" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="112" t="s">
@@ -21945,8 +21945,8 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="364"/>
-      <c r="C6" s="364"/>
+      <c r="B6" s="367"/>
+      <c r="C6" s="367"/>
       <c r="D6" s="112" t="s">
         <v>100</v>
       </c>
@@ -22232,10 +22232,10 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="364" t="s">
+      <c r="B6" s="367" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="364" t="s">
+      <c r="C6" s="367" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="270" t="s">
@@ -22253,8 +22253,8 @@
     </row>
     <row r="7" spans="1:11" ht="21">
       <c r="A7" s="13"/>
-      <c r="B7" s="364"/>
-      <c r="C7" s="364"/>
+      <c r="B7" s="367"/>
+      <c r="C7" s="367"/>
       <c r="D7" s="270" t="s">
         <v>100</v>
       </c>
@@ -22670,30 +22670,30 @@
   <sheetData>
     <row r="1" spans="2:11" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:11" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1752</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
     </row>
     <row r="3" spans="2:11" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
     </row>
     <row r="4" spans="2:11" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -23108,45 +23108,45 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A2" s="363" t="s">
+      <c r="A2" s="366" t="s">
         <v>1569</v>
       </c>
-      <c r="B2" s="363"/>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
+      <c r="B2" s="366"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
     </row>
     <row r="3" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A3" s="363"/>
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
+      <c r="A3" s="366"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
     </row>
     <row r="4" spans="1:11" ht="16.95" customHeight="1">
-      <c r="A4" s="363"/>
-      <c r="B4" s="363"/>
-      <c r="C4" s="363"/>
-      <c r="D4" s="363"/>
-      <c r="E4" s="363"/>
-      <c r="F4" s="363"/>
-      <c r="G4" s="363"/>
-      <c r="H4" s="363"/>
-      <c r="I4" s="363"/>
-      <c r="J4" s="363"/>
-      <c r="K4" s="363"/>
+      <c r="A4" s="366"/>
+      <c r="B4" s="366"/>
+      <c r="C4" s="366"/>
+      <c r="D4" s="366"/>
+      <c r="E4" s="366"/>
+      <c r="F4" s="366"/>
+      <c r="G4" s="366"/>
+      <c r="H4" s="366"/>
+      <c r="I4" s="366"/>
+      <c r="J4" s="366"/>
+      <c r="K4" s="366"/>
     </row>
     <row r="5" spans="1:11" ht="16.95" customHeight="1" thickBot="1">
       <c r="A5" s="111"/>
@@ -23183,7 +23183,7 @@
     <row r="7" spans="1:11" ht="21">
       <c r="A7" s="13"/>
       <c r="B7" s="419"/>
-      <c r="C7" s="364"/>
+      <c r="C7" s="367"/>
       <c r="D7" s="312" t="s">
         <v>100</v>
       </c>
@@ -23412,45 +23412,45 @@
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="363" t="s">
+      <c r="A2" s="366" t="s">
         <v>1691</v>
       </c>
-      <c r="B2" s="363"/>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
+      <c r="B2" s="366"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="363"/>
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
+      <c r="A3" s="366"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="363"/>
-      <c r="B4" s="363"/>
-      <c r="C4" s="363"/>
-      <c r="D4" s="363"/>
-      <c r="E4" s="363"/>
-      <c r="F4" s="363"/>
-      <c r="G4" s="363"/>
-      <c r="H4" s="363"/>
-      <c r="I4" s="363"/>
-      <c r="J4" s="363"/>
-      <c r="K4" s="363"/>
+      <c r="A4" s="366"/>
+      <c r="B4" s="366"/>
+      <c r="C4" s="366"/>
+      <c r="D4" s="366"/>
+      <c r="E4" s="366"/>
+      <c r="F4" s="366"/>
+      <c r="G4" s="366"/>
+      <c r="H4" s="366"/>
+      <c r="I4" s="366"/>
+      <c r="J4" s="366"/>
+      <c r="K4" s="366"/>
     </row>
     <row r="5" spans="1:11" ht="45">
       <c r="A5" s="111"/>
@@ -23467,10 +23467,10 @@
     </row>
     <row r="6" spans="1:11" ht="21">
       <c r="A6" s="13"/>
-      <c r="B6" s="364" t="s">
+      <c r="B6" s="367" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="364" t="s">
+      <c r="C6" s="367" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="112" t="s">
@@ -23488,8 +23488,8 @@
     </row>
     <row r="7" spans="1:11" ht="21">
       <c r="A7" s="13"/>
-      <c r="B7" s="364"/>
-      <c r="C7" s="364"/>
+      <c r="B7" s="367"/>
+      <c r="C7" s="367"/>
       <c r="D7" s="112" t="s">
         <v>100</v>
       </c>
@@ -23786,30 +23786,30 @@
   <sheetData>
     <row r="1" spans="2:11" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:11" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1570</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
     </row>
     <row r="3" spans="2:11" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
     </row>
     <row r="4" spans="2:11" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -24225,30 +24225,30 @@
   <sheetData>
     <row r="1" spans="2:11" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:11" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1514</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
     </row>
     <row r="3" spans="2:11" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
     </row>
     <row r="4" spans="2:11" ht="19.05" customHeight="1"/>
     <row r="5" spans="2:11" ht="19.05" customHeight="1" thickBot="1">
@@ -24495,28 +24495,28 @@
   <sheetData>
     <row r="1" spans="2:10" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:10" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1766</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
     </row>
     <row r="3" spans="2:10" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
     </row>
     <row r="4" spans="2:10" ht="19.05" customHeight="1">
       <c r="B4" s="334"/>
@@ -24552,10 +24552,10 @@
     </row>
     <row r="8" spans="2:10" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B8" s="13"/>
-      <c r="C8" s="364" t="s">
+      <c r="C8" s="367" t="s">
         <v>102</v>
       </c>
-      <c r="D8" s="364" t="s">
+      <c r="D8" s="367" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="112" t="s">
@@ -24568,8 +24568,8 @@
     </row>
     <row r="9" spans="2:10" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B9" s="13"/>
-      <c r="C9" s="364"/>
-      <c r="D9" s="364"/>
+      <c r="C9" s="367"/>
+      <c r="D9" s="367"/>
       <c r="E9" s="112" t="s">
         <v>100</v>
       </c>
@@ -24787,28 +24787,28 @@
   <sheetData>
     <row r="1" spans="2:10" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:10" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1593</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
     </row>
     <row r="3" spans="2:10" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
     </row>
     <row r="4" spans="2:10" ht="19.05" customHeight="1"/>
     <row r="5" spans="2:10" ht="19.05" customHeight="1" thickBot="1">
@@ -25372,28 +25372,28 @@
   <sheetData>
     <row r="1" spans="2:10" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:10" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1571</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
     </row>
     <row r="3" spans="2:10" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
     </row>
     <row r="4" spans="2:10" ht="19.05" customHeight="1"/>
     <row r="5" spans="2:10" ht="19.05" customHeight="1">
@@ -25403,10 +25403,10 @@
     </row>
     <row r="6" spans="2:10" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="364" t="s">
+      <c r="C6" s="367" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="364" t="s">
+      <c r="D6" s="367" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="112" t="s">
@@ -25663,34 +25663,34 @@
   <sheetData>
     <row r="1" spans="2:13" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:13" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1572</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
-      <c r="L2" s="363"/>
-      <c r="M2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
+      <c r="L2" s="366"/>
+      <c r="M2" s="366"/>
     </row>
     <row r="3" spans="2:13" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
-      <c r="L3" s="363"/>
-      <c r="M3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
+      <c r="L3" s="366"/>
+      <c r="M3" s="366"/>
     </row>
     <row r="4" spans="2:13" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -26764,45 +26764,45 @@
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="363" t="s">
+      <c r="A2" s="366" t="s">
         <v>1573</v>
       </c>
-      <c r="B2" s="363"/>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
+      <c r="B2" s="366"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="363"/>
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
+      <c r="A3" s="366"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="363"/>
-      <c r="B4" s="363"/>
-      <c r="C4" s="363"/>
-      <c r="D4" s="363"/>
-      <c r="E4" s="363"/>
-      <c r="F4" s="363"/>
-      <c r="G4" s="363"/>
-      <c r="H4" s="363"/>
-      <c r="I4" s="363"/>
-      <c r="J4" s="363"/>
-      <c r="K4" s="363"/>
+      <c r="A4" s="366"/>
+      <c r="B4" s="366"/>
+      <c r="C4" s="366"/>
+      <c r="D4" s="366"/>
+      <c r="E4" s="366"/>
+      <c r="F4" s="366"/>
+      <c r="G4" s="366"/>
+      <c r="H4" s="366"/>
+      <c r="I4" s="366"/>
+      <c r="J4" s="366"/>
+      <c r="K4" s="366"/>
     </row>
     <row r="5" spans="1:11" ht="45.6" thickBot="1">
       <c r="A5" s="111"/>
@@ -27007,26 +27007,26 @@
   <sheetData>
     <row r="1" spans="2:9" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:9" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1574</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
     </row>
     <row r="3" spans="2:9" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
     </row>
     <row r="4" spans="2:9" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -27821,26 +27821,26 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1581</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
     </row>
     <row r="3" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
     </row>
     <row r="4" spans="2:12" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -28758,24 +28758,24 @@
   <sheetData>
     <row r="1" spans="2:8" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:8" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1580</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
     </row>
     <row r="3" spans="2:8" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
     </row>
     <row r="4" spans="2:8" ht="19.05" customHeight="1">
       <c r="B4" s="334"/>
@@ -30036,38 +30036,38 @@
   <sheetData>
     <row r="1" spans="2:15" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:15" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1123</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
-      <c r="L2" s="363"/>
-      <c r="M2" s="363"/>
-      <c r="N2" s="363"/>
-      <c r="O2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
+      <c r="L2" s="366"/>
+      <c r="M2" s="366"/>
+      <c r="N2" s="366"/>
+      <c r="O2" s="366"/>
     </row>
     <row r="3" spans="2:15" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
-      <c r="L3" s="363"/>
-      <c r="M3" s="363"/>
-      <c r="N3" s="363"/>
-      <c r="O3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
+      <c r="L3" s="366"/>
+      <c r="M3" s="366"/>
+      <c r="N3" s="366"/>
+      <c r="O3" s="366"/>
     </row>
     <row r="4" spans="2:15" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -31329,30 +31329,30 @@
   <sheetData>
     <row r="1" spans="1:11" ht="10.050000000000001" customHeight="1"/>
     <row r="2" spans="1:11" ht="16.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1699</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
     </row>
     <row r="3" spans="1:11" ht="16.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
     </row>
     <row r="4" spans="1:11" ht="16.05" customHeight="1">
       <c r="B4" t="s">
@@ -31488,30 +31488,30 @@
   <sheetData>
     <row r="2" spans="1:11" ht="12" customHeight="1"/>
     <row r="3" spans="1:11">
-      <c r="B3" s="363" t="s">
+      <c r="B3" s="366" t="s">
         <v>1582</v>
       </c>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="B4" s="363"/>
-      <c r="C4" s="363"/>
-      <c r="D4" s="363"/>
-      <c r="E4" s="363"/>
-      <c r="F4" s="363"/>
-      <c r="G4" s="363"/>
-      <c r="H4" s="363"/>
-      <c r="I4" s="363"/>
-      <c r="J4" s="363"/>
-      <c r="K4" s="363"/>
+      <c r="B4" s="366"/>
+      <c r="C4" s="366"/>
+      <c r="D4" s="366"/>
+      <c r="E4" s="366"/>
+      <c r="F4" s="366"/>
+      <c r="G4" s="366"/>
+      <c r="H4" s="366"/>
+      <c r="I4" s="366"/>
+      <c r="J4" s="366"/>
+      <c r="K4" s="366"/>
     </row>
     <row r="5" spans="1:11">
       <c r="B5" t="s">
@@ -31630,45 +31630,45 @@
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="363" t="s">
+      <c r="A2" s="366" t="s">
         <v>1730</v>
       </c>
-      <c r="B2" s="363"/>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
+      <c r="B2" s="366"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="363"/>
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
+      <c r="A3" s="366"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="363"/>
-      <c r="B4" s="363"/>
-      <c r="C4" s="363"/>
-      <c r="D4" s="363"/>
-      <c r="E4" s="363"/>
-      <c r="F4" s="363"/>
-      <c r="G4" s="363"/>
-      <c r="H4" s="363"/>
-      <c r="I4" s="363"/>
-      <c r="J4" s="363"/>
-      <c r="K4" s="363"/>
+      <c r="A4" s="366"/>
+      <c r="B4" s="366"/>
+      <c r="C4" s="366"/>
+      <c r="D4" s="366"/>
+      <c r="E4" s="366"/>
+      <c r="F4" s="366"/>
+      <c r="G4" s="366"/>
+      <c r="H4" s="366"/>
+      <c r="I4" s="366"/>
+      <c r="J4" s="366"/>
+      <c r="K4" s="366"/>
     </row>
     <row r="5" spans="1:11" ht="45.6" thickBot="1">
       <c r="A5" s="111"/>
@@ -31857,34 +31857,34 @@
   <sheetData>
     <row r="1" spans="2:13" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:13" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1583</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
-      <c r="L2" s="363"/>
-      <c r="M2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
+      <c r="L2" s="366"/>
+      <c r="M2" s="366"/>
     </row>
     <row r="3" spans="2:13" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
-      <c r="L3" s="363"/>
-      <c r="M3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
+      <c r="L3" s="366"/>
+      <c r="M3" s="366"/>
     </row>
     <row r="4" spans="2:13" ht="19.05" customHeight="1">
       <c r="B4" s="4" t="s">
@@ -32688,34 +32688,34 @@
   <sheetData>
     <row r="1" spans="2:13" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:13" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1584</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
-      <c r="L2" s="363"/>
-      <c r="M2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
+      <c r="L2" s="366"/>
+      <c r="M2" s="366"/>
     </row>
     <row r="3" spans="2:13" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
-      <c r="L3" s="363"/>
-      <c r="M3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
+      <c r="L3" s="366"/>
+      <c r="M3" s="366"/>
     </row>
     <row r="4" spans="2:13" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -33165,30 +33165,30 @@
   <sheetData>
     <row r="1" spans="2:11" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:11" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1758</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
     </row>
     <row r="3" spans="2:11" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
     </row>
     <row r="4" spans="2:11" ht="19.05" customHeight="1">
       <c r="B4" t="s">
@@ -33583,34 +33583,34 @@
   <sheetData>
     <row r="1" spans="2:13" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:13" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1585</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
-      <c r="L2" s="363"/>
-      <c r="M2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
+      <c r="L2" s="366"/>
+      <c r="M2" s="366"/>
     </row>
     <row r="3" spans="2:13" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
-      <c r="L3" s="363"/>
-      <c r="M3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
+      <c r="L3" s="366"/>
+      <c r="M3" s="366"/>
     </row>
     <row r="4" spans="2:13" ht="19.05" customHeight="1"/>
     <row r="5" spans="2:13" ht="19.05" customHeight="1">
@@ -33620,10 +33620,10 @@
     </row>
     <row r="6" spans="2:13" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="364" t="s">
+      <c r="C6" s="367" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="364" t="s">
+      <c r="D6" s="367" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="112" t="s">
@@ -33633,8 +33633,8 @@
       <c r="G6" s="13"/>
     </row>
     <row r="7" spans="2:13" s="9" customFormat="1" ht="19.05" customHeight="1">
-      <c r="C7" s="364"/>
-      <c r="D7" s="364"/>
+      <c r="C7" s="367"/>
+      <c r="D7" s="367"/>
       <c r="E7" s="112" t="s">
         <v>100</v>
       </c>
@@ -34202,41 +34202,41 @@
       </c>
     </row>
     <row r="2" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1588</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
-      <c r="L2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
+      <c r="L2" s="366"/>
     </row>
     <row r="3" spans="2:12" ht="19.05" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
-      <c r="L3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
+      <c r="L3" s="366"/>
     </row>
     <row r="4" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="5" spans="2:12" ht="19.05" customHeight="1"/>
     <row r="6" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B6" s="13"/>
-      <c r="C6" s="364" t="s">
+      <c r="C6" s="367" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="364" t="s">
+      <c r="D6" s="367" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="112" t="s">
@@ -34247,8 +34247,8 @@
     </row>
     <row r="7" spans="2:12" s="9" customFormat="1" ht="19.05" customHeight="1">
       <c r="B7" s="13"/>
-      <c r="C7" s="364"/>
-      <c r="D7" s="364"/>
+      <c r="C7" s="367"/>
+      <c r="D7" s="367"/>
       <c r="E7" s="112" t="s">
         <v>100</v>
       </c>
@@ -34629,32 +34629,32 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.95" customHeight="1"/>
     <row r="2" spans="2:12" ht="19.95" customHeight="1">
-      <c r="B2" s="363" t="s">
+      <c r="B2" s="366" t="s">
         <v>1586</v>
       </c>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
-      <c r="L2" s="363"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
+      <c r="L2" s="366"/>
     </row>
     <row r="3" spans="2:12" ht="19.95" customHeight="1">
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
-      <c r="L3" s="363"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
+      <c r="L3" s="366"/>
     </row>
     <row r="4" spans="2:12" ht="19.95" customHeight="1">
       <c r="B4" t="s">
@@ -35143,55 +35143,55 @@
   <sheetData>
     <row r="1" spans="2:25" ht="19.05" customHeight="1"/>
     <row r="2" spans="2:25" ht="19.05" customHeight="1">
-      <c r="B2" s="442" t="s">
+      <c r="B2" s="438" t="s">
         <v>1587</v>
       </c>
-      <c r="C2" s="442"/>
-      <c r="D2" s="442"/>
-      <c r="E2" s="442"/>
-      <c r="F2" s="442"/>
-      <c r="G2" s="442"/>
-      <c r="H2" s="442"/>
-      <c r="I2" s="442"/>
-      <c r="J2" s="442"/>
-      <c r="K2" s="442"/>
-      <c r="L2" s="442"/>
-      <c r="M2" s="442"/>
-      <c r="P2" s="441" t="s">
+      <c r="C2" s="438"/>
+      <c r="D2" s="438"/>
+      <c r="E2" s="438"/>
+      <c r="F2" s="438"/>
+      <c r="G2" s="438"/>
+      <c r="H2" s="438"/>
+      <c r="I2" s="438"/>
+      <c r="J2" s="438"/>
+      <c r="K2" s="438"/>
+      <c r="L2" s="438"/>
+      <c r="M2" s="438"/>
+      <c r="P2" s="437" t="s">
         <v>1587</v>
       </c>
-      <c r="Q2" s="441"/>
-      <c r="R2" s="441"/>
-      <c r="S2" s="441"/>
-      <c r="T2" s="441"/>
-      <c r="U2" s="441"/>
-      <c r="V2" s="441"/>
-      <c r="W2" s="441"/>
-      <c r="X2" s="441"/>
+      <c r="Q2" s="437"/>
+      <c r="R2" s="437"/>
+      <c r="S2" s="437"/>
+      <c r="T2" s="437"/>
+      <c r="U2" s="437"/>
+      <c r="V2" s="437"/>
+      <c r="W2" s="437"/>
+      <c r="X2" s="437"/>
       <c r="Y2" s="47"/>
     </row>
     <row r="3" spans="2:25" ht="19.05" customHeight="1">
-      <c r="B3" s="442"/>
-      <c r="C3" s="442"/>
-      <c r="D3" s="442"/>
-      <c r="E3" s="442"/>
-      <c r="F3" s="442"/>
-      <c r="G3" s="442"/>
-      <c r="H3" s="442"/>
-      <c r="I3" s="442"/>
-      <c r="J3" s="442"/>
-      <c r="K3" s="442"/>
-      <c r="L3" s="442"/>
-      <c r="M3" s="442"/>
-      <c r="P3" s="441"/>
-      <c r="Q3" s="441"/>
-      <c r="R3" s="441"/>
-      <c r="S3" s="441"/>
-      <c r="T3" s="441"/>
-      <c r="U3" s="441"/>
-      <c r="V3" s="441"/>
-      <c r="W3" s="441"/>
-      <c r="X3" s="441"/>
+      <c r="B3" s="438"/>
+      <c r="C3" s="438"/>
+      <c r="D3" s="438"/>
+      <c r="E3" s="438"/>
+      <c r="F3" s="438"/>
+      <c r="G3" s="438"/>
+      <c r="H3" s="438"/>
+      <c r="I3" s="438"/>
+      <c r="J3" s="438"/>
+      <c r="K3" s="438"/>
+      <c r="L3" s="438"/>
+      <c r="M3" s="438"/>
+      <c r="P3" s="437"/>
+      <c r="Q3" s="437"/>
+      <c r="R3" s="437"/>
+      <c r="S3" s="437"/>
+      <c r="T3" s="437"/>
+      <c r="U3" s="437"/>
+      <c r="V3" s="437"/>
+      <c r="W3" s="437"/>
+      <c r="X3" s="437"/>
       <c r="Y3" s="47"/>
     </row>
     <row r="4" spans="2:25" ht="19.05" customHeight="1">
@@ -35282,9 +35282,9 @@
       <c r="I9" s="87">
         <v>5.7095231538849882</v>
       </c>
-      <c r="P9" s="438"/>
-      <c r="Q9" s="439"/>
-      <c r="R9" s="440"/>
+      <c r="P9" s="440"/>
+      <c r="Q9" s="441"/>
+      <c r="R9" s="442"/>
     </row>
     <row r="10" spans="2:25" s="7" customFormat="1" ht="19.05" customHeight="1">
       <c r="B10" s="315">
@@ -35336,10 +35336,10 @@
       <c r="I11" s="87">
         <v>7.9196512001468626</v>
       </c>
-      <c r="P11" s="437" t="s">
+      <c r="P11" s="439" t="s">
         <v>440</v>
       </c>
-      <c r="Q11" s="437"/>
+      <c r="Q11" s="439"/>
       <c r="R11" s="189">
         <v>10.080053500127852</v>
       </c>
@@ -35364,10 +35364,10 @@
       <c r="I12" s="87">
         <v>5.7824847400064252</v>
       </c>
-      <c r="P12" s="437" t="s">
+      <c r="P12" s="439" t="s">
         <v>441</v>
       </c>
-      <c r="Q12" s="437"/>
+      <c r="Q12" s="439"/>
       <c r="R12" s="189">
         <v>8.0737987057689669</v>
       </c>
@@ -35392,10 +35392,10 @@
       <c r="I13" s="87">
         <v>6.0682509523153891</v>
       </c>
-      <c r="P13" s="437" t="s">
+      <c r="P13" s="439" t="s">
         <v>442</v>
       </c>
-      <c r="Q13" s="437"/>
+      <c r="Q13" s="439"/>
       <c r="R13" s="189">
         <v>7.9935485139946119</v>
       </c>
@@ -35420,10 +35420,10 @@
       <c r="I14" s="87">
         <v>6.1868135297627243</v>
       </c>
-      <c r="P14" s="437" t="s">
+      <c r="P14" s="439" t="s">
         <v>443</v>
       </c>
-      <c r="Q14" s="437"/>
+      <c r="Q14" s="439"/>
       <c r="R14" s="189">
         <v>7.3515469797997683</v>
       </c>
@@ -36369,16 +36369,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="P8:R9"/>
     <mergeCell ref="P2:X3"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="B2:M3"/>
     <mergeCell ref="H6:H7"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="P8:R9"/>
   </mergeCells>
   <phoneticPr fontId="41" type="noConversion"/>
   <pageMargins left="0.5" right="0.5" top="0.39000000000000007" bottom="0.39000000000000007" header="0" footer="0"/>
@@ -36400,38 +36400,38 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14">
-      <c r="A2" s="363" t="s">
+      <c r="A2" s="366" t="s">
         <v>1518</v>
       </c>
-      <c r="B2" s="363"/>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
-      <c r="L2" s="363"/>
-      <c r="M2" s="363"/>
-      <c r="N2" s="363"/>
+      <c r="B2" s="366"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
+      <c r="L2" s="366"/>
+      <c r="M2" s="366"/>
+      <c r="N2" s="366"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="363"/>
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
-      <c r="L3" s="363"/>
-      <c r="M3" s="363"/>
-      <c r="N3" s="363"/>
+      <c r="A3" s="366"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
+      <c r="L3" s="366"/>
+      <c r="M3" s="366"/>
+      <c r="N3" s="366"/>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
@@ -38861,45 +38861,45 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A2" s="363" t="s">
+      <c r="A2" s="366" t="s">
         <v>1519</v>
       </c>
-      <c r="B2" s="363"/>
-      <c r="C2" s="363"/>
-      <c r="D2" s="363"/>
-      <c r="E2" s="363"/>
-      <c r="F2" s="363"/>
-      <c r="G2" s="363"/>
-      <c r="H2" s="363"/>
-      <c r="I2" s="363"/>
-      <c r="J2" s="363"/>
-      <c r="K2" s="363"/>
+      <c r="B2" s="366"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
+      <c r="J2" s="366"/>
+      <c r="K2" s="366"/>
     </row>
     <row r="3" spans="1:11" ht="16.05" customHeight="1">
-      <c r="A3" s="363"/>
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
+      <c r="A3" s="366"/>
+      <c r="B3" s="366"/>
+      <c r="C3" s="366"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="366"/>
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="366"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
     </row>
     <row r="4" spans="1:11" ht="16.95" customHeight="1">
-      <c r="A4" s="363"/>
-      <c r="B4" s="363"/>
-      <c r="C4" s="363"/>
-      <c r="D4" s="363"/>
-      <c r="E4" s="363"/>
-      <c r="F4" s="363"/>
-      <c r="G4" s="363"/>
-      <c r="H4" s="363"/>
-      <c r="I4" s="363"/>
-      <c r="J4" s="363"/>
-      <c r="K4" s="363"/>
+      <c r="A4" s="366"/>
+      <c r="B4" s="366"/>
+      <c r="C4" s="366"/>
+      <c r="D4" s="366"/>
+      <c r="E4" s="366"/>
+      <c r="F4" s="366"/>
+      <c r="G4" s="366"/>
+      <c r="H4" s="366"/>
+      <c r="I4" s="366"/>
+      <c r="J4" s="366"/>
+      <c r="K4" s="366"/>
     </row>
     <row r="5" spans="1:11" ht="16.95" customHeight="1" thickBot="1">
       <c r="A5" s="111"/>
@@ -39036,25 +39036,25 @@
       </c>
     </row>
     <row r="2" spans="2:17" ht="19.05" customHeight="1">
-      <c r="B2" s="365" t="s">
+      <c r="B2" s="363" t="s">
         <v>1520</v>
       </c>
-      <c r="C2" s="365"/>
-      <c r="D2" s="365"/>
-      <c r="E2" s="365"/>
-      <c r="F2" s="365"/>
-      <c r="G2" s="365"/>
-      <c r="H2" s="365"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
       <c r="I2" s="38"/>
     </row>
     <row r="3" spans="2:17" ht="19.05" customHeight="1">
-      <c r="B3" s="365"/>
-      <c r="C3" s="365"/>
-      <c r="D3" s="365"/>
-      <c r="E3" s="365"/>
-      <c r="F3" s="365"/>
-      <c r="G3" s="365"/>
-      <c r="H3" s="365"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
       <c r="I3" s="38"/>
     </row>
     <row r="4" spans="2:17" ht="19.05" customHeight="1"/>
@@ -39134,9 +39134,9 @@
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="32"/>
-      <c r="G9" s="367"/>
-      <c r="H9" s="367"/>
-      <c r="I9" s="367"/>
+      <c r="G9" s="365"/>
+      <c r="H9" s="365"/>
+      <c r="I9" s="365"/>
       <c r="J9" s="32"/>
       <c r="L9" s="31"/>
       <c r="M9" s="32"/>
@@ -39150,9 +39150,9 @@
       <c r="D10" s="53"/>
       <c r="E10" s="31"/>
       <c r="F10" s="32"/>
-      <c r="G10" s="367"/>
-      <c r="H10" s="367"/>
-      <c r="I10" s="367"/>
+      <c r="G10" s="365"/>
+      <c r="H10" s="365"/>
+      <c r="I10" s="365"/>
       <c r="J10" s="32"/>
       <c r="L10" s="31"/>
       <c r="M10" s="32"/>
@@ -39575,25 +39575,25 @@
       <c r="A1" s="333" t="s">
         <v>1701</v>
       </c>
-      <c r="B1" s="365" t="s">
+      <c r="B1" s="363" t="s">
         <v>1618</v>
       </c>
-      <c r="C1" s="365"/>
-      <c r="D1" s="365"/>
-      <c r="E1" s="365"/>
-      <c r="F1" s="365"/>
-      <c r="G1" s="365"/>
-      <c r="H1" s="365"/>
+      <c r="C1" s="363"/>
+      <c r="D1" s="363"/>
+      <c r="E1" s="363"/>
+      <c r="F1" s="363"/>
+      <c r="G1" s="363"/>
+      <c r="H1" s="363"/>
       <c r="I1" s="38"/>
     </row>
     <row r="2" spans="1:17" s="30" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B2" s="365"/>
-      <c r="C2" s="365"/>
-      <c r="D2" s="365"/>
-      <c r="E2" s="365"/>
-      <c r="F2" s="365"/>
-      <c r="G2" s="365"/>
-      <c r="H2" s="365"/>
+      <c r="B2" s="363"/>
+      <c r="C2" s="363"/>
+      <c r="D2" s="363"/>
+      <c r="E2" s="363"/>
+      <c r="F2" s="363"/>
+      <c r="G2" s="363"/>
+      <c r="H2" s="363"/>
       <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:17" s="30" customFormat="1" ht="19.05" customHeight="1"/>
@@ -39603,10 +39603,10 @@
       <c r="Q4" s="41"/>
     </row>
     <row r="5" spans="1:17" s="30" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B5" s="366" t="s">
+      <c r="B5" s="364" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="366" t="s">
+      <c r="C5" s="364" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="106" t="s">
@@ -39624,8 +39624,8 @@
       <c r="Q5" s="41"/>
     </row>
     <row r="6" spans="1:17" s="30" customFormat="1" ht="19.05" customHeight="1">
-      <c r="B6" s="366"/>
-      <c r="C6" s="366"/>
+      <c r="B6" s="364"/>
+      <c r="C6" s="364"/>
       <c r="D6" s="106" t="s">
         <v>104</v>
       </c>
@@ -39673,9 +39673,9 @@
       </c>
       <c r="E8" s="31"/>
       <c r="F8" s="32"/>
-      <c r="G8" s="367"/>
-      <c r="H8" s="367"/>
-      <c r="I8" s="367"/>
+      <c r="G8" s="365"/>
+      <c r="H8" s="365"/>
+      <c r="I8" s="365"/>
       <c r="J8" s="32"/>
       <c r="L8" s="31"/>
       <c r="M8" s="32"/>
@@ -39695,9 +39695,9 @@
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="32"/>
-      <c r="G9" s="367"/>
-      <c r="H9" s="367"/>
-      <c r="I9" s="367"/>
+      <c r="G9" s="365"/>
+      <c r="H9" s="365"/>
+      <c r="I9" s="365"/>
       <c r="J9" s="32"/>
       <c r="L9" s="31"/>
       <c r="M9" s="32"/>
